--- a/data/punts/punts-mesura-at.xlsx
+++ b/data/punts/punts-mesura-at.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\punts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0754F07-5958-419A-84EE-617DD9643AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFDC6187-A128-43B5-BBC5-A1100F6C7CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4CA701B3-5EB8-45D8-B6BB-1F057196BE44}"/>
   </bookViews>
@@ -805,7 +805,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -814,9 +814,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1177,10 +1174,10 @@
     <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
     <col min="6" max="6" width="11.44140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="1"/>
-    <col min="8" max="9" width="9.5546875" style="7" customWidth="1"/>
+    <col min="8" max="9" width="9.5546875" style="6" customWidth="1"/>
     <col min="10" max="10" width="11" style="1" customWidth="1"/>
     <col min="11" max="11" width="13.109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17.109375" style="7" customWidth="1"/>
+    <col min="12" max="12" width="17.109375" style="6" customWidth="1"/>
     <col min="13" max="13" width="21.44140625" style="1" customWidth="1"/>
     <col min="14" max="14" width="21.77734375" style="1" customWidth="1"/>
     <col min="15" max="16384" width="8.88671875" style="1"/>
@@ -1208,10 +1205,10 @@
       <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>87</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -1220,7 +1217,7 @@
       <c r="K1" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>88</v>
       </c>
       <c r="M1" s="2" t="s">
@@ -1252,29 +1249,29 @@
       <c r="G2" s="3">
         <v>150</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>168.3</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="5">
         <v>4.8</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K2" s="4">
-        <f>PI()*(((H2-I2)*10^-3)^2/4)</f>
-        <v>2.0995460053481439E-2</v>
-      </c>
-      <c r="L2" s="6">
+      <c r="K2" s="3">
+        <f>PI()*(((H2-2*I2)*10^-3)^2/4)</f>
+        <v>1.9780794669897482E-2</v>
+      </c>
+      <c r="L2" s="5">
         <v>3</v>
       </c>
-      <c r="M2" s="4">
-        <f>L2*K2</f>
-        <v>6.2986380160444319E-2</v>
-      </c>
-      <c r="N2" s="4">
+      <c r="M2" s="3">
+        <f t="shared" ref="M2:M33" si="0">L2*K2</f>
+        <v>5.9342384009692446E-2</v>
+      </c>
+      <c r="N2" s="3">
         <f>M2*3600</f>
-        <v>226.75096857759954</v>
+        <v>213.63258243489281</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -1299,29 +1296,29 @@
       <c r="G3" s="3">
         <v>150</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>168.3</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="5">
         <v>4.8</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K3" s="4">
-        <f>PI()*(((H3-I3)*10^-3)^2/4)</f>
-        <v>2.0995460053481439E-2</v>
-      </c>
-      <c r="L3" s="6">
+      <c r="K3" s="3">
+        <f t="shared" ref="K3:K66" si="1">PI()*(((H3-2*I3)*10^-3)^2/4)</f>
+        <v>1.9780794669897482E-2</v>
+      </c>
+      <c r="L3" s="5">
         <v>3</v>
       </c>
-      <c r="M3" s="4">
-        <f>L3*K3</f>
-        <v>6.2986380160444319E-2</v>
-      </c>
-      <c r="N3" s="4">
-        <f t="shared" ref="N3:N66" si="0">M3*3600</f>
-        <v>226.75096857759954</v>
+      <c r="M3" s="3">
+        <f t="shared" si="0"/>
+        <v>5.9342384009692446E-2</v>
+      </c>
+      <c r="N3" s="3">
+        <f t="shared" ref="N3:N66" si="2">M3*3600</f>
+        <v>213.63258243489281</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -1346,29 +1343,29 @@
       <c r="G4" s="3">
         <v>150</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>168.3</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>4.8</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K4" s="4">
-        <f t="shared" ref="K3:K33" si="1">PI()*(((H4-I4)*10^-3)^2/4)</f>
-        <v>2.0995460053481439E-2</v>
-      </c>
-      <c r="L4" s="6">
+      <c r="K4" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9780794669897482E-2</v>
+      </c>
+      <c r="L4" s="5">
         <v>3</v>
       </c>
-      <c r="M4" s="4">
-        <f>L4*K4</f>
-        <v>6.2986380160444319E-2</v>
-      </c>
-      <c r="N4" s="4">
+      <c r="M4" s="3">
         <f t="shared" si="0"/>
-        <v>226.75096857759954</v>
+        <v>5.9342384009692446E-2</v>
+      </c>
+      <c r="N4" s="3">
+        <f t="shared" si="2"/>
+        <v>213.63258243489281</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -1393,29 +1390,29 @@
       <c r="G5" s="3">
         <v>150</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>168.3</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>4.8</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K5" s="4">
-        <f t="shared" si="1"/>
-        <v>2.0995460053481439E-2</v>
-      </c>
-      <c r="L5" s="6">
+      <c r="K5" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9780794669897482E-2</v>
+      </c>
+      <c r="L5" s="5">
         <v>3.4</v>
       </c>
-      <c r="M5" s="4">
-        <f>L5*K5</f>
-        <v>7.138456418183689E-2</v>
-      </c>
-      <c r="N5" s="4">
+      <c r="M5" s="3">
         <f t="shared" si="0"/>
-        <v>256.9844310546128</v>
+        <v>6.7254701877651438E-2</v>
+      </c>
+      <c r="N5" s="3">
+        <f t="shared" si="2"/>
+        <v>242.11692675954518</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1440,29 +1437,29 @@
       <c r="G6" s="3">
         <v>150</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>168.3</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <v>4.8</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="4">
-        <f t="shared" si="1"/>
-        <v>2.0995460053481439E-2</v>
-      </c>
-      <c r="L6" s="6">
+      <c r="K6" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9780794669897482E-2</v>
+      </c>
+      <c r="L6" s="5">
         <v>3.4</v>
       </c>
-      <c r="M6" s="4">
-        <f>L6*K6</f>
-        <v>7.138456418183689E-2</v>
-      </c>
-      <c r="N6" s="4">
+      <c r="M6" s="3">
         <f t="shared" si="0"/>
-        <v>256.9844310546128</v>
+        <v>6.7254701877651438E-2</v>
+      </c>
+      <c r="N6" s="3">
+        <f t="shared" si="2"/>
+        <v>242.11692675954518</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1487,29 +1484,29 @@
       <c r="G7" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>204</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>4.8</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K7" s="4">
-        <f t="shared" si="1"/>
-        <v>3.116510177843532E-2</v>
-      </c>
-      <c r="L7" s="6">
+      <c r="K7" s="3">
+        <f t="shared" si="1"/>
+        <v>2.9681264736291797E-2</v>
+      </c>
+      <c r="L7" s="5">
         <v>1.35</v>
       </c>
-      <c r="M7" s="4">
-        <f>L7*K7</f>
-        <v>4.2072887400887687E-2</v>
-      </c>
-      <c r="N7" s="4">
+      <c r="M7" s="3">
         <f t="shared" si="0"/>
-        <v>151.46239464319567</v>
+        <v>4.0069707393993931E-2</v>
+      </c>
+      <c r="N7" s="3">
+        <f t="shared" si="2"/>
+        <v>144.25094661837815</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1534,29 +1531,29 @@
       <c r="G8" s="3">
         <v>350</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>355.6</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>8</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K8" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4896329995100878E-2</v>
-      </c>
-      <c r="L8" s="6">
+      <c r="K8" s="3">
+        <f t="shared" si="1"/>
+        <v>9.0578525052007072E-2</v>
+      </c>
+      <c r="L8" s="5">
         <v>2.35</v>
       </c>
-      <c r="M8" s="4">
-        <f>L8*K8</f>
-        <v>0.22300637548848706</v>
-      </c>
-      <c r="N8" s="4">
+      <c r="M8" s="3">
         <f t="shared" si="0"/>
-        <v>802.82295175855347</v>
+        <v>0.21285953387221662</v>
+      </c>
+      <c r="N8" s="3">
+        <f t="shared" si="2"/>
+        <v>766.2943219399798</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1581,24 +1578,24 @@
       <c r="G9" s="3">
         <v>200</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>220</v>
       </c>
-      <c r="I9" s="6"/>
+      <c r="I9" s="5"/>
       <c r="J9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="3">
         <f t="shared" si="1"/>
         <v>3.8013271108436497E-2</v>
       </c>
-      <c r="L9" s="6"/>
-      <c r="M9" s="4">
-        <f>L9*K9</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="4">
+      <c r="L9" s="5"/>
+      <c r="M9" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1624,26 +1621,26 @@
       <c r="G10" s="3">
         <v>80</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>88.9</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <v>4</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K10" s="4">
-        <f t="shared" si="1"/>
-        <v>5.661157815750442E-3</v>
-      </c>
-      <c r="L10" s="6"/>
-      <c r="M10" s="4">
-        <f>L10*K10</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="4">
+      <c r="K10" s="3">
+        <f t="shared" si="1"/>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="L10" s="5"/>
+      <c r="M10" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1669,26 +1666,26 @@
       <c r="G11" s="3">
         <v>80</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>88.9</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="5">
         <v>4</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K11" s="4">
-        <f t="shared" si="1"/>
-        <v>5.661157815750442E-3</v>
-      </c>
-      <c r="L11" s="6"/>
-      <c r="M11" s="4">
-        <f>L11*K11</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="4">
+      <c r="K11" s="3">
+        <f t="shared" si="1"/>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="L11" s="5"/>
+      <c r="M11" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1714,26 +1711,26 @@
       <c r="G12" s="3">
         <v>65</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>76.099999999999994</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="5">
         <v>3.6</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K12" s="4">
-        <f t="shared" si="1"/>
-        <v>4.1282490963578371E-3</v>
-      </c>
-      <c r="L12" s="6"/>
-      <c r="M12" s="4">
-        <f>L12*K12</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="4">
+      <c r="K12" s="3">
+        <f t="shared" si="1"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L12" s="5"/>
+      <c r="M12" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1759,26 +1756,26 @@
       <c r="G13" s="3">
         <v>100</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <v>114</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="5">
         <v>4.5</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K13" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4171203286762539E-3</v>
-      </c>
-      <c r="L13" s="6"/>
-      <c r="M13" s="4">
-        <f>L13*K13</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="4">
+      <c r="K13" s="3">
+        <f t="shared" si="1"/>
+        <v>8.6590147514568668E-3</v>
+      </c>
+      <c r="L13" s="5"/>
+      <c r="M13" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1802,22 +1799,22 @@
         <v>33</v>
       </c>
       <c r="G14" s="3"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
       <c r="J14" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="6"/>
-      <c r="M14" s="4">
-        <f>L14*K14</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="4">
+      <c r="K14" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1841,22 +1838,22 @@
         <v>34</v>
       </c>
       <c r="G15" s="3"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
       <c r="J15" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L15" s="6"/>
-      <c r="M15" s="4">
-        <f>L15*K15</f>
-        <v>0</v>
-      </c>
-      <c r="N15" s="4">
+      <c r="K15" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1882,26 +1879,26 @@
       <c r="G16" s="3">
         <v>125</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="5">
         <v>141</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="5">
         <v>5</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K16" s="4">
-        <f t="shared" si="1"/>
-        <v>1.4526724430199206E-2</v>
-      </c>
-      <c r="L16" s="6"/>
-      <c r="M16" s="4">
-        <f>L16*K16</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="4">
+      <c r="K16" s="3">
+        <f t="shared" si="1"/>
+        <v>1.3478217882063612E-2</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1927,29 +1924,29 @@
       <c r="G17" s="3">
         <v>155</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="5">
         <v>155</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="5">
         <v>1.8</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K17" s="4">
-        <f t="shared" si="1"/>
-        <v>1.8433483390497326E-2</v>
-      </c>
-      <c r="L17" s="6">
+      <c r="K17" s="3">
+        <f t="shared" si="1"/>
+        <v>1.8002865285469776E-2</v>
+      </c>
+      <c r="L17" s="5">
         <v>0.7</v>
       </c>
-      <c r="M17" s="4">
-        <f>L17*K17</f>
-        <v>1.2903438373348128E-2</v>
-      </c>
-      <c r="N17" s="4">
+      <c r="M17" s="3">
         <f t="shared" si="0"/>
-        <v>46.452378144053263</v>
+        <v>1.2602005699828842E-2</v>
+      </c>
+      <c r="N17" s="3">
+        <f t="shared" si="2"/>
+        <v>45.367220519383828</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1974,29 +1971,29 @@
       <c r="G18" s="3">
         <v>80</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="5">
         <v>88.9</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="5">
         <v>2</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K18" s="4">
-        <f t="shared" si="1"/>
-        <v>5.9310206246938049E-3</v>
-      </c>
-      <c r="L18" s="6">
+      <c r="K18" s="3">
+        <f t="shared" si="1"/>
+        <v>5.661157815750442E-3</v>
+      </c>
+      <c r="L18" s="5">
         <v>0.5</v>
       </c>
-      <c r="M18" s="4">
-        <f>L18*K18</f>
-        <v>2.9655103123469024E-3</v>
-      </c>
-      <c r="N18" s="4">
+      <c r="M18" s="3">
         <f t="shared" si="0"/>
-        <v>10.675837124448849</v>
+        <v>2.830578907875221E-3</v>
+      </c>
+      <c r="N18" s="3">
+        <f t="shared" si="2"/>
+        <v>10.190084068350796</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -2021,29 +2018,29 @@
       <c r="G19" s="3">
         <v>125</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="5">
         <v>139.69999999999999</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="5">
         <v>2</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K19" s="4">
-        <f t="shared" si="1"/>
-        <v>1.4892162341646401E-2</v>
-      </c>
-      <c r="L19" s="6">
+      <c r="K19" s="3">
+        <f t="shared" si="1"/>
+        <v>1.4462706625900674E-2</v>
+      </c>
+      <c r="L19" s="5">
         <v>0.62</v>
       </c>
-      <c r="M19" s="4">
-        <f>L19*K19</f>
-        <v>9.2331406518207683E-3</v>
-      </c>
-      <c r="N19" s="4">
+      <c r="M19" s="3">
         <f t="shared" si="0"/>
-        <v>33.239306346554763</v>
+        <v>8.9668781080584174E-3</v>
+      </c>
+      <c r="N19" s="3">
+        <f t="shared" si="2"/>
+        <v>32.280761189010306</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -2068,26 +2065,26 @@
       <c r="G20" s="3">
         <v>80</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="5">
         <v>88.9</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="5">
         <v>2</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K20" s="4">
-        <f t="shared" si="1"/>
-        <v>5.9310206246938049E-3</v>
-      </c>
-      <c r="L20" s="6"/>
-      <c r="M20" s="4">
-        <f>L20*K20</f>
-        <v>0</v>
-      </c>
-      <c r="N20" s="4">
+      <c r="K20" s="3">
+        <f t="shared" si="1"/>
+        <v>5.661157815750442E-3</v>
+      </c>
+      <c r="L20" s="5"/>
+      <c r="M20" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2113,29 +2110,29 @@
       <c r="G21" s="3">
         <v>125</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="5">
         <v>139.69999999999999</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="5">
         <v>2</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K21" s="4">
-        <f t="shared" si="1"/>
-        <v>1.4892162341646401E-2</v>
-      </c>
-      <c r="L21" s="6">
+      <c r="K21" s="3">
+        <f t="shared" si="1"/>
+        <v>1.4462706625900674E-2</v>
+      </c>
+      <c r="L21" s="5">
         <v>0.9</v>
       </c>
-      <c r="M21" s="4">
-        <f>L21*K21</f>
-        <v>1.340294610748176E-2</v>
-      </c>
-      <c r="N21" s="4">
+      <c r="M21" s="3">
         <f t="shared" si="0"/>
-        <v>48.250605986934339</v>
+        <v>1.3016435963310606E-2</v>
+      </c>
+      <c r="N21" s="3">
+        <f t="shared" si="2"/>
+        <v>46.859169467918186</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -2160,26 +2157,26 @@
       <c r="G22" s="3">
         <v>204</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="5">
         <v>204</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="5">
         <v>2</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K22" s="4">
-        <f t="shared" si="1"/>
-        <v>3.2047386659269483E-2</v>
-      </c>
-      <c r="L22" s="6"/>
-      <c r="M22" s="4">
-        <f>L22*K22</f>
-        <v>0</v>
-      </c>
-      <c r="N22" s="4">
+      <c r="K22" s="3">
+        <f t="shared" si="1"/>
+        <v>3.1415926535897934E-2</v>
+      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2205,29 +2202,29 @@
       <c r="G23" s="3">
         <v>204</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="5">
         <v>204</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="5">
         <v>2</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K23" s="4">
-        <f t="shared" si="1"/>
-        <v>3.2047386659269483E-2</v>
-      </c>
-      <c r="L23" s="6">
+      <c r="K23" s="3">
+        <f t="shared" si="1"/>
+        <v>3.1415926535897934E-2</v>
+      </c>
+      <c r="L23" s="5">
         <v>2</v>
       </c>
-      <c r="M23" s="4">
-        <f>L23*K23</f>
-        <v>6.4094773318538967E-2</v>
-      </c>
-      <c r="N23" s="4">
+      <c r="M23" s="3">
         <f t="shared" si="0"/>
-        <v>230.74118394674028</v>
+        <v>6.2831853071795868E-2</v>
+      </c>
+      <c r="N23" s="3">
+        <f t="shared" si="2"/>
+        <v>226.19467105846513</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -2252,26 +2249,26 @@
       <c r="G24" s="3">
         <v>80</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="5">
         <v>88.9</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="5">
         <v>2</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K24" s="4">
-        <f t="shared" si="1"/>
-        <v>5.9310206246938049E-3</v>
-      </c>
-      <c r="L24" s="6"/>
-      <c r="M24" s="4">
-        <f>L24*K24</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="4">
+      <c r="K24" s="3">
+        <f t="shared" si="1"/>
+        <v>5.661157815750442E-3</v>
+      </c>
+      <c r="L24" s="5"/>
+      <c r="M24" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2297,29 +2294,29 @@
       <c r="G25" s="3">
         <v>125</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="5">
         <v>139.69999999999999</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="5">
         <v>2</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K25" s="4">
-        <f t="shared" si="1"/>
-        <v>1.4892162341646401E-2</v>
-      </c>
-      <c r="L25" s="6">
+      <c r="K25" s="3">
+        <f t="shared" si="1"/>
+        <v>1.4462706625900674E-2</v>
+      </c>
+      <c r="L25" s="5">
         <v>1.8</v>
       </c>
-      <c r="M25" s="4">
-        <f>L25*K25</f>
-        <v>2.6805892214963521E-2</v>
-      </c>
-      <c r="N25" s="4">
+      <c r="M25" s="3">
         <f t="shared" si="0"/>
-        <v>96.501211973868678</v>
+        <v>2.6032871926621213E-2</v>
+      </c>
+      <c r="N25" s="3">
+        <f t="shared" si="2"/>
+        <v>93.718338935836371</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -2344,29 +2341,29 @@
       <c r="G26" s="3">
         <v>155</v>
       </c>
-      <c r="H26" s="6">
+      <c r="H26" s="5">
         <v>154</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="5">
         <v>2</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K26" s="4">
-        <f t="shared" si="1"/>
-        <v>1.8145839167134643E-2</v>
-      </c>
-      <c r="L26" s="6">
+      <c r="K26" s="3">
+        <f t="shared" si="1"/>
+        <v>1.7671458676442587E-2</v>
+      </c>
+      <c r="L26" s="5">
         <v>2.5</v>
       </c>
-      <c r="M26" s="4">
-        <f>L26*K26</f>
-        <v>4.5364597917836605E-2</v>
-      </c>
-      <c r="N26" s="4">
+      <c r="M26" s="3">
         <f t="shared" si="0"/>
-        <v>163.31255250421177</v>
+        <v>4.4178646691106466E-2</v>
+      </c>
+      <c r="N26" s="3">
+        <f t="shared" si="2"/>
+        <v>159.04312808798326</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -2391,29 +2388,29 @@
       <c r="G27" s="3">
         <v>204</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="5">
         <v>204</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I27" s="5">
         <v>2</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K27" s="4">
-        <f t="shared" si="1"/>
-        <v>3.2047386659269483E-2</v>
-      </c>
-      <c r="L27" s="6">
+      <c r="K27" s="3">
+        <f t="shared" si="1"/>
+        <v>3.1415926535897934E-2</v>
+      </c>
+      <c r="L27" s="5">
         <v>1.8</v>
       </c>
-      <c r="M27" s="4">
-        <f>L27*K27</f>
-        <v>5.7685295986685071E-2</v>
-      </c>
-      <c r="N27" s="4">
+      <c r="M27" s="3">
         <f t="shared" si="0"/>
-        <v>207.66706555206625</v>
+        <v>5.6548667764616284E-2</v>
+      </c>
+      <c r="N27" s="3">
+        <f t="shared" si="2"/>
+        <v>203.57520395261861</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -2438,29 +2435,29 @@
       <c r="G28" s="3">
         <v>155</v>
       </c>
-      <c r="H28" s="6">
+      <c r="H28" s="5">
         <v>154</v>
       </c>
-      <c r="I28" s="6">
+      <c r="I28" s="5">
         <v>2</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K28" s="4">
-        <f t="shared" si="1"/>
-        <v>1.8145839167134643E-2</v>
-      </c>
-      <c r="L28" s="6">
+      <c r="K28" s="3">
+        <f t="shared" si="1"/>
+        <v>1.7671458676442587E-2</v>
+      </c>
+      <c r="L28" s="5">
         <v>2.8</v>
       </c>
-      <c r="M28" s="4">
-        <f>L28*K28</f>
-        <v>5.0808349667976996E-2</v>
-      </c>
-      <c r="N28" s="4">
+      <c r="M28" s="3">
         <f t="shared" si="0"/>
-        <v>182.91005880471718</v>
+        <v>4.9480084294039238E-2</v>
+      </c>
+      <c r="N28" s="3">
+        <f t="shared" si="2"/>
+        <v>178.12830345854127</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2485,26 +2482,26 @@
       <c r="G29" s="3">
         <v>204</v>
       </c>
-      <c r="H29" s="6">
+      <c r="H29" s="5">
         <v>204</v>
       </c>
-      <c r="I29" s="6">
+      <c r="I29" s="5">
         <v>2</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K29" s="4">
-        <f t="shared" si="1"/>
-        <v>3.2047386659269483E-2</v>
-      </c>
-      <c r="L29" s="6"/>
-      <c r="M29" s="4">
-        <f>L29*K29</f>
-        <v>0</v>
-      </c>
-      <c r="N29" s="4">
+      <c r="K29" s="3">
+        <f t="shared" si="1"/>
+        <v>3.1415926535897934E-2</v>
+      </c>
+      <c r="L29" s="5"/>
+      <c r="M29" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2526,26 +2523,26 @@
       <c r="G30" s="3">
         <v>129</v>
       </c>
-      <c r="H30" s="6">
+      <c r="H30" s="5">
         <v>129</v>
       </c>
-      <c r="I30" s="6">
+      <c r="I30" s="5">
         <v>2</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K30" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2667686977437444E-2</v>
-      </c>
-      <c r="L30" s="6"/>
-      <c r="M30" s="4">
-        <f>L30*K30</f>
-        <v>0</v>
-      </c>
-      <c r="N30" s="4">
+      <c r="K30" s="3">
+        <f t="shared" si="1"/>
+        <v>1.2271846303085129E-2</v>
+      </c>
+      <c r="L30" s="5"/>
+      <c r="M30" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2571,26 +2568,26 @@
       <c r="G31" s="3">
         <v>129</v>
       </c>
-      <c r="H31" s="6">
+      <c r="H31" s="5">
         <v>129</v>
       </c>
-      <c r="I31" s="6">
+      <c r="I31" s="5">
         <v>2</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K31" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2667686977437444E-2</v>
-      </c>
-      <c r="L31" s="6"/>
-      <c r="M31" s="4">
-        <f>L31*K31</f>
-        <v>0</v>
-      </c>
-      <c r="N31" s="4">
+      <c r="K31" s="3">
+        <f t="shared" si="1"/>
+        <v>1.2271846303085129E-2</v>
+      </c>
+      <c r="L31" s="5"/>
+      <c r="M31" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2616,26 +2613,26 @@
       <c r="G32" s="3">
         <v>204</v>
       </c>
-      <c r="H32" s="6">
+      <c r="H32" s="5">
         <v>204</v>
       </c>
-      <c r="I32" s="6">
+      <c r="I32" s="5">
         <v>2</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K32" s="4">
-        <f t="shared" si="1"/>
-        <v>3.2047386659269483E-2</v>
-      </c>
-      <c r="L32" s="6"/>
-      <c r="M32" s="4">
-        <f>L32*K32</f>
-        <v>0</v>
-      </c>
-      <c r="N32" s="4">
+      <c r="K32" s="3">
+        <f t="shared" si="1"/>
+        <v>3.1415926535897934E-2</v>
+      </c>
+      <c r="L32" s="5"/>
+      <c r="M32" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2661,26 +2658,26 @@
       <c r="G33" s="3">
         <v>100</v>
       </c>
-      <c r="H33" s="6">
+      <c r="H33" s="5">
         <v>114</v>
       </c>
-      <c r="I33" s="6">
+      <c r="I33" s="5">
         <v>2</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K33" s="4">
-        <f t="shared" si="1"/>
-        <v>9.8520345616575928E-3</v>
-      </c>
-      <c r="L33" s="6"/>
-      <c r="M33" s="4">
-        <f>L33*K33</f>
-        <v>0</v>
-      </c>
-      <c r="N33" s="4">
+      <c r="K33" s="3">
+        <f t="shared" si="1"/>
+        <v>9.5033177771091243E-3</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2706,26 +2703,26 @@
       <c r="G34" s="3">
         <v>65</v>
       </c>
-      <c r="H34" s="6">
+      <c r="H34" s="5">
         <v>76.099999999999994</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="5">
         <v>3.6</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K34" s="4">
-        <f t="shared" ref="K34:K65" si="2">PI()*(((H34-I34)*10^-3)^2/4)</f>
-        <v>4.1282490963578371E-3</v>
-      </c>
-      <c r="L34" s="6"/>
-      <c r="M34" s="4">
-        <f>L34*K34</f>
-        <v>0</v>
-      </c>
-      <c r="N34" s="4">
-        <f t="shared" si="0"/>
+      <c r="K34" s="3">
+        <f t="shared" si="1"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="3">
+        <f t="shared" ref="M34:M65" si="3">L34*K34</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2751,26 +2748,26 @@
       <c r="G35" s="3">
         <v>125</v>
       </c>
-      <c r="H35" s="6">
+      <c r="H35" s="5">
         <v>139</v>
       </c>
-      <c r="I35" s="6">
+      <c r="I35" s="5">
         <v>5</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K35" s="4">
-        <f t="shared" si="2"/>
-        <v>1.4102609421964583E-2</v>
-      </c>
-      <c r="L35" s="6"/>
-      <c r="M35" s="4">
-        <f>L35*K35</f>
-        <v>0</v>
-      </c>
-      <c r="N35" s="4">
-        <f t="shared" si="0"/>
+      <c r="K35" s="3">
+        <f t="shared" si="1"/>
+        <v>1.3069810837096936E-2</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2796,26 +2793,26 @@
       <c r="G36" s="3">
         <v>43</v>
       </c>
-      <c r="H36" s="6">
+      <c r="H36" s="5">
         <v>43</v>
       </c>
-      <c r="I36" s="6">
+      <c r="I36" s="5">
         <v>2</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K36" s="4">
-        <f t="shared" si="2"/>
-        <v>1.3202543126711107E-3</v>
-      </c>
-      <c r="L36" s="6"/>
-      <c r="M36" s="4">
-        <f>L36*K36</f>
-        <v>0</v>
-      </c>
-      <c r="N36" s="4">
-        <f t="shared" si="0"/>
+      <c r="K36" s="3">
+        <f t="shared" si="1"/>
+        <v>1.1945906065275189E-3</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N36" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2841,26 +2838,26 @@
       <c r="G37" s="3">
         <v>50</v>
       </c>
-      <c r="H37" s="6">
+      <c r="H37" s="5">
         <v>60.3</v>
       </c>
-      <c r="I37" s="6">
+      <c r="I37" s="5">
         <v>3.6</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K37" s="4">
-        <f t="shared" si="2"/>
-        <v>2.524968701524822E-3</v>
-      </c>
-      <c r="L37" s="6"/>
-      <c r="M37" s="4">
-        <f>L37*K37</f>
-        <v>0</v>
-      </c>
-      <c r="N37" s="4">
-        <f t="shared" si="0"/>
+      <c r="K37" s="3">
+        <f t="shared" si="1"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N37" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2886,26 +2883,26 @@
       <c r="G38" s="3">
         <v>50</v>
       </c>
-      <c r="H38" s="6">
+      <c r="H38" s="5">
         <v>60.3</v>
       </c>
-      <c r="I38" s="6">
+      <c r="I38" s="5">
         <v>3.6</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K38" s="4">
-        <f t="shared" si="2"/>
-        <v>2.524968701524822E-3</v>
-      </c>
-      <c r="L38" s="6"/>
-      <c r="M38" s="4">
-        <f>L38*K38</f>
-        <v>0</v>
-      </c>
-      <c r="N38" s="4">
-        <f t="shared" si="0"/>
+      <c r="K38" s="3">
+        <f t="shared" si="1"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N38" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2931,26 +2928,26 @@
       <c r="G39" s="3">
         <v>100</v>
       </c>
-      <c r="H39" s="6">
+      <c r="H39" s="5">
         <v>114</v>
       </c>
-      <c r="I39" s="6">
+      <c r="I39" s="5">
         <v>4.5</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K39" s="4">
-        <f t="shared" si="2"/>
-        <v>9.4171203286762539E-3</v>
-      </c>
-      <c r="L39" s="6"/>
-      <c r="M39" s="4">
-        <f>L39*K39</f>
-        <v>0</v>
-      </c>
-      <c r="N39" s="4">
-        <f t="shared" si="0"/>
+      <c r="K39" s="3">
+        <f t="shared" si="1"/>
+        <v>8.6590147514568668E-3</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N39" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2976,26 +2973,26 @@
       <c r="G40" s="3">
         <v>80</v>
       </c>
-      <c r="H40" s="6">
+      <c r="H40" s="5">
         <v>88.9</v>
       </c>
-      <c r="I40" s="6">
+      <c r="I40" s="5">
         <v>4</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K40" s="4">
-        <f t="shared" si="2"/>
-        <v>5.661157815750442E-3</v>
-      </c>
-      <c r="L40" s="6"/>
-      <c r="M40" s="4">
-        <f>L40*K40</f>
-        <v>0</v>
-      </c>
-      <c r="N40" s="4">
-        <f t="shared" si="0"/>
+      <c r="K40" s="3">
+        <f t="shared" si="1"/>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="L40" s="5"/>
+      <c r="M40" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N40" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3021,26 +3018,26 @@
       <c r="G41" s="3">
         <v>50</v>
       </c>
-      <c r="H41" s="6">
+      <c r="H41" s="5">
         <v>60.3</v>
       </c>
-      <c r="I41" s="6">
+      <c r="I41" s="5">
         <v>3.6</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K41" s="4">
-        <f t="shared" si="2"/>
-        <v>2.524968701524822E-3</v>
-      </c>
-      <c r="L41" s="6"/>
-      <c r="M41" s="4">
-        <f>L41*K41</f>
-        <v>0</v>
-      </c>
-      <c r="N41" s="4">
-        <f t="shared" si="0"/>
+      <c r="K41" s="3">
+        <f t="shared" si="1"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L41" s="5"/>
+      <c r="M41" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3066,26 +3063,26 @@
       <c r="G42" s="3">
         <v>50</v>
       </c>
-      <c r="H42" s="6">
+      <c r="H42" s="5">
         <v>60.3</v>
       </c>
-      <c r="I42" s="6">
+      <c r="I42" s="5">
         <v>3.6</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K42" s="4">
-        <f t="shared" si="2"/>
-        <v>2.524968701524822E-3</v>
-      </c>
-      <c r="L42" s="6"/>
-      <c r="M42" s="4">
-        <f>L42*K42</f>
-        <v>0</v>
-      </c>
-      <c r="N42" s="4">
-        <f t="shared" si="0"/>
+      <c r="K42" s="3">
+        <f t="shared" si="1"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L42" s="5"/>
+      <c r="M42" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3111,26 +3108,26 @@
       <c r="G43" s="3">
         <v>40</v>
       </c>
-      <c r="H43" s="6">
+      <c r="H43" s="5">
         <v>48.3</v>
       </c>
-      <c r="I43" s="6">
+      <c r="I43" s="5">
         <v>3.2</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K43" s="4">
-        <f t="shared" si="2"/>
-        <v>1.5975077183320431E-3</v>
-      </c>
-      <c r="L43" s="6"/>
-      <c r="M43" s="4">
-        <f>L43*K43</f>
-        <v>0</v>
-      </c>
-      <c r="N43" s="4">
-        <f t="shared" si="0"/>
+      <c r="K43" s="3">
+        <f t="shared" si="1"/>
+        <v>1.378852869642194E-3</v>
+      </c>
+      <c r="L43" s="5"/>
+      <c r="M43" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3156,26 +3153,26 @@
       <c r="G44" s="3">
         <v>40</v>
       </c>
-      <c r="H44" s="6">
+      <c r="H44" s="5">
         <v>48.3</v>
       </c>
-      <c r="I44" s="6">
+      <c r="I44" s="5">
         <v>3.2</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K44" s="4">
-        <f t="shared" si="2"/>
-        <v>1.5975077183320431E-3</v>
-      </c>
-      <c r="L44" s="6"/>
-      <c r="M44" s="4">
-        <f>L44*K44</f>
-        <v>0</v>
-      </c>
-      <c r="N44" s="4">
-        <f t="shared" si="0"/>
+      <c r="K44" s="3">
+        <f t="shared" si="1"/>
+        <v>1.378852869642194E-3</v>
+      </c>
+      <c r="L44" s="5"/>
+      <c r="M44" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3201,26 +3198,26 @@
       <c r="G45" s="3">
         <v>50</v>
       </c>
-      <c r="H45" s="6">
+      <c r="H45" s="5">
         <v>60.3</v>
       </c>
-      <c r="I45" s="6">
+      <c r="I45" s="5">
         <v>3.6</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K45" s="4">
-        <f t="shared" si="2"/>
-        <v>2.524968701524822E-3</v>
-      </c>
-      <c r="L45" s="6"/>
-      <c r="M45" s="4">
-        <f>L45*K45</f>
-        <v>0</v>
-      </c>
-      <c r="N45" s="4">
-        <f t="shared" si="0"/>
+      <c r="K45" s="3">
+        <f t="shared" si="1"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L45" s="5"/>
+      <c r="M45" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3246,26 +3243,26 @@
       <c r="G46" s="3">
         <v>50</v>
       </c>
-      <c r="H46" s="6">
+      <c r="H46" s="5">
         <v>60.3</v>
       </c>
-      <c r="I46" s="6">
+      <c r="I46" s="5">
         <v>3.6</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K46" s="4">
-        <f t="shared" si="2"/>
-        <v>2.524968701524822E-3</v>
-      </c>
-      <c r="L46" s="6"/>
-      <c r="M46" s="4">
-        <f>L46*K46</f>
-        <v>0</v>
-      </c>
-      <c r="N46" s="4">
-        <f t="shared" si="0"/>
+      <c r="K46" s="3">
+        <f t="shared" si="1"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L46" s="5"/>
+      <c r="M46" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N46" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3291,26 +3288,26 @@
       <c r="G47" s="3">
         <v>50</v>
       </c>
-      <c r="H47" s="6">
+      <c r="H47" s="5">
         <v>60.3</v>
       </c>
-      <c r="I47" s="6">
+      <c r="I47" s="5">
         <v>3.6</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K47" s="4">
-        <f t="shared" si="2"/>
-        <v>2.524968701524822E-3</v>
-      </c>
-      <c r="L47" s="6"/>
-      <c r="M47" s="4">
-        <f>L47*K47</f>
-        <v>0</v>
-      </c>
-      <c r="N47" s="4">
-        <f t="shared" si="0"/>
+      <c r="K47" s="3">
+        <f t="shared" si="1"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L47" s="5"/>
+      <c r="M47" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3336,24 +3333,24 @@
       <c r="G48" s="3">
         <v>200</v>
       </c>
-      <c r="H48" s="6">
+      <c r="H48" s="5">
         <v>220</v>
       </c>
-      <c r="I48" s="6"/>
+      <c r="I48" s="5"/>
       <c r="J48" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K48" s="4">
-        <f t="shared" si="2"/>
+      <c r="K48" s="3">
+        <f t="shared" si="1"/>
         <v>3.8013271108436497E-2</v>
       </c>
-      <c r="L48" s="6"/>
-      <c r="M48" s="4">
-        <f>L48*K48</f>
-        <v>0</v>
-      </c>
-      <c r="N48" s="4">
-        <f t="shared" si="0"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N48" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3379,26 +3376,26 @@
       <c r="G49" s="3">
         <v>50</v>
       </c>
-      <c r="H49" s="6">
+      <c r="H49" s="5">
         <v>60.3</v>
       </c>
-      <c r="I49" s="6">
+      <c r="I49" s="5">
         <v>3.6</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K49" s="4">
-        <f t="shared" si="2"/>
-        <v>2.524968701524822E-3</v>
-      </c>
-      <c r="L49" s="6"/>
-      <c r="M49" s="4">
-        <f>L49*K49</f>
-        <v>0</v>
-      </c>
-      <c r="N49" s="4">
-        <f t="shared" si="0"/>
+      <c r="K49" s="3">
+        <f t="shared" si="1"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L49" s="5"/>
+      <c r="M49" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3424,29 +3421,29 @@
       <c r="G50" s="3">
         <v>125</v>
       </c>
-      <c r="H50" s="6">
+      <c r="H50" s="5">
         <v>141</v>
       </c>
-      <c r="I50" s="6">
+      <c r="I50" s="5">
         <v>5</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K50" s="4">
-        <f t="shared" si="2"/>
-        <v>1.4526724430199206E-2</v>
-      </c>
-      <c r="L50" s="6">
+      <c r="K50" s="3">
+        <f t="shared" si="1"/>
+        <v>1.3478217882063612E-2</v>
+      </c>
+      <c r="L50" s="5">
         <v>1.9</v>
       </c>
-      <c r="M50" s="4">
-        <f>L50*K50</f>
-        <v>2.760077641737849E-2</v>
-      </c>
-      <c r="N50" s="4">
-        <f t="shared" si="0"/>
-        <v>99.362795102562558</v>
+      <c r="M50" s="3">
+        <f t="shared" si="3"/>
+        <v>2.560861397592086E-2</v>
+      </c>
+      <c r="N50" s="3">
+        <f t="shared" si="2"/>
+        <v>92.191010313315104</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
@@ -3471,29 +3468,29 @@
       <c r="G51" s="3">
         <v>80</v>
       </c>
-      <c r="H51" s="6">
+      <c r="H51" s="5">
         <v>88.9</v>
       </c>
-      <c r="I51" s="6">
+      <c r="I51" s="5">
         <v>4</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K51" s="4">
-        <f t="shared" si="2"/>
-        <v>5.661157815750442E-3</v>
-      </c>
-      <c r="L51" s="6">
+      <c r="K51" s="3">
+        <f t="shared" si="1"/>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="L51" s="5">
         <v>3</v>
       </c>
-      <c r="M51" s="4">
-        <f>L51*K51</f>
-        <v>1.6983473447251325E-2</v>
-      </c>
-      <c r="N51" s="4">
-        <f t="shared" si="0"/>
-        <v>61.140504410104768</v>
+      <c r="M51" s="3">
+        <f t="shared" si="3"/>
+        <v>1.5420845261355766E-2</v>
+      </c>
+      <c r="N51" s="3">
+        <f t="shared" si="2"/>
+        <v>55.515042940880754</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
@@ -3518,29 +3515,29 @@
       <c r="G52" s="3">
         <v>80</v>
       </c>
-      <c r="H52" s="6">
+      <c r="H52" s="5">
         <v>88.9</v>
       </c>
-      <c r="I52" s="6">
+      <c r="I52" s="5">
         <v>4</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K52" s="4">
-        <f t="shared" si="2"/>
-        <v>5.661157815750442E-3</v>
-      </c>
-      <c r="L52" s="6">
+      <c r="K52" s="3">
+        <f t="shared" si="1"/>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="L52" s="5">
         <v>0.46</v>
       </c>
-      <c r="M52" s="4">
-        <f>L52*K52</f>
-        <v>2.6041325952452033E-3</v>
-      </c>
-      <c r="N52" s="4">
-        <f t="shared" si="0"/>
-        <v>9.3748773428827317</v>
+      <c r="M52" s="3">
+        <f t="shared" si="3"/>
+        <v>2.3645296067412178E-3</v>
+      </c>
+      <c r="N52" s="3">
+        <f t="shared" si="2"/>
+        <v>8.5123065842683836</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
@@ -3565,29 +3562,29 @@
       <c r="G53" s="3">
         <v>50</v>
       </c>
-      <c r="H53" s="6">
+      <c r="H53" s="5">
         <v>60.3</v>
       </c>
-      <c r="I53" s="6">
+      <c r="I53" s="5">
         <v>3.6</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K53" s="4">
-        <f t="shared" si="2"/>
-        <v>2.524968701524822E-3</v>
-      </c>
-      <c r="L53" s="6">
+      <c r="K53" s="3">
+        <f t="shared" si="1"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L53" s="5">
         <v>3</v>
       </c>
-      <c r="M53" s="4">
-        <f>L53*K53</f>
-        <v>7.5749061045744664E-3</v>
-      </c>
-      <c r="N53" s="4">
-        <f t="shared" si="0"/>
-        <v>27.269661976468079</v>
+      <c r="M53" s="3">
+        <f t="shared" si="3"/>
+        <v>6.6435495464912363E-3</v>
+      </c>
+      <c r="N53" s="3">
+        <f t="shared" si="2"/>
+        <v>23.916778367368451</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
@@ -3612,26 +3609,26 @@
       <c r="G54" s="3">
         <v>200</v>
       </c>
-      <c r="H54" s="6">
+      <c r="H54" s="5">
         <v>220</v>
       </c>
-      <c r="I54" s="6"/>
+      <c r="I54" s="5"/>
       <c r="J54" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K54" s="4">
-        <f t="shared" si="2"/>
+      <c r="K54" s="3">
+        <f t="shared" si="1"/>
         <v>3.8013271108436497E-2</v>
       </c>
-      <c r="L54" s="6">
+      <c r="L54" s="5">
         <v>0.9</v>
       </c>
-      <c r="M54" s="4">
-        <f>L54*K54</f>
+      <c r="M54" s="3">
+        <f t="shared" si="3"/>
         <v>3.421194399759285E-2</v>
       </c>
-      <c r="N54" s="4">
-        <f t="shared" si="0"/>
+      <c r="N54" s="3">
+        <f t="shared" si="2"/>
         <v>123.16299839133426</v>
       </c>
     </row>
@@ -3651,26 +3648,26 @@
       <c r="G55" s="3">
         <v>80</v>
       </c>
-      <c r="H55" s="6">
+      <c r="H55" s="5">
         <v>88.9</v>
       </c>
-      <c r="I55" s="6">
+      <c r="I55" s="5">
         <v>4</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K55" s="4">
-        <f t="shared" si="2"/>
-        <v>5.661157815750442E-3</v>
-      </c>
-      <c r="L55" s="6"/>
-      <c r="M55" s="4">
-        <f>L55*K55</f>
-        <v>0</v>
-      </c>
-      <c r="N55" s="4">
-        <f t="shared" si="0"/>
+      <c r="K55" s="3">
+        <f t="shared" si="1"/>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="L55" s="5"/>
+      <c r="M55" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N55" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3696,26 +3693,26 @@
       <c r="G56" s="3">
         <v>100</v>
       </c>
-      <c r="H56" s="6">
+      <c r="H56" s="5">
         <v>114</v>
       </c>
-      <c r="I56" s="6">
+      <c r="I56" s="5">
         <v>4.5</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K56" s="4">
-        <f t="shared" si="2"/>
-        <v>9.4171203286762539E-3</v>
-      </c>
-      <c r="L56" s="6"/>
-      <c r="M56" s="4">
-        <f>L56*K56</f>
-        <v>0</v>
-      </c>
-      <c r="N56" s="4">
-        <f t="shared" si="0"/>
+      <c r="K56" s="3">
+        <f t="shared" si="1"/>
+        <v>8.6590147514568668E-3</v>
+      </c>
+      <c r="L56" s="5"/>
+      <c r="M56" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N56" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3741,27 +3738,29 @@
       <c r="G57" s="3">
         <v>65</v>
       </c>
-      <c r="H57" s="6">
+      <c r="H57" s="5">
         <v>76.099999999999994</v>
       </c>
-      <c r="I57" s="6">
+      <c r="I57" s="5">
         <v>3.6</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K57" s="4">
-        <f t="shared" si="2"/>
-        <v>4.1282490963578371E-3</v>
-      </c>
-      <c r="L57" s="6"/>
-      <c r="M57" s="4">
-        <f>L57*K57</f>
-        <v>0</v>
-      </c>
-      <c r="N57" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="K57" s="3">
+        <f>PI()*(((H57-2*I57)*10^-3)^2/4)</f>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L57" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M57" s="3">
+        <f t="shared" si="3"/>
+        <v>4.1012950167881989E-3</v>
+      </c>
+      <c r="N57" s="3">
+        <f t="shared" si="2"/>
+        <v>14.764662060437516</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
@@ -3786,27 +3785,29 @@
       <c r="G58" s="3">
         <v>65</v>
       </c>
-      <c r="H58" s="6">
+      <c r="H58" s="5">
         <v>76.099999999999994</v>
       </c>
-      <c r="I58" s="6">
+      <c r="I58" s="5">
         <v>3.6</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K58" s="4">
-        <f t="shared" si="2"/>
-        <v>4.1282490963578371E-3</v>
-      </c>
-      <c r="L58" s="6"/>
-      <c r="M58" s="4">
-        <f>L58*K58</f>
-        <v>0</v>
-      </c>
-      <c r="N58" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="K58" s="3">
+        <f t="shared" si="1"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L58" s="5">
+        <v>1</v>
+      </c>
+      <c r="M58" s="3">
+        <f t="shared" si="3"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="N58" s="3">
+        <f t="shared" si="2"/>
+        <v>13.422420054943197</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
@@ -3831,26 +3832,26 @@
       <c r="G59" s="3">
         <v>65</v>
       </c>
-      <c r="H59" s="6">
+      <c r="H59" s="5">
         <v>76.099999999999994</v>
       </c>
-      <c r="I59" s="6">
+      <c r="I59" s="5">
         <v>3.6</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K59" s="4">
-        <f t="shared" si="2"/>
-        <v>4.1282490963578371E-3</v>
-      </c>
-      <c r="L59" s="6"/>
-      <c r="M59" s="4">
-        <f>L59*K59</f>
-        <v>0</v>
-      </c>
-      <c r="N59" s="4">
-        <f t="shared" si="0"/>
+      <c r="K59" s="3">
+        <f t="shared" si="1"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L59" s="5"/>
+      <c r="M59" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N59" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3876,26 +3877,26 @@
       <c r="G60" s="3">
         <v>50</v>
       </c>
-      <c r="H60" s="6">
+      <c r="H60" s="5">
         <v>60.3</v>
       </c>
-      <c r="I60" s="6">
+      <c r="I60" s="5">
         <v>3.6</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K60" s="4">
-        <f t="shared" si="2"/>
-        <v>2.524968701524822E-3</v>
-      </c>
-      <c r="L60" s="6"/>
-      <c r="M60" s="4">
-        <f>L60*K60</f>
-        <v>0</v>
-      </c>
-      <c r="N60" s="4">
-        <f t="shared" si="0"/>
+      <c r="K60" s="3">
+        <f t="shared" si="1"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L60" s="5"/>
+      <c r="M60" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3921,26 +3922,26 @@
       <c r="G61" s="3">
         <v>50</v>
       </c>
-      <c r="H61" s="6">
+      <c r="H61" s="5">
         <v>60.3</v>
       </c>
-      <c r="I61" s="6">
+      <c r="I61" s="5">
         <v>3.6</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K61" s="4">
-        <f t="shared" si="2"/>
-        <v>2.524968701524822E-3</v>
-      </c>
-      <c r="L61" s="6"/>
-      <c r="M61" s="4">
-        <f>L61*K61</f>
-        <v>0</v>
-      </c>
-      <c r="N61" s="4">
-        <f t="shared" si="0"/>
+      <c r="K61" s="3">
+        <f t="shared" si="1"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L61" s="5"/>
+      <c r="M61" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3966,26 +3967,26 @@
       <c r="G62" s="3">
         <v>32</v>
       </c>
-      <c r="H62" s="6">
+      <c r="H62" s="5">
         <v>42.2</v>
       </c>
-      <c r="I62" s="6">
+      <c r="I62" s="5">
         <v>3.2</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K62" s="4">
-        <f t="shared" si="2"/>
-        <v>1.1945906065275189E-3</v>
-      </c>
-      <c r="L62" s="6"/>
-      <c r="M62" s="4">
-        <f>L62*K62</f>
-        <v>0</v>
-      </c>
-      <c r="N62" s="4">
-        <f t="shared" si="0"/>
+      <c r="K62" s="3">
+        <f t="shared" si="1"/>
+        <v>1.0065977021367059E-3</v>
+      </c>
+      <c r="L62" s="5"/>
+      <c r="M62" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -4007,26 +4008,26 @@
       <c r="G63" s="3">
         <v>100</v>
       </c>
-      <c r="H63" s="6">
+      <c r="H63" s="5">
         <v>114</v>
       </c>
-      <c r="I63" s="6">
+      <c r="I63" s="5">
         <v>5</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K63" s="4">
-        <f t="shared" si="2"/>
-        <v>9.3313155793250824E-3</v>
-      </c>
-      <c r="L63" s="6"/>
-      <c r="M63" s="4">
-        <f>L63*K63</f>
-        <v>0</v>
-      </c>
-      <c r="N63" s="4">
-        <f t="shared" si="0"/>
+      <c r="K63" s="3">
+        <f t="shared" si="1"/>
+        <v>8.4948665353068026E-3</v>
+      </c>
+      <c r="L63" s="5"/>
+      <c r="M63" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -4052,26 +4053,26 @@
       <c r="G64" s="3">
         <v>150</v>
       </c>
-      <c r="H64" s="6">
+      <c r="H64" s="5">
         <v>168.3</v>
       </c>
-      <c r="I64" s="6">
+      <c r="I64" s="5">
         <v>5</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K64" s="4">
-        <f t="shared" si="2"/>
-        <v>2.0944126429521787E-2</v>
-      </c>
-      <c r="L64" s="6"/>
-      <c r="M64" s="4">
-        <f>L64*K64</f>
-        <v>0</v>
-      </c>
-      <c r="N64" s="4">
-        <f t="shared" si="0"/>
+      <c r="K64" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9681206182778688E-2</v>
+      </c>
+      <c r="L64" s="5"/>
+      <c r="M64" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -4093,26 +4094,26 @@
       <c r="G65" s="3">
         <v>100</v>
       </c>
-      <c r="H65" s="6">
+      <c r="H65" s="5">
         <v>114</v>
       </c>
-      <c r="I65" s="6">
+      <c r="I65" s="5">
         <v>4.5</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K65" s="4">
-        <f t="shared" si="2"/>
-        <v>9.4171203286762539E-3</v>
-      </c>
-      <c r="L65" s="6"/>
-      <c r="M65" s="4">
-        <f>L65*K65</f>
-        <v>0</v>
-      </c>
-      <c r="N65" s="4">
-        <f t="shared" si="0"/>
+      <c r="K65" s="3">
+        <f t="shared" si="1"/>
+        <v>8.6590147514568668E-3</v>
+      </c>
+      <c r="L65" s="5"/>
+      <c r="M65" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -4138,26 +4139,26 @@
       <c r="G66" s="3">
         <v>65</v>
       </c>
-      <c r="H66" s="6">
+      <c r="H66" s="5">
         <v>73</v>
       </c>
-      <c r="I66" s="6">
+      <c r="I66" s="5">
         <v>3.6</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K66" s="4">
-        <f t="shared" ref="K66:K71" si="3">PI()*(((H66-I66)*10^-3)^2/4)</f>
-        <v>3.7827602982609342E-3</v>
-      </c>
-      <c r="L66" s="6"/>
-      <c r="M66" s="4">
-        <f>L66*K66</f>
-        <v>0</v>
-      </c>
-      <c r="N66" s="4">
-        <f t="shared" si="0"/>
+      <c r="K66" s="3">
+        <f t="shared" si="1"/>
+        <v>3.4004913041721279E-3</v>
+      </c>
+      <c r="L66" s="5"/>
+      <c r="M66" s="3">
+        <f t="shared" ref="M66:M97" si="4">L66*K66</f>
+        <v>0</v>
+      </c>
+      <c r="N66" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -4183,26 +4184,26 @@
       <c r="G67" s="3">
         <v>65</v>
       </c>
-      <c r="H67" s="6">
+      <c r="H67" s="5">
         <v>76.099999999999994</v>
       </c>
-      <c r="I67" s="6">
+      <c r="I67" s="5">
         <v>3.6</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K67" s="4">
-        <f t="shared" si="3"/>
-        <v>4.1282490963578371E-3</v>
-      </c>
-      <c r="L67" s="6"/>
-      <c r="M67" s="4">
-        <f>L67*K67</f>
-        <v>0</v>
-      </c>
-      <c r="N67" s="4">
-        <f t="shared" ref="N67:N71" si="4">M67*3600</f>
+      <c r="K67" s="3">
+        <f t="shared" ref="K67:K71" si="5">PI()*(((H67-2*I67)*10^-3)^2/4)</f>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L67" s="5"/>
+      <c r="M67" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N67" s="3">
+        <f t="shared" ref="N67:N71" si="6">M67*3600</f>
         <v>0</v>
       </c>
     </row>
@@ -4224,26 +4225,26 @@
       <c r="G68" s="3">
         <v>50</v>
       </c>
-      <c r="H68" s="6">
+      <c r="H68" s="5">
         <v>60.3</v>
       </c>
-      <c r="I68" s="6">
+      <c r="I68" s="5">
         <v>3.6</v>
       </c>
       <c r="J68" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K68" s="4">
-        <f t="shared" si="3"/>
-        <v>2.524968701524822E-3</v>
-      </c>
-      <c r="L68" s="6"/>
-      <c r="M68" s="4">
-        <f>L68*K68</f>
-        <v>0</v>
-      </c>
-      <c r="N68" s="4">
+      <c r="K68" s="3">
+        <f t="shared" si="5"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L68" s="5"/>
+      <c r="M68" s="3">
         <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -4265,26 +4266,26 @@
       <c r="G69" s="3">
         <v>50</v>
       </c>
-      <c r="H69" s="6">
+      <c r="H69" s="5">
         <v>60.3</v>
       </c>
-      <c r="I69" s="6">
+      <c r="I69" s="5">
         <v>3.6</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K69" s="4">
-        <f t="shared" si="3"/>
-        <v>2.524968701524822E-3</v>
-      </c>
-      <c r="L69" s="6"/>
-      <c r="M69" s="4">
-        <f>L69*K69</f>
-        <v>0</v>
-      </c>
-      <c r="N69" s="4">
+      <c r="K69" s="3">
+        <f t="shared" si="5"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L69" s="5"/>
+      <c r="M69" s="3">
         <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -4304,26 +4305,26 @@
       <c r="G70" s="3">
         <v>100</v>
       </c>
-      <c r="H70" s="6">
+      <c r="H70" s="5">
         <v>114</v>
       </c>
-      <c r="I70" s="6">
+      <c r="I70" s="5">
         <v>4.5</v>
       </c>
       <c r="J70" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K70" s="4">
-        <f t="shared" si="3"/>
-        <v>9.4171203286762539E-3</v>
-      </c>
-      <c r="L70" s="6"/>
-      <c r="M70" s="4">
-        <f>L70*K70</f>
-        <v>0</v>
-      </c>
-      <c r="N70" s="4">
+      <c r="K70" s="3">
+        <f t="shared" si="5"/>
+        <v>8.6590147514568668E-3</v>
+      </c>
+      <c r="L70" s="5"/>
+      <c r="M70" s="3">
         <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -4343,31 +4344,30 @@
       <c r="G71" s="3">
         <v>80</v>
       </c>
-      <c r="H71" s="6">
+      <c r="H71" s="5">
         <v>88.9</v>
       </c>
-      <c r="I71" s="6">
+      <c r="I71" s="5">
         <v>4</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K71" s="4">
-        <f t="shared" si="3"/>
-        <v>5.661157815750442E-3</v>
-      </c>
-      <c r="L71" s="6"/>
-      <c r="M71" s="4">
-        <f>L71*K71</f>
-        <v>0</v>
-      </c>
-      <c r="N71" s="4">
+      <c r="K71" s="3">
+        <f t="shared" si="5"/>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="L71" s="5"/>
+      <c r="M71" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="N71" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="g3d3e1Fm2tFm+4Kpa7Itvx8njHFV8W6HiKgvAfEhMHuCEZtGXwq24UkJFmJ6avfqAxiWLNS1MlfLLDfCwfaVWA==" saltValue="r+1d25qDUUEIwfXgXx7U7A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <autoFilter ref="A1:N1" xr:uid="{80D9219E-119C-467C-9531-507D24E0A5C1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M72">
     <sortCondition ref="C40:C72"/>

--- a/data/punts/punts-mesura-at.xlsx
+++ b/data/punts/punts-mesura-at.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\punts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFDC6187-A128-43B5-BBC5-A1100F6C7CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49900FE-BD47-49D0-BA11-DD1DF48713C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4CA701B3-5EB8-45D8-B6BB-1F057196BE44}"/>
   </bookViews>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="3">
-        <f t="shared" ref="M66:M97" si="4">L66*K66</f>
+        <f t="shared" ref="M66:M71" si="4">L66*K66</f>
         <v>0</v>
       </c>
       <c r="N66" s="3">

--- a/data/punts/punts-mesura-at.xlsx
+++ b/data/punts/punts-mesura-at.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\punts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49900FE-BD47-49D0-BA11-DD1DF48713C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01ED9052-6439-44B1-A2F7-919180CC047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4CA701B3-5EB8-45D8-B6BB-1F057196BE44}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="229">
   <si>
     <t>id</t>
   </si>
@@ -308,9 +308,6 @@
     <t>Flow velocity ms</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>AT-01</t>
   </si>
   <si>
@@ -506,27 +503,6 @@
     <t>V-700/V-800-07</t>
   </si>
   <si>
-    <t>-01</t>
-  </si>
-  <si>
-    <t>-02</t>
-  </si>
-  <si>
-    <t>-10702</t>
-  </si>
-  <si>
-    <t>-10603</t>
-  </si>
-  <si>
-    <t>-10804</t>
-  </si>
-  <si>
-    <t>-10405</t>
-  </si>
-  <si>
-    <t>-10906</t>
-  </si>
-  <si>
     <t>-07</t>
   </si>
   <si>
@@ -713,12 +689,6 @@
     <t>V-81007</t>
   </si>
   <si>
-    <t>R-70101</t>
-  </si>
-  <si>
-    <t>R-70102</t>
-  </si>
-  <si>
     <t>BV-10501</t>
   </si>
   <si>
@@ -729,6 +699,33 @@
   </si>
   <si>
     <t>volume flow rate m3h</t>
+  </si>
+  <si>
+    <t>BV-10906</t>
+  </si>
+  <si>
+    <t>BV-10702</t>
+  </si>
+  <si>
+    <t>BV-10603</t>
+  </si>
+  <si>
+    <t>BV-10804</t>
+  </si>
+  <si>
+    <t>BV-10405</t>
+  </si>
+  <si>
+    <t>SS-700B</t>
+  </si>
+  <si>
+    <t>EI-70101</t>
+  </si>
+  <si>
+    <t>EI-70102</t>
+  </si>
+  <si>
+    <t>measured speed</t>
   </si>
 </sst>
 </file>
@@ -805,7 +802,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -825,6 +822,14 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -1165,25 +1170,26 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" style="1" customWidth="1"/>
     <col min="6" max="6" width="11.44140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="1"/>
     <col min="8" max="9" width="9.5546875" style="6" customWidth="1"/>
     <col min="10" max="10" width="11" style="1" customWidth="1"/>
     <col min="11" max="11" width="13.109375" style="1" customWidth="1"/>
     <col min="12" max="12" width="17.109375" style="6" customWidth="1"/>
-    <col min="13" max="13" width="21.44140625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="21.77734375" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="1"/>
+    <col min="13" max="13" width="17.109375" style="8" customWidth="1"/>
+    <col min="14" max="14" width="21.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="21.77734375" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -1215,130 +1221,139 @@
         <v>83</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="L1" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="N1" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>350</v>
+        <v>1121</v>
       </c>
       <c r="B2" s="3">
-        <v>131</v>
+        <v>785</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>90</v>
+        <v>225</v>
+      </c>
+      <c r="D2" s="3" t="str">
+        <f>C2&amp;"-01"</f>
+        <v>SS-700B-01</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>226</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="G2" s="3">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H2" s="5">
-        <v>168.3</v>
+        <v>114</v>
       </c>
       <c r="I2" s="5">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K2" s="3">
-        <f>PI()*(((H2-2*I2)*10^-3)^2/4)</f>
-        <v>1.9780794669897482E-2</v>
-      </c>
-      <c r="L2" s="5">
-        <v>3</v>
-      </c>
-      <c r="M2" s="3">
-        <f t="shared" ref="M2:M33" si="0">L2*K2</f>
-        <v>5.9342384009692446E-2</v>
+        <f t="shared" ref="K2:K33" si="0">PI()*(((H2-2*I2)*10^-3)^2/4)</f>
+        <v>8.6590147514568668E-3</v>
+      </c>
+      <c r="L2" s="5"/>
+      <c r="M2" s="7">
+        <f>IF(L2&gt;0, L2, 1)</f>
+        <v>1</v>
       </c>
       <c r="N2" s="3">
-        <f>M2*3600</f>
-        <v>213.63258243489281</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <f>M2*K2</f>
+        <v>8.6590147514568668E-3</v>
+      </c>
+      <c r="O2" s="3">
+        <f t="shared" ref="O2:O33" si="1">N2*3600</f>
+        <v>31.17245310524472</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <v>370</v>
+        <v>1131</v>
       </c>
       <c r="B3" s="3">
-        <v>134</v>
+        <v>785</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>91</v>
+        <v>225</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <f>C3&amp;"-02"</f>
+        <v>SS-700B-02</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>157</v>
+        <v>227</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="3">
+        <v>80</v>
+      </c>
+      <c r="H3" s="5">
+        <v>88.9</v>
+      </c>
+      <c r="I3" s="5">
         <v>4</v>
       </c>
-      <c r="G3" s="3">
-        <v>150</v>
-      </c>
-      <c r="H3" s="5">
-        <v>168.3</v>
-      </c>
-      <c r="I3" s="5">
-        <v>4.8</v>
-      </c>
       <c r="J3" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K3" s="3">
-        <f t="shared" ref="K3:K66" si="1">PI()*(((H3-2*I3)*10^-3)^2/4)</f>
-        <v>1.9780794669897482E-2</v>
-      </c>
-      <c r="L3" s="5">
-        <v>3</v>
-      </c>
-      <c r="M3" s="3">
         <f t="shared" si="0"/>
-        <v>5.9342384009692446E-2</v>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="M3" s="7">
+        <f t="shared" ref="M3:M66" si="2">IF(L3&gt;0, L3, 1)</f>
+        <v>1</v>
       </c>
       <c r="N3" s="3">
-        <f t="shared" ref="N3:N66" si="2">M3*3600</f>
-        <v>213.63258243489281</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" ref="N3:N66" si="3">M3*K3</f>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="O3" s="3">
+        <f t="shared" si="1"/>
+        <v>18.505014313626919</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>398</v>
+        <v>350</v>
       </c>
       <c r="B4" s="3">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>81</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>158</v>
+        <v>216</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" s="3">
         <v>150</v>
@@ -1353,39 +1368,43 @@
         <v>84</v>
       </c>
       <c r="K4" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.9780794669897482E-2</v>
       </c>
       <c r="L4" s="5">
         <v>3</v>
       </c>
-      <c r="M4" s="3">
-        <f t="shared" si="0"/>
+      <c r="M4" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="N4" s="3">
+        <f t="shared" si="3"/>
         <v>5.9342384009692446E-2</v>
       </c>
-      <c r="N4" s="3">
-        <f t="shared" si="2"/>
+      <c r="O4" s="3">
+        <f t="shared" si="1"/>
         <v>213.63258243489281</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>413</v>
+        <v>370</v>
       </c>
       <c r="B5" s="3">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>81</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>159</v>
+        <v>221</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5" s="3">
         <v>150</v>
@@ -1400,39 +1419,43 @@
         <v>84</v>
       </c>
       <c r="K5" s="3">
+        <f t="shared" si="0"/>
+        <v>1.9780794669897482E-2</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="N5" s="3">
+        <f t="shared" si="3"/>
+        <v>5.9342384009692446E-2</v>
+      </c>
+      <c r="O5" s="3">
         <f t="shared" si="1"/>
-        <v>1.9780794669897482E-2</v>
-      </c>
-      <c r="L5" s="5">
-        <v>3.4</v>
-      </c>
-      <c r="M5" s="3">
-        <f t="shared" si="0"/>
-        <v>6.7254701877651438E-2</v>
-      </c>
-      <c r="N5" s="3">
-        <f t="shared" si="2"/>
-        <v>242.11692675954518</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>213.63258243489281</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>430</v>
+        <v>398</v>
       </c>
       <c r="B6" s="3">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>81</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>160</v>
+        <v>222</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G6" s="3">
         <v>150</v>
@@ -1447,344 +1470,374 @@
         <v>84</v>
       </c>
       <c r="K6" s="3">
+        <f t="shared" si="0"/>
+        <v>1.9780794669897482E-2</v>
+      </c>
+      <c r="L6" s="5">
+        <v>3</v>
+      </c>
+      <c r="M6" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="N6" s="3">
+        <f t="shared" si="3"/>
+        <v>5.9342384009692446E-2</v>
+      </c>
+      <c r="O6" s="3">
         <f t="shared" si="1"/>
-        <v>1.9780794669897482E-2</v>
-      </c>
-      <c r="L6" s="5">
-        <v>3.4</v>
-      </c>
-      <c r="M6" s="3">
-        <f t="shared" si="0"/>
-        <v>6.7254701877651438E-2</v>
-      </c>
-      <c r="N6" s="3">
-        <f t="shared" si="2"/>
-        <v>242.11692675954518</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>213.63258243489281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>482</v>
+        <v>413</v>
       </c>
       <c r="B7" s="3">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>81</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>161</v>
+        <v>223</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>89</v>
+        <v>6</v>
+      </c>
+      <c r="G7" s="3">
+        <v>150</v>
       </c>
       <c r="H7" s="5">
-        <v>204</v>
+        <v>168.3</v>
       </c>
       <c r="I7" s="5">
         <v>4.8</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K7" s="3">
+        <f t="shared" si="0"/>
+        <v>1.9780794669897482E-2</v>
+      </c>
+      <c r="L7" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="M7" s="7">
+        <f t="shared" si="2"/>
+        <v>3.4</v>
+      </c>
+      <c r="N7" s="3">
+        <f t="shared" si="3"/>
+        <v>6.7254701877651438E-2</v>
+      </c>
+      <c r="O7" s="3">
         <f t="shared" si="1"/>
-        <v>2.9681264736291797E-2</v>
-      </c>
-      <c r="L7" s="5">
-        <v>1.35</v>
-      </c>
-      <c r="M7" s="3">
-        <f t="shared" si="0"/>
-        <v>4.0069707393993931E-2</v>
-      </c>
-      <c r="N7" s="3">
-        <f t="shared" si="2"/>
-        <v>144.25094661837815</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>242.11692675954518</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <v>600</v>
+        <v>430</v>
       </c>
       <c r="B8" s="3">
-        <v>215</v>
+        <v>140</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="3">
+        <v>150</v>
+      </c>
+      <c r="H8" s="5">
+        <v>168.3</v>
+      </c>
+      <c r="I8" s="5">
+        <v>4.8</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" s="3">
+        <f t="shared" si="0"/>
+        <v>1.9780794669897482E-2</v>
+      </c>
+      <c r="L8" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="M8" s="7">
+        <f t="shared" si="2"/>
+        <v>3.4</v>
+      </c>
+      <c r="N8" s="3">
+        <f t="shared" si="3"/>
+        <v>6.7254701877651438E-2</v>
+      </c>
+      <c r="O8" s="3">
+        <f t="shared" si="1"/>
+        <v>242.11692675954518</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>482</v>
+      </c>
+      <c r="B9" s="3">
+        <v>118</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3">
+        <v>204</v>
+      </c>
+      <c r="H9" s="5">
+        <v>204</v>
+      </c>
+      <c r="I9" s="5">
+        <v>4.8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K9" s="3">
+        <f t="shared" si="0"/>
+        <v>2.9681264736291797E-2</v>
+      </c>
+      <c r="L9" s="5">
+        <v>1.35</v>
+      </c>
+      <c r="M9" s="7">
+        <f t="shared" si="2"/>
+        <v>1.35</v>
+      </c>
+      <c r="N9" s="3">
+        <f t="shared" si="3"/>
+        <v>4.0069707393993931E-2</v>
+      </c>
+      <c r="O9" s="3">
+        <f t="shared" si="1"/>
+        <v>144.25094661837815</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>600</v>
+      </c>
+      <c r="B10" s="3">
+        <v>215</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="3">
+        <v>350</v>
+      </c>
+      <c r="H10" s="5">
+        <v>355.6</v>
+      </c>
+      <c r="I10" s="5">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="3">
+        <f t="shared" si="0"/>
+        <v>9.0578525052007072E-2</v>
+      </c>
+      <c r="L10" s="5">
+        <v>2.35</v>
+      </c>
+      <c r="M10" s="7">
+        <f t="shared" si="2"/>
+        <v>2.35</v>
+      </c>
+      <c r="N10" s="3">
+        <f t="shared" si="3"/>
+        <v>0.21285953387221662</v>
+      </c>
+      <c r="O10" s="3">
+        <f t="shared" si="1"/>
+        <v>766.2943219399798</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>1042</v>
+      </c>
+      <c r="B11" s="3">
+        <v>785</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="3">
-        <v>350</v>
-      </c>
-      <c r="H8" s="5">
-        <v>355.6</v>
-      </c>
-      <c r="I8" s="5">
-        <v>8</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="E11" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="3">
+        <v>200</v>
+      </c>
+      <c r="H11" s="5">
+        <v>220</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K11" s="3">
+        <f t="shared" si="0"/>
+        <v>3.8013271108436497E-2</v>
+      </c>
+      <c r="L11" s="5"/>
+      <c r="M11" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N11" s="3">
+        <f t="shared" si="3"/>
+        <v>3.8013271108436497E-2</v>
+      </c>
+      <c r="O11" s="3">
         <f t="shared" si="1"/>
-        <v>9.0578525052007072E-2</v>
-      </c>
-      <c r="L8" s="5">
-        <v>2.35</v>
-      </c>
-      <c r="M8" s="3">
+        <v>136.84777599037139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>928</v>
+      </c>
+      <c r="B12" s="3">
+        <v>746</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="3">
+        <v>80</v>
+      </c>
+      <c r="H12" s="5">
+        <v>88.9</v>
+      </c>
+      <c r="I12" s="5">
+        <v>4</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K12" s="3">
         <f t="shared" si="0"/>
-        <v>0.21285953387221662</v>
-      </c>
-      <c r="N8" s="3">
-        <f t="shared" si="2"/>
-        <v>766.2943219399798</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <v>1042</v>
-      </c>
-      <c r="B9" s="3">
-        <v>785</v>
-      </c>
-      <c r="C9" s="3" t="s">
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="L12" s="5"/>
+      <c r="M12" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N12" s="3">
+        <f t="shared" si="3"/>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="O12" s="3">
+        <f t="shared" si="1"/>
+        <v>18.505014313626919</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>926</v>
+      </c>
+      <c r="B13" s="3">
+        <v>838</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="3">
-        <v>200</v>
-      </c>
-      <c r="H9" s="5">
-        <v>220</v>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K9" s="3">
-        <f t="shared" si="1"/>
-        <v>3.8013271108436497E-2</v>
-      </c>
-      <c r="L9" s="5"/>
-      <c r="M9" s="3">
+      <c r="D13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N9" s="3">
-        <f t="shared" si="2"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N13" s="3">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <v>928</v>
-      </c>
-      <c r="B10" s="3">
-        <v>746</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="3">
-        <v>80</v>
-      </c>
-      <c r="H10" s="5">
-        <v>88.9</v>
-      </c>
-      <c r="I10" s="5">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="O13" s="3">
         <f t="shared" si="1"/>
-        <v>5.1402817537852556E-3</v>
-      </c>
-      <c r="L10" s="5"/>
-      <c r="M10" s="3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
-        <v>820</v>
-      </c>
-      <c r="B11" s="3">
-        <v>1017</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="3">
-        <v>80</v>
-      </c>
-      <c r="H11" s="5">
-        <v>88.9</v>
-      </c>
-      <c r="I11" s="5">
-        <v>4</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K11" s="3">
-        <f t="shared" si="1"/>
-        <v>5.1402817537852556E-3</v>
-      </c>
-      <c r="L11" s="5"/>
-      <c r="M11" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <v>819</v>
-      </c>
-      <c r="B12" s="3">
-        <v>982.8</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="3">
-        <v>65</v>
-      </c>
-      <c r="H12" s="5">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="I12" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K12" s="3">
-        <f t="shared" si="1"/>
-        <v>3.728450015261999E-3</v>
-      </c>
-      <c r="L12" s="5"/>
-      <c r="M12" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
-        <v>813</v>
-      </c>
-      <c r="B13" s="3">
-        <v>935</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="3">
-        <v>100</v>
-      </c>
-      <c r="H13" s="5">
-        <v>114</v>
-      </c>
-      <c r="I13" s="5">
-        <v>4.5</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K13" s="3">
-        <f t="shared" si="1"/>
-        <v>8.6590147514568668E-3</v>
-      </c>
-      <c r="L13" s="5"/>
-      <c r="M13" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>926</v>
+        <v>882</v>
       </c>
       <c r="B14" s="3">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>73</v>
@@ -1793,10 +1846,10 @@
         <v>102</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="5"/>
@@ -1805,262 +1858,288 @@
         <v>84</v>
       </c>
       <c r="K14" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N14" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L14" s="5"/>
-      <c r="M14" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>882</v>
+        <v>813</v>
       </c>
       <c r="B15" s="3">
-        <v>845</v>
+        <v>935</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>73</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
+        <v>35</v>
+      </c>
+      <c r="G15" s="3">
+        <v>100</v>
+      </c>
+      <c r="H15" s="5">
+        <v>114</v>
+      </c>
+      <c r="I15" s="5">
+        <v>4.5</v>
+      </c>
       <c r="J15" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K15" s="3">
+        <f t="shared" si="0"/>
+        <v>8.6590147514568668E-3</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N15" s="3">
+        <f t="shared" si="3"/>
+        <v>8.6590147514568668E-3</v>
+      </c>
+      <c r="O15" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L15" s="5"/>
-      <c r="M15" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+        <v>31.17245310524472</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>1073</v>
+        <v>819</v>
       </c>
       <c r="B16" s="3">
-        <v>1081</v>
+        <v>982.8</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>73</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="3">
+        <v>65</v>
+      </c>
+      <c r="H16" s="5">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="I16" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K16" s="3">
+        <f t="shared" si="0"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N16" s="3">
+        <f t="shared" si="3"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="O16" s="3">
+        <f t="shared" si="1"/>
+        <v>13.422420054943197</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>820</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1017</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="3">
+        <v>80</v>
+      </c>
+      <c r="H17" s="5">
+        <v>88.9</v>
+      </c>
+      <c r="I17" s="5">
+        <v>4</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K17" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="L17" s="5"/>
+      <c r="M17" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N17" s="3">
+        <f t="shared" si="3"/>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="O17" s="3">
+        <f t="shared" si="1"/>
+        <v>18.505014313626919</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>1073</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1081</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G18" s="3">
         <v>125</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H18" s="5">
         <v>141</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I18" s="5">
         <v>5</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K16" s="3">
+      <c r="J18" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K18" s="3">
+        <f t="shared" si="0"/>
+        <v>1.3478217882063612E-2</v>
+      </c>
+      <c r="L18" s="5"/>
+      <c r="M18" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N18" s="3">
+        <f t="shared" si="3"/>
+        <v>1.3478217882063612E-2</v>
+      </c>
+      <c r="O18" s="3">
         <f t="shared" si="1"/>
-        <v>1.3478217882063612E-2</v>
-      </c>
-      <c r="L16" s="5"/>
-      <c r="M16" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
+        <v>48.521584375429001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
         <v>1515</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B19" s="3">
         <v>911</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" s="3">
-        <v>155</v>
-      </c>
-      <c r="H17" s="5">
-        <v>155</v>
-      </c>
-      <c r="I17" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K17" s="3">
-        <f t="shared" si="1"/>
-        <v>1.8002865285469776E-2</v>
-      </c>
-      <c r="L17" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="M17" s="3">
-        <f t="shared" si="0"/>
-        <v>1.2602005699828842E-2</v>
-      </c>
-      <c r="N17" s="3">
-        <f t="shared" si="2"/>
-        <v>45.367220519383828</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
-        <v>1504</v>
-      </c>
-      <c r="B18" s="3">
-        <v>967</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18" s="3">
-        <v>80</v>
-      </c>
-      <c r="H18" s="5">
-        <v>88.9</v>
-      </c>
-      <c r="I18" s="5">
-        <v>2</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K18" s="3">
-        <f t="shared" si="1"/>
-        <v>5.661157815750442E-3</v>
-      </c>
-      <c r="L18" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="M18" s="3">
-        <f t="shared" si="0"/>
-        <v>2.830578907875221E-3</v>
-      </c>
-      <c r="N18" s="3">
-        <f t="shared" si="2"/>
-        <v>10.190084068350796</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
-        <v>1525</v>
-      </c>
-      <c r="B19" s="3">
-        <v>952</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" s="3">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="H19" s="5">
-        <v>139.69999999999999</v>
+        <v>155</v>
       </c>
       <c r="I19" s="5">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>85</v>
       </c>
       <c r="K19" s="3">
+        <f t="shared" si="0"/>
+        <v>1.8002865285469776E-2</v>
+      </c>
+      <c r="L19" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="M19" s="7">
+        <f t="shared" si="2"/>
+        <v>0.7</v>
+      </c>
+      <c r="N19" s="3">
+        <f t="shared" si="3"/>
+        <v>1.2602005699828842E-2</v>
+      </c>
+      <c r="O19" s="3">
         <f t="shared" si="1"/>
-        <v>1.4462706625900674E-2</v>
-      </c>
-      <c r="L19" s="5">
-        <v>0.62</v>
-      </c>
-      <c r="M19" s="3">
-        <f t="shared" si="0"/>
-        <v>8.9668781080584174E-3</v>
-      </c>
-      <c r="N19" s="3">
-        <f t="shared" si="2"/>
-        <v>32.280761189010306</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+        <v>45.367220519383828</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>1340</v>
+        <v>1504</v>
       </c>
       <c r="B20" s="3">
-        <v>912</v>
+        <v>967</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G20" s="3">
         <v>80</v>
@@ -2075,37 +2154,43 @@
         <v>85</v>
       </c>
       <c r="K20" s="3">
+        <f t="shared" si="0"/>
+        <v>5.661157815750442E-3</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M20" s="7">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="N20" s="3">
+        <f t="shared" si="3"/>
+        <v>2.830578907875221E-3</v>
+      </c>
+      <c r="O20" s="3">
         <f t="shared" si="1"/>
-        <v>5.661157815750442E-3</v>
-      </c>
-      <c r="L20" s="5"/>
-      <c r="M20" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+        <v>10.190084068350796</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>1346</v>
+        <v>1525</v>
       </c>
       <c r="B21" s="3">
-        <v>1187</v>
+        <v>952</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G21" s="3">
         <v>125</v>
@@ -2120,22 +2205,26 @@
         <v>85</v>
       </c>
       <c r="K21" s="3">
+        <f t="shared" si="0"/>
+        <v>1.4462706625900674E-2</v>
+      </c>
+      <c r="L21" s="5">
+        <v>0.62</v>
+      </c>
+      <c r="M21" s="7">
+        <f t="shared" si="2"/>
+        <v>0.62</v>
+      </c>
+      <c r="N21" s="3">
+        <f t="shared" si="3"/>
+        <v>8.9668781080584174E-3</v>
+      </c>
+      <c r="O21" s="3">
         <f t="shared" si="1"/>
-        <v>1.4462706625900674E-2</v>
-      </c>
-      <c r="L21" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="M21" s="3">
-        <f t="shared" si="0"/>
-        <v>1.3016435963310606E-2</v>
-      </c>
-      <c r="N21" s="3">
-        <f t="shared" si="2"/>
-        <v>46.859169467918186</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+        <v>32.280761189010306</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>1121</v>
       </c>
@@ -2146,10 +2235,10 @@
         <v>75</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>47</v>
@@ -2167,20 +2256,24 @@
         <v>85</v>
       </c>
       <c r="K22" s="3">
+        <f t="shared" si="0"/>
+        <v>3.1415926535897934E-2</v>
+      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N22" s="3">
+        <f t="shared" si="3"/>
+        <v>3.1415926535897934E-2</v>
+      </c>
+      <c r="O22" s="3">
         <f t="shared" si="1"/>
-        <v>3.1415926535897934E-2</v>
-      </c>
-      <c r="L22" s="5"/>
-      <c r="M22" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+        <v>113.09733552923257</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>1359</v>
       </c>
@@ -2191,10 +2284,10 @@
         <v>75</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>44</v>
@@ -2212,45 +2305,49 @@
         <v>85</v>
       </c>
       <c r="K23" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.1415926535897934E-2</v>
       </c>
       <c r="L23" s="5">
         <v>2</v>
       </c>
-      <c r="M23" s="3">
-        <f t="shared" si="0"/>
+      <c r="M23" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="N23" s="3">
+        <f t="shared" si="3"/>
         <v>6.2831853071795868E-2</v>
       </c>
-      <c r="N23" s="3">
-        <f t="shared" si="2"/>
+      <c r="O23" s="3">
+        <f t="shared" si="1"/>
         <v>226.19467105846513</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>1337</v>
+        <v>1359</v>
       </c>
       <c r="B24" s="3">
-        <v>1003</v>
+        <v>1108</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G24" s="3">
-        <v>80</v>
+        <v>204</v>
       </c>
       <c r="H24" s="5">
-        <v>88.9</v>
+        <v>204</v>
       </c>
       <c r="I24" s="5">
         <v>2</v>
@@ -2259,43 +2356,49 @@
         <v>85</v>
       </c>
       <c r="K24" s="3">
+        <f t="shared" si="0"/>
+        <v>3.1415926535897934E-2</v>
+      </c>
+      <c r="L24" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="M24" s="7">
+        <f t="shared" si="2"/>
+        <v>1.8</v>
+      </c>
+      <c r="N24" s="3">
+        <f t="shared" si="3"/>
+        <v>5.6548667764616284E-2</v>
+      </c>
+      <c r="O24" s="3">
         <f t="shared" si="1"/>
-        <v>5.661157815750442E-3</v>
-      </c>
-      <c r="L24" s="5"/>
-      <c r="M24" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+        <v>203.57520395261861</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>1346</v>
+        <v>1359</v>
       </c>
       <c r="B25" s="3">
-        <v>1260</v>
+        <v>1163</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G25" s="3">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="H25" s="5">
-        <v>139.69999999999999</v>
+        <v>154</v>
       </c>
       <c r="I25" s="5">
         <v>2</v>
@@ -2304,22 +2407,26 @@
         <v>85</v>
       </c>
       <c r="K25" s="3">
+        <f t="shared" si="0"/>
+        <v>1.7671458676442587E-2</v>
+      </c>
+      <c r="L25" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="M25" s="7">
+        <f t="shared" si="2"/>
+        <v>2.8</v>
+      </c>
+      <c r="N25" s="3">
+        <f t="shared" si="3"/>
+        <v>4.9480084294039238E-2</v>
+      </c>
+      <c r="O25" s="3">
         <f t="shared" si="1"/>
-        <v>1.4462706625900674E-2</v>
-      </c>
-      <c r="L25" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="M25" s="3">
-        <f t="shared" si="0"/>
-        <v>2.6032871926621213E-2</v>
-      </c>
-      <c r="N25" s="3">
-        <f t="shared" si="2"/>
-        <v>93.718338935836371</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+        <v>178.12830345854127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>1359</v>
       </c>
@@ -2330,10 +2437,10 @@
         <v>75</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>42</v>
@@ -2351,45 +2458,49 @@
         <v>85</v>
       </c>
       <c r="K26" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.7671458676442587E-2</v>
       </c>
       <c r="L26" s="5">
         <v>2.5</v>
       </c>
-      <c r="M26" s="3">
-        <f t="shared" si="0"/>
+      <c r="M26" s="7">
+        <f t="shared" si="2"/>
+        <v>2.5</v>
+      </c>
+      <c r="N26" s="3">
+        <f t="shared" si="3"/>
         <v>4.4178646691106466E-2</v>
       </c>
-      <c r="N26" s="3">
-        <f t="shared" si="2"/>
+      <c r="O26" s="3">
+        <f t="shared" si="1"/>
         <v>159.04312808798326</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>1359</v>
+        <v>1340</v>
       </c>
       <c r="B27" s="3">
-        <v>1108</v>
+        <v>912</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G27" s="3">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="H27" s="5">
-        <v>204</v>
+        <v>88.9</v>
       </c>
       <c r="I27" s="5">
         <v>2</v>
@@ -2398,45 +2509,47 @@
         <v>85</v>
       </c>
       <c r="K27" s="3">
+        <f t="shared" si="0"/>
+        <v>5.661157815750442E-3</v>
+      </c>
+      <c r="L27" s="5"/>
+      <c r="M27" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N27" s="3">
+        <f t="shared" si="3"/>
+        <v>5.661157815750442E-3</v>
+      </c>
+      <c r="O27" s="3">
         <f t="shared" si="1"/>
-        <v>3.1415926535897934E-2</v>
-      </c>
-      <c r="L27" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="M27" s="3">
-        <f t="shared" si="0"/>
-        <v>5.6548667764616284E-2</v>
-      </c>
-      <c r="N27" s="3">
-        <f t="shared" si="2"/>
-        <v>203.57520395261861</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+        <v>20.380168136701592</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
-        <v>1359</v>
+        <v>1337</v>
       </c>
       <c r="B28" s="3">
-        <v>1163</v>
+        <v>1003</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G28" s="3">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="H28" s="5">
-        <v>154</v>
+        <v>88.9</v>
       </c>
       <c r="I28" s="5">
         <v>2</v>
@@ -2445,45 +2558,47 @@
         <v>85</v>
       </c>
       <c r="K28" s="3">
+        <f t="shared" si="0"/>
+        <v>5.661157815750442E-3</v>
+      </c>
+      <c r="L28" s="5"/>
+      <c r="M28" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N28" s="3">
+        <f t="shared" si="3"/>
+        <v>5.661157815750442E-3</v>
+      </c>
+      <c r="O28" s="3">
         <f t="shared" si="1"/>
-        <v>1.7671458676442587E-2</v>
-      </c>
-      <c r="L28" s="5">
-        <v>2.8</v>
-      </c>
-      <c r="M28" s="3">
-        <f t="shared" si="0"/>
-        <v>4.9480084294039238E-2</v>
-      </c>
-      <c r="N28" s="3">
-        <f t="shared" si="2"/>
-        <v>178.12830345854127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+        <v>20.380168136701592</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>1049</v>
+        <v>1346</v>
       </c>
       <c r="B29" s="3">
-        <v>913</v>
+        <v>1260</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G29" s="3">
-        <v>204</v>
+        <v>125</v>
       </c>
       <c r="H29" s="5">
-        <v>204</v>
+        <v>139.69999999999999</v>
       </c>
       <c r="I29" s="5">
         <v>2</v>
@@ -2492,39 +2607,49 @@
         <v>85</v>
       </c>
       <c r="K29" s="3">
+        <f t="shared" si="0"/>
+        <v>1.4462706625900674E-2</v>
+      </c>
+      <c r="L29" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="M29" s="7">
+        <f t="shared" si="2"/>
+        <v>1.8</v>
+      </c>
+      <c r="N29" s="3">
+        <f t="shared" si="3"/>
+        <v>2.6032871926621213E-2</v>
+      </c>
+      <c r="O29" s="3">
         <f t="shared" si="1"/>
-        <v>3.1415926535897934E-2</v>
-      </c>
-      <c r="L29" s="5"/>
-      <c r="M29" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
+        <v>93.718338935836371</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>1346</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1187</v>
+      </c>
       <c r="C30" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G30" s="3">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H30" s="5">
-        <v>129</v>
+        <v>139.69999999999999</v>
       </c>
       <c r="I30" s="5">
         <v>2</v>
@@ -2533,43 +2658,49 @@
         <v>85</v>
       </c>
       <c r="K30" s="3">
+        <f t="shared" si="0"/>
+        <v>1.4462706625900674E-2</v>
+      </c>
+      <c r="L30" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="M30" s="7">
+        <f t="shared" si="2"/>
+        <v>0.9</v>
+      </c>
+      <c r="N30" s="3">
+        <f t="shared" si="3"/>
+        <v>1.3016435963310606E-2</v>
+      </c>
+      <c r="O30" s="3">
         <f t="shared" si="1"/>
-        <v>1.2271846303085129E-2</v>
-      </c>
-      <c r="L30" s="5"/>
-      <c r="M30" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N30" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+        <v>46.859169467918186</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <v>1020</v>
+        <v>1049</v>
       </c>
       <c r="B31" s="3">
-        <v>1174</v>
+        <v>913</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>80</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G31" s="3">
-        <v>129</v>
+        <v>204</v>
       </c>
       <c r="H31" s="5">
-        <v>129</v>
+        <v>204</v>
       </c>
       <c r="I31" s="5">
         <v>2</v>
@@ -2578,20 +2709,24 @@
         <v>85</v>
       </c>
       <c r="K31" s="3">
+        <f t="shared" si="0"/>
+        <v>3.1415926535897934E-2</v>
+      </c>
+      <c r="L31" s="5"/>
+      <c r="M31" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N31" s="3">
+        <f t="shared" si="3"/>
+        <v>3.1415926535897934E-2</v>
+      </c>
+      <c r="O31" s="3">
         <f t="shared" si="1"/>
-        <v>1.2271846303085129E-2</v>
-      </c>
-      <c r="L31" s="5"/>
-      <c r="M31" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N31" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+        <v>113.09733552923257</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>1024</v>
       </c>
@@ -2602,10 +2737,10 @@
         <v>80</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>52</v>
@@ -2623,20 +2758,24 @@
         <v>85</v>
       </c>
       <c r="K32" s="3">
+        <f t="shared" si="0"/>
+        <v>3.1415926535897934E-2</v>
+      </c>
+      <c r="L32" s="5"/>
+      <c r="M32" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N32" s="3">
+        <f t="shared" si="3"/>
+        <v>3.1415926535897934E-2</v>
+      </c>
+      <c r="O32" s="3">
         <f t="shared" si="1"/>
-        <v>3.1415926535897934E-2</v>
-      </c>
-      <c r="L32" s="5"/>
-      <c r="M32" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+        <v>113.09733552923257</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>1024</v>
       </c>
@@ -2647,10 +2786,10 @@
         <v>80</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>53</v>
@@ -2668,217 +2807,233 @@
         <v>85</v>
       </c>
       <c r="K33" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5033177771091243E-3</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N33" s="3">
+        <f t="shared" si="3"/>
+        <v>9.5033177771091243E-3</v>
+      </c>
+      <c r="O33" s="3">
         <f t="shared" si="1"/>
-        <v>9.5033177771091243E-3</v>
-      </c>
-      <c r="L33" s="5"/>
-      <c r="M33" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N33" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="3">
+        <v>34.211943997592847</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G34" s="3">
+        <v>129</v>
+      </c>
+      <c r="H34" s="5">
+        <v>129</v>
+      </c>
+      <c r="I34" s="5">
+        <v>2</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K34" s="3">
+        <f t="shared" ref="K34:K65" si="4">PI()*(((H34-2*I34)*10^-3)^2/4)</f>
+        <v>1.2271846303085129E-2</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N34" s="3">
+        <f t="shared" si="3"/>
+        <v>1.2271846303085129E-2</v>
+      </c>
+      <c r="O34" s="3">
+        <f t="shared" ref="O34:O65" si="5">N34*3600</f>
+        <v>44.178646691106465</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <v>1020</v>
+      </c>
+      <c r="B35" s="3">
+        <v>1174</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G35" s="3">
+        <v>129</v>
+      </c>
+      <c r="H35" s="5">
+        <v>129</v>
+      </c>
+      <c r="I35" s="5">
+        <v>2</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K35" s="3">
+        <f t="shared" si="4"/>
+        <v>1.2271846303085129E-2</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N35" s="3">
+        <f t="shared" si="3"/>
+        <v>1.2271846303085129E-2</v>
+      </c>
+      <c r="O35" s="3">
+        <f t="shared" si="5"/>
+        <v>44.178646691106465</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
         <v>933</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B36" s="3">
         <v>1204</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G34" s="3">
-        <v>65</v>
-      </c>
-      <c r="H34" s="5">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="I34" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K34" s="3">
-        <f t="shared" si="1"/>
-        <v>3.728450015261999E-3</v>
-      </c>
-      <c r="L34" s="5"/>
-      <c r="M34" s="3">
-        <f t="shared" ref="M34:M65" si="3">L34*K34</f>
-        <v>0</v>
-      </c>
-      <c r="N34" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="3">
-        <v>926</v>
-      </c>
-      <c r="B35" s="3">
-        <v>1092</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G35" s="3">
-        <v>125</v>
-      </c>
-      <c r="H35" s="5">
-        <v>139</v>
-      </c>
-      <c r="I35" s="5">
-        <v>5</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K35" s="3">
-        <f t="shared" si="1"/>
-        <v>1.3069810837096936E-2</v>
-      </c>
-      <c r="L35" s="5"/>
-      <c r="M35" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N35" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="3">
-        <v>923</v>
-      </c>
-      <c r="B36" s="3">
-        <v>1292</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G36" s="3">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="H36" s="5">
-        <v>43</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="I36" s="5">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K36" s="3">
-        <f t="shared" si="1"/>
-        <v>1.1945906065275189E-3</v>
+        <f t="shared" si="4"/>
+        <v>3.728450015261999E-3</v>
       </c>
       <c r="L36" s="5"/>
-      <c r="M36" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="M36" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N36" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="O36" s="3">
+        <f t="shared" si="5"/>
+        <v>13.422420054943197</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
-        <v>778</v>
+        <v>923</v>
       </c>
       <c r="B37" s="3">
-        <v>1285</v>
+        <v>1292</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G37" s="3">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H37" s="5">
-        <v>60.3</v>
+        <v>43</v>
       </c>
       <c r="I37" s="5">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K37" s="3">
-        <f t="shared" si="1"/>
-        <v>2.2145165154970788E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.1945906065275189E-3</v>
       </c>
       <c r="L37" s="5"/>
-      <c r="M37" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="M37" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N37" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>1.1945906065275189E-3</v>
+      </c>
+      <c r="O37" s="3">
+        <f t="shared" si="5"/>
+        <v>4.300526183499068</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
-        <v>888</v>
+        <v>778</v>
       </c>
       <c r="B38" s="3">
-        <v>1109</v>
+        <v>1285</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G38" s="3">
         <v>50</v>
@@ -2893,127 +3048,139 @@
         <v>84</v>
       </c>
       <c r="K38" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.2145165154970788E-3</v>
       </c>
       <c r="L38" s="5"/>
-      <c r="M38" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="M38" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N38" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O38" s="3">
+        <f t="shared" si="5"/>
+        <v>7.9722594557894837</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
-        <v>823</v>
+        <v>926</v>
       </c>
       <c r="B39" s="3">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="F39" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G39" s="3">
+        <v>125</v>
+      </c>
+      <c r="H39" s="5">
+        <v>139</v>
+      </c>
+      <c r="I39" s="5">
+        <v>5</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K39" s="3">
+        <f t="shared" si="4"/>
+        <v>1.3069810837096936E-2</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N39" s="3">
+        <f t="shared" si="3"/>
+        <v>1.3069810837096936E-2</v>
+      </c>
+      <c r="O39" s="3">
+        <f t="shared" si="5"/>
+        <v>47.051319013548969</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <v>823</v>
+      </c>
+      <c r="B40" s="3">
+        <v>1093</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G40" s="3">
         <v>100</v>
       </c>
-      <c r="H39" s="5">
+      <c r="H40" s="5">
         <v>114</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I40" s="5">
         <v>4.5</v>
       </c>
-      <c r="J39" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K39" s="3">
-        <f t="shared" si="1"/>
+      <c r="J40" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K40" s="3">
+        <f t="shared" si="4"/>
         <v>8.6590147514568668E-3</v>
       </c>
-      <c r="L39" s="5"/>
-      <c r="M39" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N39" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="3">
-        <v>1390</v>
-      </c>
-      <c r="B40" s="3">
-        <v>1248</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G40" s="3">
-        <v>80</v>
-      </c>
-      <c r="H40" s="5">
-        <v>88.9</v>
-      </c>
-      <c r="I40" s="5">
-        <v>4</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K40" s="3">
-        <f t="shared" si="1"/>
-        <v>5.1402817537852556E-3</v>
-      </c>
       <c r="L40" s="5"/>
-      <c r="M40" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="M40" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N40" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>8.6590147514568668E-3</v>
+      </c>
+      <c r="O40" s="3">
+        <f t="shared" si="5"/>
+        <v>31.17245310524472</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <v>1454</v>
+        <v>888</v>
       </c>
       <c r="B41" s="3">
-        <v>1130</v>
+        <v>1109</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="G41" s="3">
         <v>50</v>
@@ -3028,65 +3195,73 @@
         <v>84</v>
       </c>
       <c r="K41" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.2145165154970788E-3</v>
       </c>
       <c r="L41" s="5"/>
-      <c r="M41" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="M41" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N41" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O41" s="3">
+        <f t="shared" si="5"/>
+        <v>7.9722594557894837</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <v>1574</v>
+        <v>1390</v>
       </c>
       <c r="B42" s="3">
-        <v>1150</v>
+        <v>1248</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>78</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G42" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H42" s="5">
-        <v>60.3</v>
+        <v>88.9</v>
       </c>
       <c r="I42" s="5">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K42" s="3">
-        <f t="shared" si="1"/>
-        <v>2.2145165154970788E-3</v>
+        <f t="shared" si="4"/>
+        <v>5.1402817537852556E-3</v>
       </c>
       <c r="L42" s="5"/>
-      <c r="M42" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="M42" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N42" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="O42" s="3">
+        <f t="shared" si="5"/>
+        <v>18.505014313626919</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>1416</v>
       </c>
@@ -3097,10 +3272,10 @@
         <v>78</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>25</v>
@@ -3118,82 +3293,90 @@
         <v>84</v>
       </c>
       <c r="K43" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1.378852869642194E-3</v>
       </c>
       <c r="L43" s="5"/>
-      <c r="M43" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="M43" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N43" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>1.378852869642194E-3</v>
+      </c>
+      <c r="O43" s="3">
+        <f t="shared" si="5"/>
+        <v>4.9638703307118988</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <v>1629</v>
+        <v>1454</v>
       </c>
       <c r="B44" s="3">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>78</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G44" s="3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H44" s="5">
-        <v>48.3</v>
+        <v>60.3</v>
       </c>
       <c r="I44" s="5">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K44" s="3">
-        <f t="shared" si="1"/>
-        <v>1.378852869642194E-3</v>
+        <f t="shared" si="4"/>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="L44" s="5"/>
-      <c r="M44" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="M44" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N44" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O44" s="3">
+        <f t="shared" si="5"/>
+        <v>7.9722594557894837</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
-        <v>1234</v>
+        <v>1574</v>
       </c>
       <c r="B45" s="3">
-        <v>1271</v>
+        <v>1150</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G45" s="3">
         <v>50</v>
@@ -3208,82 +3391,90 @@
         <v>84</v>
       </c>
       <c r="K45" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.2145165154970788E-3</v>
       </c>
       <c r="L45" s="5"/>
-      <c r="M45" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="M45" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N45" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O45" s="3">
+        <f t="shared" si="5"/>
+        <v>7.9722594557894837</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <v>1216</v>
+        <v>1629</v>
       </c>
       <c r="B46" s="3">
-        <v>1184</v>
+        <v>1132</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G46" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H46" s="5">
-        <v>60.3</v>
+        <v>48.3</v>
       </c>
       <c r="I46" s="5">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K46" s="3">
-        <f t="shared" si="1"/>
-        <v>2.2145165154970788E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.378852869642194E-3</v>
       </c>
       <c r="L46" s="5"/>
-      <c r="M46" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="M46" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N46" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>1.378852869642194E-3</v>
+      </c>
+      <c r="O46" s="3">
+        <f t="shared" si="5"/>
+        <v>4.9638703307118988</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <v>1217</v>
+        <v>1234</v>
       </c>
       <c r="B47" s="3">
-        <v>1237</v>
+        <v>1271</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>79</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G47" s="3">
         <v>50</v>
@@ -3298,80 +3489,90 @@
         <v>84</v>
       </c>
       <c r="K47" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.2145165154970788E-3</v>
       </c>
       <c r="L47" s="5"/>
-      <c r="M47" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="M47" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N47" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O47" s="3">
+        <f t="shared" si="5"/>
+        <v>7.9722594557894837</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <v>1570</v>
+        <v>1217</v>
       </c>
       <c r="B48" s="3">
-        <v>380</v>
+        <v>1237</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G48" s="3">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H48" s="5">
-        <v>220</v>
-      </c>
-      <c r="I48" s="5"/>
+        <v>60.3</v>
+      </c>
+      <c r="I48" s="5">
+        <v>3.6</v>
+      </c>
       <c r="J48" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K48" s="3">
-        <f t="shared" si="1"/>
-        <v>3.8013271108436497E-2</v>
+        <f t="shared" si="4"/>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="L48" s="5"/>
-      <c r="M48" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="M48" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N48" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O48" s="3">
+        <f t="shared" si="5"/>
+        <v>7.9722594557894837</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>1600</v>
+        <v>1216</v>
       </c>
       <c r="B49" s="3">
-        <v>446</v>
+        <v>1184</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G49" s="3">
         <v>50</v>
@@ -3386,131 +3587,141 @@
         <v>84</v>
       </c>
       <c r="K49" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.2145165154970788E-3</v>
       </c>
       <c r="L49" s="5"/>
-      <c r="M49" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="M49" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N49" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O49" s="3">
+        <f t="shared" si="5"/>
+        <v>7.9722594557894837</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <v>1553</v>
+        <v>1490</v>
       </c>
       <c r="B50" s="3">
-        <v>345</v>
+        <v>311</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G50" s="3">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="H50" s="5">
-        <v>141</v>
-      </c>
-      <c r="I50" s="5">
-        <v>5</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="I50" s="5"/>
       <c r="J50" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K50" s="3">
-        <f t="shared" si="1"/>
-        <v>1.3478217882063612E-2</v>
+        <f t="shared" si="4"/>
+        <v>3.8013271108436497E-2</v>
       </c>
       <c r="L50" s="5">
-        <v>1.9</v>
-      </c>
-      <c r="M50" s="3">
-        <f t="shared" si="3"/>
-        <v>2.560861397592086E-2</v>
+        <v>0.9</v>
+      </c>
+      <c r="M50" s="7">
+        <f t="shared" si="2"/>
+        <v>0.9</v>
       </c>
       <c r="N50" s="3">
-        <f t="shared" si="2"/>
-        <v>92.191010313315104</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>3.421194399759285E-2</v>
+      </c>
+      <c r="O50" s="3">
+        <f t="shared" si="5"/>
+        <v>123.16299839133426</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
-        <v>1534</v>
+        <v>1553</v>
       </c>
       <c r="B51" s="3">
-        <v>436</v>
+        <v>345</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G51" s="3">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="H51" s="5">
-        <v>88.9</v>
+        <v>141</v>
       </c>
       <c r="I51" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K51" s="3">
-        <f t="shared" si="1"/>
-        <v>5.1402817537852556E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.3478217882063612E-2</v>
       </c>
       <c r="L51" s="5">
-        <v>3</v>
-      </c>
-      <c r="M51" s="3">
-        <f t="shared" si="3"/>
-        <v>1.5420845261355766E-2</v>
+        <v>1.9</v>
+      </c>
+      <c r="M51" s="7">
+        <f t="shared" si="2"/>
+        <v>1.9</v>
       </c>
       <c r="N51" s="3">
-        <f t="shared" si="2"/>
-        <v>55.515042940880754</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>2.560861397592086E-2</v>
+      </c>
+      <c r="O51" s="3">
+        <f t="shared" si="5"/>
+        <v>92.191010313315104</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
-        <v>1541</v>
+        <v>1534</v>
       </c>
       <c r="B52" s="3">
-        <v>476</v>
+        <v>436</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G52" s="3">
         <v>80</v>
@@ -3525,86 +3736,94 @@
         <v>84</v>
       </c>
       <c r="K52" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>5.1402817537852556E-3</v>
       </c>
       <c r="L52" s="5">
-        <v>0.46</v>
-      </c>
-      <c r="M52" s="3">
-        <f t="shared" si="3"/>
-        <v>2.3645296067412178E-3</v>
+        <v>3</v>
+      </c>
+      <c r="M52" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="N52" s="3">
-        <f t="shared" si="2"/>
-        <v>8.5123065842683836</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>1.5420845261355766E-2</v>
+      </c>
+      <c r="O52" s="3">
+        <f t="shared" si="5"/>
+        <v>55.515042940880754</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <v>1702</v>
+        <v>1541</v>
       </c>
       <c r="B53" s="3">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G53" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H53" s="5">
-        <v>60.3</v>
+        <v>88.9</v>
       </c>
       <c r="I53" s="5">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K53" s="3">
-        <f t="shared" si="1"/>
-        <v>2.2145165154970788E-3</v>
+        <f t="shared" si="4"/>
+        <v>5.1402817537852556E-3</v>
       </c>
       <c r="L53" s="5">
-        <v>3</v>
-      </c>
-      <c r="M53" s="3">
-        <f t="shared" si="3"/>
-        <v>6.6435495464912363E-3</v>
+        <v>0.46</v>
+      </c>
+      <c r="M53" s="7">
+        <f t="shared" si="2"/>
+        <v>0.46</v>
       </c>
       <c r="N53" s="3">
-        <f t="shared" si="2"/>
-        <v>23.916778367368451</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>2.3645296067412178E-3</v>
+      </c>
+      <c r="O53" s="3">
+        <f t="shared" si="5"/>
+        <v>8.5123065842683836</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <v>1490</v>
+        <v>1570</v>
       </c>
       <c r="B54" s="3">
-        <v>311</v>
+        <v>380</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G54" s="3">
         <v>200</v>
@@ -3617,170 +3836,184 @@
         <v>84</v>
       </c>
       <c r="K54" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>3.8013271108436497E-2</v>
       </c>
-      <c r="L54" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="M54" s="3">
-        <f t="shared" si="3"/>
-        <v>3.421194399759285E-2</v>
+      <c r="L54" s="5"/>
+      <c r="M54" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N54" s="3">
-        <f t="shared" si="2"/>
-        <v>123.16299839133426</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
+        <f t="shared" si="3"/>
+        <v>3.8013271108436497E-2</v>
+      </c>
+      <c r="O54" s="3">
+        <f t="shared" si="5"/>
+        <v>136.84777599037139</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <v>1600</v>
+      </c>
+      <c r="B55" s="3">
+        <v>446</v>
+      </c>
       <c r="C55" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="F55" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="G55" s="3">
+        <v>50</v>
+      </c>
+      <c r="H55" s="5">
+        <v>60.3</v>
+      </c>
+      <c r="I55" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K55" s="3">
+        <f t="shared" si="4"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L55" s="5"/>
+      <c r="M55" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N55" s="3">
+        <f t="shared" si="3"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O55" s="3">
+        <f t="shared" si="5"/>
+        <v>7.9722594557894837</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <v>1702</v>
+      </c>
+      <c r="B56" s="3">
+        <v>463</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" s="3">
+        <v>50</v>
+      </c>
+      <c r="H56" s="5">
+        <v>60.3</v>
+      </c>
+      <c r="I56" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K56" s="3">
+        <f t="shared" si="4"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L56" s="5">
+        <v>3</v>
+      </c>
+      <c r="M56" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="N56" s="3">
+        <f t="shared" si="3"/>
+        <v>6.6435495464912363E-3</v>
+      </c>
+      <c r="O56" s="3">
+        <f t="shared" si="5"/>
+        <v>23.916778367368451</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3">
         <v>80</v>
       </c>
-      <c r="H55" s="5">
+      <c r="H57" s="5">
         <v>88.9</v>
       </c>
-      <c r="I55" s="5">
+      <c r="I57" s="5">
         <v>4</v>
       </c>
-      <c r="J55" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K55" s="3">
-        <f t="shared" si="1"/>
+      <c r="J57" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K57" s="3">
+        <f t="shared" si="4"/>
         <v>5.1402817537852556E-3</v>
       </c>
-      <c r="L55" s="5"/>
-      <c r="M55" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N55" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="3">
-        <v>1754</v>
-      </c>
-      <c r="B56" s="3">
-        <v>894.7</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G56" s="3">
-        <v>100</v>
-      </c>
-      <c r="H56" s="5">
-        <v>114</v>
-      </c>
-      <c r="I56" s="5">
-        <v>4.5</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K56" s="3">
-        <f t="shared" si="1"/>
-        <v>8.6590147514568668E-3</v>
-      </c>
-      <c r="L56" s="5"/>
-      <c r="M56" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N56" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="3">
-        <v>1739</v>
-      </c>
-      <c r="B57" s="3">
-        <v>957</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G57" s="3">
-        <v>65</v>
-      </c>
-      <c r="H57" s="5">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="I57" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K57" s="3">
-        <f>PI()*(((H57-2*I57)*10^-3)^2/4)</f>
-        <v>3.728450015261999E-3</v>
-      </c>
-      <c r="L57" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="M57" s="3">
-        <f t="shared" si="3"/>
-        <v>4.1012950167881989E-3</v>
+      <c r="L57" s="5"/>
+      <c r="M57" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N57" s="3">
-        <f t="shared" si="2"/>
-        <v>14.764662060437516</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="O57" s="3">
+        <f t="shared" si="5"/>
+        <v>18.505014313626919</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
-        <v>1748</v>
+        <v>1887</v>
       </c>
       <c r="B58" s="3">
-        <v>918</v>
+        <v>897</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G58" s="3">
         <v>65</v>
@@ -3795,84 +4028,90 @@
         <v>84</v>
       </c>
       <c r="K58" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>3.728450015261999E-3</v>
       </c>
-      <c r="L58" s="5">
-        <v>1</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="L58" s="5"/>
+      <c r="M58" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N58" s="3">
         <f t="shared" si="3"/>
         <v>3.728450015261999E-3</v>
       </c>
-      <c r="N58" s="3">
-        <f t="shared" si="2"/>
+      <c r="O58" s="3">
+        <f t="shared" si="5"/>
         <v>13.422420054943197</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <v>1887</v>
+        <v>1754</v>
       </c>
       <c r="B59" s="3">
-        <v>897</v>
+        <v>894.7</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G59" s="3">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="H59" s="5">
-        <v>76.099999999999994</v>
+        <v>114</v>
       </c>
       <c r="I59" s="5">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K59" s="3">
-        <f t="shared" si="1"/>
-        <v>3.728450015261999E-3</v>
+        <f t="shared" si="4"/>
+        <v>8.6590147514568668E-3</v>
       </c>
       <c r="L59" s="5"/>
-      <c r="M59" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="M59" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N59" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>8.6590147514568668E-3</v>
+      </c>
+      <c r="O59" s="3">
+        <f t="shared" si="5"/>
+        <v>31.17245310524472</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="B60" s="3">
-        <v>986</v>
+        <v>944</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G60" s="3">
         <v>50</v>
@@ -3887,43 +4126,47 @@
         <v>84</v>
       </c>
       <c r="K60" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.2145165154970788E-3</v>
       </c>
       <c r="L60" s="5"/>
-      <c r="M60" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="M60" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N60" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O60" s="3">
+        <f t="shared" si="5"/>
+        <v>7.9722594557894837</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>1872</v>
+        <v>1739</v>
       </c>
       <c r="B61" s="3">
-        <v>944</v>
+        <v>957</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G61" s="3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H61" s="5">
-        <v>60.3</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="I61" s="5">
         <v>3.6</v>
@@ -3932,301 +4175,337 @@
         <v>84</v>
       </c>
       <c r="K61" s="3">
-        <f t="shared" si="1"/>
-        <v>2.2145165154970788E-3</v>
-      </c>
-      <c r="L61" s="5"/>
-      <c r="M61" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L61" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M61" s="7">
+        <f t="shared" si="2"/>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N61" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>4.1012950167881989E-3</v>
+      </c>
+      <c r="O61" s="3">
+        <f t="shared" si="5"/>
+        <v>14.764662060437516</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>1920</v>
+        <v>1873</v>
       </c>
       <c r="B62" s="3">
-        <v>1000</v>
+        <v>986</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="F62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G62" s="3">
+        <v>50</v>
+      </c>
+      <c r="H62" s="5">
+        <v>60.3</v>
+      </c>
+      <c r="I62" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K62" s="3">
+        <f t="shared" si="4"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L62" s="5"/>
+      <c r="M62" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N62" s="3">
+        <f t="shared" si="3"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O62" s="3">
+        <f t="shared" si="5"/>
+        <v>7.9722594557894837</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A63" s="3">
+        <v>1748</v>
+      </c>
+      <c r="B63" s="3">
+        <v>918</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G63" s="3">
+        <v>65</v>
+      </c>
+      <c r="H63" s="5">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="I63" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K63" s="3">
+        <f t="shared" si="4"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L63" s="5">
+        <v>1</v>
+      </c>
+      <c r="M63" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N63" s="3">
+        <f t="shared" si="3"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="O63" s="3">
+        <f t="shared" si="5"/>
+        <v>13.422420054943197</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A64" s="3">
+        <v>1920</v>
+      </c>
+      <c r="B64" s="3">
+        <v>1000</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F64" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G64" s="3">
         <v>32</v>
       </c>
-      <c r="H62" s="5">
+      <c r="H64" s="5">
         <v>42.2</v>
       </c>
-      <c r="I62" s="5">
+      <c r="I64" s="5">
         <v>3.2</v>
       </c>
-      <c r="J62" s="3" t="s">
+      <c r="J64" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K62" s="3">
-        <f t="shared" si="1"/>
+      <c r="K64" s="3">
+        <f t="shared" si="4"/>
         <v>1.0065977021367059E-3</v>
       </c>
-      <c r="L62" s="5"/>
-      <c r="M62" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N62" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G63" s="3">
-        <v>100</v>
-      </c>
-      <c r="H63" s="5">
-        <v>114</v>
-      </c>
-      <c r="I63" s="5">
-        <v>5</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K63" s="3">
-        <f t="shared" si="1"/>
-        <v>8.4948665353068026E-3</v>
-      </c>
-      <c r="L63" s="5"/>
-      <c r="M63" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N63" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="3">
+      <c r="L64" s="5"/>
+      <c r="M64" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N64" s="3">
+        <f t="shared" si="3"/>
+        <v>1.0065977021367059E-3</v>
+      </c>
+      <c r="O64" s="3">
+        <f t="shared" si="5"/>
+        <v>3.6237517276921412</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A65" s="3">
         <v>983</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B65" s="3">
         <v>952</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G64" s="3">
-        <v>150</v>
-      </c>
-      <c r="H64" s="5">
-        <v>168.3</v>
-      </c>
-      <c r="I64" s="5">
-        <v>5</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K64" s="3">
-        <f t="shared" si="1"/>
-        <v>1.9681206182778688E-2</v>
-      </c>
-      <c r="L64" s="5"/>
-      <c r="M64" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N64" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
       <c r="C65" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D65" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G65" s="3">
         <v>150</v>
       </c>
-      <c r="E65" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G65" s="3">
-        <v>100</v>
-      </c>
       <c r="H65" s="5">
-        <v>114</v>
+        <v>168.3</v>
       </c>
       <c r="I65" s="5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K65" s="3">
-        <f t="shared" si="1"/>
-        <v>8.6590147514568668E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.9681206182778688E-2</v>
       </c>
       <c r="L65" s="5"/>
-      <c r="M65" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="M65" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N65" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="3">
-        <v>1035</v>
-      </c>
-      <c r="B66" s="3">
-        <v>1023</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>1.9681206182778688E-2</v>
+      </c>
+      <c r="O65" s="3">
+        <f t="shared" si="5"/>
+        <v>70.852342258003276</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
       <c r="C66" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G66" s="3">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="H66" s="5">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="I66" s="5">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K66" s="3">
-        <f t="shared" si="1"/>
-        <v>3.4004913041721279E-3</v>
+        <f t="shared" ref="K66:K71" si="6">PI()*(((H66-2*I66)*10^-3)^2/4)</f>
+        <v>8.4948665353068026E-3</v>
       </c>
       <c r="L66" s="5"/>
-      <c r="M66" s="3">
-        <f t="shared" ref="M66:M71" si="4">L66*K66</f>
-        <v>0</v>
+      <c r="M66" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N66" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="3">
-        <v>1031</v>
-      </c>
-      <c r="B67" s="3">
-        <v>931</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>8.4948665353068026E-3</v>
+      </c>
+      <c r="O66" s="3">
+        <f t="shared" ref="O66:O71" si="7">N66*3600</f>
+        <v>30.58151952710449</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
       <c r="C67" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G67" s="3">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="H67" s="5">
-        <v>76.099999999999994</v>
+        <v>114</v>
       </c>
       <c r="I67" s="5">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K67" s="3">
-        <f t="shared" ref="K67:K71" si="5">PI()*(((H67-2*I67)*10^-3)^2/4)</f>
-        <v>3.728450015261999E-3</v>
+        <f t="shared" si="6"/>
+        <v>8.6590147514568668E-3</v>
       </c>
       <c r="L67" s="5"/>
-      <c r="M67" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
+      <c r="M67" s="7">
+        <f t="shared" ref="M67:M71" si="8">IF(L67&gt;0, L67, 1)</f>
+        <v>1</v>
       </c>
       <c r="N67" s="3">
-        <f t="shared" ref="N67:N71" si="6">M67*3600</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
+        <f t="shared" ref="N67:N71" si="9">M67*K67</f>
+        <v>8.6590147514568668E-3</v>
+      </c>
+      <c r="O67" s="3">
+        <f t="shared" si="7"/>
+        <v>31.17245310524472</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A68" s="3">
+        <v>1035</v>
+      </c>
+      <c r="B68" s="3">
+        <v>1023</v>
+      </c>
       <c r="C68" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G68" s="3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H68" s="5">
-        <v>60.3</v>
+        <v>73</v>
       </c>
       <c r="I68" s="5">
         <v>3.6</v>
@@ -4235,33 +4514,37 @@
         <v>84</v>
       </c>
       <c r="K68" s="3">
-        <f t="shared" si="5"/>
-        <v>2.2145165154970788E-3</v>
+        <f t="shared" si="6"/>
+        <v>3.4004913041721279E-3</v>
       </c>
       <c r="L68" s="5"/>
-      <c r="M68" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
+      <c r="M68" s="7">
+        <f t="shared" si="8"/>
+        <v>1</v>
       </c>
       <c r="N68" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v>3.4004913041721279E-3</v>
+      </c>
+      <c r="O68" s="3">
+        <f t="shared" si="7"/>
+        <v>12.24176869501966</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G69" s="3">
         <v>50</v>
@@ -4276,100 +4559,124 @@
         <v>84</v>
       </c>
       <c r="K69" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.2145165154970788E-3</v>
       </c>
       <c r="L69" s="5"/>
-      <c r="M69" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
+      <c r="M69" s="7">
+        <f t="shared" si="8"/>
+        <v>1</v>
       </c>
       <c r="N69" s="3">
+        <f t="shared" si="9"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O69" s="3">
+        <f t="shared" si="7"/>
+        <v>7.9722594557894837</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A70" s="3">
+        <v>1031</v>
+      </c>
+      <c r="B70" s="3">
+        <v>931</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G70" s="3">
+        <v>65</v>
+      </c>
+      <c r="H70" s="5">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="I70" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K70" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G70" s="3">
-        <v>100</v>
-      </c>
-      <c r="H70" s="5">
-        <v>114</v>
-      </c>
-      <c r="I70" s="5">
-        <v>4.5</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K70" s="3">
-        <f t="shared" si="5"/>
-        <v>8.6590147514568668E-3</v>
+        <v>3.728450015261999E-3</v>
       </c>
       <c r="L70" s="5"/>
-      <c r="M70" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
+      <c r="M70" s="7">
+        <f t="shared" si="8"/>
+        <v>1</v>
       </c>
       <c r="N70" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="O70" s="3">
+        <f t="shared" si="7"/>
+        <v>13.422420054943197</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
+      <c r="C71" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="D71" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G71" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H71" s="5">
-        <v>88.9</v>
+        <v>60.3</v>
       </c>
       <c r="I71" s="5">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K71" s="3">
-        <f t="shared" si="5"/>
-        <v>5.1402817537852556E-3</v>
+        <f t="shared" si="6"/>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="L71" s="5"/>
-      <c r="M71" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
+      <c r="M71" s="7">
+        <f t="shared" si="8"/>
+        <v>1</v>
       </c>
       <c r="N71" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O71" s="3">
+        <f t="shared" si="7"/>
+        <v>7.9722594557894837</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1" xr:uid="{80D9219E-119C-467C-9531-507D24E0A5C1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M72">
+  <autoFilter ref="A1:O1" xr:uid="{80D9219E-119C-467C-9531-507D24E0A5C1}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O71">
+      <sortCondition ref="D1"/>
+    </sortState>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N72">
     <sortCondition ref="C40:C72"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/punts/punts-mesura-at.xlsx
+++ b/data/punts/punts-mesura-at.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\punts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01ED9052-6439-44B1-A2F7-919180CC047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DFE0AA-45CC-4C77-944D-45B086AA12DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4CA701B3-5EB8-45D8-B6BB-1F057196BE44}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{4CA701B3-5EB8-45D8-B6BB-1F057196BE44}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1170,19 +1170,20 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="1"/>
-    <col min="8" max="9" width="9.5546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="5.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" style="6" customWidth="1"/>
+    <col min="9" max="9" width="8.21875" style="6" customWidth="1"/>
     <col min="10" max="10" width="11" style="1" customWidth="1"/>
     <col min="11" max="11" width="13.109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17.109375" style="6" customWidth="1"/>
+    <col min="12" max="12" width="15.33203125" style="6" customWidth="1"/>
     <col min="13" max="13" width="17.109375" style="8" customWidth="1"/>
     <col min="14" max="14" width="21.44140625" style="1" customWidth="1"/>
     <col min="15" max="15" width="21.77734375" style="1" customWidth="1"/>
@@ -1238,10 +1239,10 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>1121</v>
+        <v>0.45165189363416597</v>
       </c>
       <c r="B2" s="3">
-        <v>785</v>
+        <v>0.44729344729344728</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>225</v>
@@ -1288,10 +1289,10 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <v>1131</v>
+        <v>0.45568090249798548</v>
       </c>
       <c r="B3" s="3">
-        <v>785</v>
+        <v>0.44729344729344728</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>225</v>
@@ -1338,10 +1339,10 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>350</v>
+        <v>0.14101531023368252</v>
       </c>
       <c r="B4" s="3">
-        <v>131</v>
+        <v>7.4643874643874647E-2</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>81</v>
@@ -1389,10 +1390,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>370</v>
+        <v>0.14907332796132153</v>
       </c>
       <c r="B5" s="3">
-        <v>134</v>
+        <v>7.635327635327635E-2</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>81</v>
@@ -1440,10 +1441,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>398</v>
+        <v>0.16035455278001612</v>
       </c>
       <c r="B6" s="3">
-        <v>135</v>
+        <v>7.6923076923076927E-2</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>81</v>
@@ -1491,10 +1492,10 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>413</v>
+        <v>0.16639806607574537</v>
       </c>
       <c r="B7" s="3">
-        <v>137</v>
+        <v>7.8062678062678068E-2</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>81</v>
@@ -1542,10 +1543,10 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <v>430</v>
+        <v>0.17324738114423852</v>
       </c>
       <c r="B8" s="3">
-        <v>140</v>
+        <v>7.9772079772079771E-2</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>81</v>
@@ -1593,10 +1594,10 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>482</v>
+        <v>0.19419822723609992</v>
       </c>
       <c r="B9" s="3">
-        <v>118</v>
+        <v>6.7236467236467243E-2</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>81</v>
@@ -1644,10 +1645,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>600</v>
+        <v>0.24174053182917002</v>
       </c>
       <c r="B10" s="3">
-        <v>215</v>
+        <v>0.12250712250712251</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>81</v>
@@ -1695,10 +1696,10 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
-        <v>1042</v>
+        <v>0.41982272360999195</v>
       </c>
       <c r="B11" s="3">
-        <v>785</v>
+        <v>0.44729344729344728</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>73</v>
@@ -1742,10 +1743,10 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>928</v>
+        <v>0.37389202256244963</v>
       </c>
       <c r="B12" s="3">
-        <v>746</v>
+        <v>0.42507122507122508</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>73</v>
@@ -1791,10 +1792,10 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <v>926</v>
+        <v>0.37308622078968573</v>
       </c>
       <c r="B13" s="3">
-        <v>838</v>
+        <v>0.4774928774928775</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>73</v>
@@ -1834,10 +1835,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>882</v>
+        <v>0.35535858178887991</v>
       </c>
       <c r="B14" s="3">
-        <v>845</v>
+        <v>0.48148148148148145</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>73</v>
@@ -1877,10 +1878,10 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>813</v>
+        <v>0.32755842062852536</v>
       </c>
       <c r="B15" s="3">
-        <v>935</v>
+        <v>0.53276353276353272</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>73</v>
@@ -1926,10 +1927,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>819</v>
+        <v>0.32997582594681707</v>
       </c>
       <c r="B16" s="3">
-        <v>982.8</v>
+        <v>0.55999999999999994</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>73</v>
@@ -1975,10 +1976,10 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>820</v>
+        <v>0.33037872683319902</v>
       </c>
       <c r="B17" s="3">
-        <v>1017</v>
+        <v>0.57948717948717954</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>73</v>
@@ -2024,10 +2025,10 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>1073</v>
+        <v>0.4323126510878324</v>
       </c>
       <c r="B18" s="3">
-        <v>1081</v>
+        <v>0.61595441595441591</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>73</v>
@@ -2073,10 +2074,10 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>1515</v>
+        <v>0.61039484286865431</v>
       </c>
       <c r="B19" s="3">
-        <v>911</v>
+        <v>0.51908831908831909</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>74</v>
@@ -2124,10 +2125,10 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>1504</v>
+        <v>0.60596293311845284</v>
       </c>
       <c r="B20" s="3">
-        <v>967</v>
+        <v>0.55099715099715096</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>74</v>
@@ -2175,10 +2176,10 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>1525</v>
+        <v>0.61442385173247382</v>
       </c>
       <c r="B21" s="3">
-        <v>952</v>
+        <v>0.54245014245014245</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>74</v>
@@ -2226,10 +2227,10 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>1121</v>
+        <v>0.45165189363416597</v>
       </c>
       <c r="B22" s="3">
-        <v>827</v>
+        <v>0.47122507122507123</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>75</v>
@@ -2275,10 +2276,10 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>1359</v>
+        <v>0.54754230459307007</v>
       </c>
       <c r="B23" s="3">
-        <v>956</v>
+        <v>0.54472934472934476</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>75</v>
@@ -2326,10 +2327,10 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>1359</v>
+        <v>0.54754230459307007</v>
       </c>
       <c r="B24" s="3">
-        <v>1108</v>
+        <v>0.63133903133903135</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>75</v>
@@ -2377,10 +2378,10 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>1359</v>
+        <v>0.54754230459307007</v>
       </c>
       <c r="B25" s="3">
-        <v>1163</v>
+        <v>0.66267806267806273</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>75</v>
@@ -2428,10 +2429,10 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>1359</v>
+        <v>0.54754230459307007</v>
       </c>
       <c r="B26" s="3">
-        <v>1228</v>
+        <v>0.69971509971509971</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>75</v>
@@ -2479,10 +2480,10 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>1340</v>
+        <v>0.5398871877518131</v>
       </c>
       <c r="B27" s="3">
-        <v>912</v>
+        <v>0.5196581196581197</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>75</v>
@@ -2528,10 +2529,10 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
-        <v>1337</v>
+        <v>0.53867848509266725</v>
       </c>
       <c r="B28" s="3">
-        <v>1003</v>
+        <v>0.57150997150997151</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>75</v>
@@ -2577,10 +2578,10 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>1346</v>
+        <v>0.5423045930701047</v>
       </c>
       <c r="B29" s="3">
-        <v>1260</v>
+        <v>0.71794871794871795</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>75</v>
@@ -2628,10 +2629,10 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
-        <v>1346</v>
+        <v>0.5423045930701047</v>
       </c>
       <c r="B30" s="3">
-        <v>1187</v>
+        <v>0.67635327635327636</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>75</v>
@@ -2679,10 +2680,10 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <v>1049</v>
+        <v>0.42264302981466562</v>
       </c>
       <c r="B31" s="3">
-        <v>913</v>
+        <v>0.52022792022792019</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>80</v>
@@ -2728,10 +2729,10 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <v>1024</v>
+        <v>0.41257050765511682</v>
       </c>
       <c r="B32" s="3">
-        <v>1148</v>
+        <v>0.6541310541310541</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>80</v>
@@ -2777,10 +2778,10 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
-        <v>1024</v>
+        <v>0.41257050765511682</v>
       </c>
       <c r="B33" s="3">
-        <v>1233</v>
+        <v>0.70256410256410251</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>80</v>
@@ -2825,8 +2826,12 @@
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
+      <c r="A34" s="3">
+        <v>0</v>
+      </c>
+      <c r="B34" s="3">
+        <v>0</v>
+      </c>
       <c r="C34" s="3" t="s">
         <v>80</v>
       </c>
@@ -2871,10 +2876,10 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <v>1020</v>
+        <v>0.41095890410958902</v>
       </c>
       <c r="B35" s="3">
-        <v>1174</v>
+        <v>0.66894586894586894</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>80</v>
@@ -2920,10 +2925,10 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
-        <v>933</v>
+        <v>0.37590652699435939</v>
       </c>
       <c r="B36" s="3">
-        <v>1204</v>
+        <v>0.68603988603988608</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>76</v>
@@ -2969,10 +2974,10 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
-        <v>923</v>
+        <v>0.37187751813053987</v>
       </c>
       <c r="B37" s="3">
-        <v>1292</v>
+        <v>0.73618233618233619</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>76</v>
@@ -3018,10 +3023,10 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
-        <v>778</v>
+        <v>0.31345688960515711</v>
       </c>
       <c r="B38" s="3">
-        <v>1285</v>
+        <v>0.73219373219373218</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>76</v>
@@ -3067,10 +3072,10 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
-        <v>926</v>
+        <v>0.37308622078968573</v>
       </c>
       <c r="B39" s="3">
-        <v>1092</v>
+        <v>0.62222222222222223</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>76</v>
@@ -3116,10 +3121,10 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <v>823</v>
+        <v>0.33158742949234488</v>
       </c>
       <c r="B40" s="3">
-        <v>1093</v>
+        <v>0.62279202279202284</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>76</v>
@@ -3165,10 +3170,10 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <v>888</v>
+        <v>0.35777598710717162</v>
       </c>
       <c r="B41" s="3">
-        <v>1109</v>
+        <v>0.63190883190883196</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>76</v>
@@ -3214,10 +3219,10 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <v>1390</v>
+        <v>0.56003223207091057</v>
       </c>
       <c r="B42" s="3">
-        <v>1248</v>
+        <v>0.71111111111111114</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>78</v>
@@ -3263,10 +3268,10 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
-        <v>1416</v>
+        <v>0.57050765511684121</v>
       </c>
       <c r="B43" s="3">
-        <v>1175</v>
+        <v>0.66951566951566954</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>78</v>
@@ -3312,10 +3317,10 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <v>1454</v>
+        <v>0.58581788879935537</v>
       </c>
       <c r="B44" s="3">
-        <v>1130</v>
+        <v>0.64387464387464388</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>78</v>
@@ -3361,10 +3366,10 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
-        <v>1574</v>
+        <v>0.63416599516518934</v>
       </c>
       <c r="B45" s="3">
-        <v>1150</v>
+        <v>0.65527065527065531</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>78</v>
@@ -3410,10 +3415,10 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <v>1629</v>
+        <v>0.65632554391619657</v>
       </c>
       <c r="B46" s="3">
-        <v>1132</v>
+        <v>0.64501424501424498</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>78</v>
@@ -3459,10 +3464,10 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <v>1234</v>
+        <v>0.49717969379532634</v>
       </c>
       <c r="B47" s="3">
-        <v>1271</v>
+        <v>0.72421652421652427</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>79</v>
@@ -3508,10 +3513,10 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <v>1217</v>
+        <v>0.49033037872683322</v>
       </c>
       <c r="B48" s="3">
-        <v>1237</v>
+        <v>0.70484330484330482</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>79</v>
@@ -3557,10 +3562,10 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>1216</v>
+        <v>0.48992747784045126</v>
       </c>
       <c r="B49" s="3">
-        <v>1184</v>
+        <v>0.67464387464387465</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>79</v>
@@ -3606,10 +3611,10 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <v>1490</v>
+        <v>0.60032232070910552</v>
       </c>
       <c r="B50" s="3">
-        <v>311</v>
+        <v>0.17720797720797721</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>11</v>
@@ -3655,10 +3660,10 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
-        <v>1553</v>
+        <v>0.62570507655116836</v>
       </c>
       <c r="B51" s="3">
-        <v>345</v>
+        <v>0.19658119658119658</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>11</v>
@@ -3706,10 +3711,10 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
-        <v>1534</v>
+        <v>0.61804995970991139</v>
       </c>
       <c r="B52" s="3">
-        <v>436</v>
+        <v>0.24843304843304842</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>11</v>
@@ -3757,10 +3762,10 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <v>1541</v>
+        <v>0.62087026591458505</v>
       </c>
       <c r="B53" s="3">
-        <v>476</v>
+        <v>0.27122507122507122</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>11</v>
@@ -3808,10 +3813,10 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <v>1570</v>
+        <v>0.63255439161966154</v>
       </c>
       <c r="B54" s="3">
-        <v>380</v>
+        <v>0.21652421652421652</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>11</v>
@@ -3855,10 +3860,10 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
-        <v>1600</v>
+        <v>0.64464141821112009</v>
       </c>
       <c r="B55" s="3">
-        <v>446</v>
+        <v>0.25413105413105413</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>11</v>
@@ -3904,10 +3909,10 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <v>1702</v>
+        <v>0.68573730862207893</v>
       </c>
       <c r="B56" s="3">
-        <v>463</v>
+        <v>0.26381766381766381</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>11</v>
@@ -3954,8 +3959,12 @@
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
+      <c r="A57" s="3">
+        <v>0</v>
+      </c>
+      <c r="B57" s="3">
+        <v>0</v>
+      </c>
       <c r="C57" s="3" t="s">
         <v>11</v>
       </c>
@@ -3998,10 +4007,10 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
-        <v>1887</v>
+        <v>0.76027397260273977</v>
       </c>
       <c r="B58" s="3">
-        <v>897</v>
+        <v>0.51111111111111107</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>77</v>
@@ -4047,10 +4056,10 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <v>1754</v>
+        <v>0.70668815471394042</v>
       </c>
       <c r="B59" s="3">
-        <v>894.7</v>
+        <v>0.50980056980056987</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>77</v>
@@ -4096,10 +4105,10 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <v>1872</v>
+        <v>0.75423045930701049</v>
       </c>
       <c r="B60" s="3">
-        <v>944</v>
+        <v>0.53789173789173794</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>77</v>
@@ -4145,10 +4154,10 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>1739</v>
+        <v>0.70064464141821114</v>
       </c>
       <c r="B61" s="3">
-        <v>957</v>
+        <v>0.54529914529914525</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>77</v>
@@ -4196,10 +4205,10 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>1873</v>
+        <v>0.75463336019339244</v>
       </c>
       <c r="B62" s="3">
-        <v>986</v>
+        <v>0.56182336182336179</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>77</v>
@@ -4245,10 +4254,10 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
-        <v>1748</v>
+        <v>0.70427074939564871</v>
       </c>
       <c r="B63" s="3">
-        <v>918</v>
+        <v>0.52307692307692311</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>77</v>
@@ -4296,10 +4305,10 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
-        <v>1920</v>
+        <v>0.77356970185334406</v>
       </c>
       <c r="B64" s="3">
-        <v>1000</v>
+        <v>0.56980056980056981</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>77</v>
@@ -4345,10 +4354,10 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
-        <v>983</v>
+        <v>0.39605157131345686</v>
       </c>
       <c r="B65" s="3">
-        <v>952</v>
+        <v>0.54245014245014245</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>72</v>
@@ -4393,8 +4402,12 @@
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
+      <c r="A66" s="3">
+        <v>0</v>
+      </c>
+      <c r="B66" s="3">
+        <v>0</v>
+      </c>
       <c r="C66" s="3" t="s">
         <v>72</v>
       </c>
@@ -4438,8 +4451,12 @@
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
+      <c r="A67" s="3">
+        <v>0</v>
+      </c>
+      <c r="B67" s="3">
+        <v>0</v>
+      </c>
       <c r="C67" s="3" t="s">
         <v>72</v>
       </c>
@@ -4484,10 +4501,10 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
-        <v>1035</v>
+        <v>0.41700241740531829</v>
       </c>
       <c r="B68" s="3">
-        <v>1023</v>
+        <v>0.58290598290598294</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>72</v>
@@ -4532,8 +4549,12 @@
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
+      <c r="A69" s="3">
+        <v>0</v>
+      </c>
+      <c r="B69" s="3">
+        <v>0</v>
+      </c>
       <c r="C69" s="3" t="s">
         <v>72</v>
       </c>
@@ -4578,10 +4599,10 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
-        <v>1031</v>
+        <v>0.41539081385979049</v>
       </c>
       <c r="B70" s="3">
-        <v>931</v>
+        <v>0.53048433048433052</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>72</v>
@@ -4626,8 +4647,12 @@
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
+      <c r="A71" s="3">
+        <v>0</v>
+      </c>
+      <c r="B71" s="3">
+        <v>0</v>
+      </c>
       <c r="C71" s="3" t="s">
         <v>72</v>
       </c>
@@ -4669,6 +4694,108 @@
         <f t="shared" si="7"/>
         <v>7.9722594557894837</v>
       </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A72" s="3">
+        <v>0</v>
+      </c>
+      <c r="B72" s="3">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A73" s="3">
+        <v>0</v>
+      </c>
+      <c r="B73" s="3">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1" xr:uid="{80D9219E-119C-467C-9531-507D24E0A5C1}">
@@ -4681,6 +4808,6 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="60" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="71" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/punts/punts-mesura-at.xlsx
+++ b/data/punts/punts-mesura-at.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\punts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DFE0AA-45CC-4C77-944D-45B086AA12DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1AB8AC-434F-424B-B264-AC4D13B79A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{4CA701B3-5EB8-45D8-B6BB-1F057196BE44}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4CA701B3-5EB8-45D8-B6BB-1F057196BE44}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="255">
   <si>
     <t>id</t>
   </si>
@@ -726,6 +726,84 @@
   </si>
   <si>
     <t>measured speed</t>
+  </si>
+  <si>
+    <t>GF-ASS</t>
+  </si>
+  <si>
+    <t>GF-ASS-1</t>
+  </si>
+  <si>
+    <t>GF-ASS-2</t>
+  </si>
+  <si>
+    <t>GF-ASS-3</t>
+  </si>
+  <si>
+    <t>GF-ASS-4</t>
+  </si>
+  <si>
+    <t>Y-190-1</t>
+  </si>
+  <si>
+    <t>Y-190-2</t>
+  </si>
+  <si>
+    <t>Y-180-3</t>
+  </si>
+  <si>
+    <t>Y-180-4</t>
+  </si>
+  <si>
+    <t>Nautas</t>
+  </si>
+  <si>
+    <t>SS-3000</t>
+  </si>
+  <si>
+    <t>SS-1000</t>
+  </si>
+  <si>
+    <t>S-600</t>
+  </si>
+  <si>
+    <t>SI-603</t>
+  </si>
+  <si>
+    <t>S-2100/S-2200</t>
+  </si>
+  <si>
+    <t>S-2100/S-2201</t>
+  </si>
+  <si>
+    <t>S-2100/S-2202</t>
+  </si>
+  <si>
+    <t>S-2100/S-2203</t>
+  </si>
+  <si>
+    <t>S-2100/S-2204</t>
+  </si>
+  <si>
+    <t>SI-2107</t>
+  </si>
+  <si>
+    <t>SI-2x07</t>
+  </si>
+  <si>
+    <t>SI-2207</t>
+  </si>
+  <si>
+    <t>SS-2100</t>
+  </si>
+  <si>
+    <t>SS-2200</t>
+  </si>
+  <si>
+    <t>S-6000</t>
+  </si>
+  <si>
+    <t>S-6002</t>
   </si>
 </sst>
 </file>
@@ -1170,13 +1248,13 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.88671875" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.5546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="5.44140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.5546875" style="6" customWidth="1"/>
@@ -4433,7 +4511,7 @@
         <v>84</v>
       </c>
       <c r="K66" s="3">
-        <f t="shared" ref="K66:K71" si="6">PI()*(((H66-2*I66)*10^-3)^2/4)</f>
+        <f t="shared" ref="K66:K87" si="6">PI()*(((H66-2*I66)*10^-3)^2/4)</f>
         <v>8.4948665353068026E-3</v>
       </c>
       <c r="L66" s="5"/>
@@ -4697,105 +4775,620 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="B72" s="3">
-        <v>0</v>
-      </c>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
+      <c r="G72" s="3">
+        <v>65</v>
+      </c>
+      <c r="H72" s="3">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="I72" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K72" s="3">
+        <f t="shared" si="6"/>
+        <v>3.728450015261999E-3</v>
+      </c>
       <c r="L72" s="3"/>
-      <c r="M72" s="3"/>
-      <c r="N72" s="3"/>
-      <c r="O72" s="3"/>
+      <c r="M72" s="3">
+        <v>1</v>
+      </c>
+      <c r="N72" s="3">
+        <f t="shared" ref="N72:N86" si="10">M72*K72</f>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="O72" s="3">
+        <f t="shared" ref="O72:O75" si="11">N72*3600</f>
+        <v>13.422420054943197</v>
+      </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="B73" s="3">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3">
+        <v>65</v>
+      </c>
+      <c r="H73" s="3">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="I73" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K73" s="3">
+        <f t="shared" si="6"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3">
+        <v>1</v>
+      </c>
+      <c r="N73" s="3">
+        <f t="shared" si="10"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="O73" s="3">
+        <f t="shared" si="11"/>
+        <v>13.422420054943197</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A74" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="B74" s="3">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3">
+        <v>65</v>
+      </c>
+      <c r="H74" s="3">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="I74" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K74" s="3">
+        <f t="shared" si="6"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3">
+        <v>1</v>
+      </c>
+      <c r="N74" s="3">
+        <f t="shared" si="10"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="O74" s="3">
+        <f t="shared" si="11"/>
+        <v>13.422420054943197</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A75" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="B75" s="3">
+        <v>0.374</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3">
+        <v>65</v>
+      </c>
+      <c r="H75" s="3">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="I75" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K75" s="3">
+        <f t="shared" si="6"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3">
+        <v>1</v>
+      </c>
+      <c r="N75" s="3">
+        <f t="shared" si="10"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="O75" s="3">
+        <f t="shared" si="11"/>
+        <v>13.422420054943197</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E76" s="3" t="str">
+        <f>D76&amp;"01"</f>
+        <v>SS-300001</v>
+      </c>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3">
+        <v>50</v>
+      </c>
+      <c r="H76" s="3">
+        <v>60.3</v>
+      </c>
+      <c r="I76" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3">
+        <f t="shared" si="6"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3">
+        <v>1</v>
+      </c>
+      <c r="N76" s="3">
+        <f t="shared" si="10"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O76" s="3">
+        <f t="shared" ref="O76:O86" si="12">N76*3600</f>
+        <v>7.9722594557894837</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A77" s="3">
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="B77" s="3">
+        <v>0.33600000000000002</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E77" s="3" t="str">
+        <f>D77&amp;"02"</f>
+        <v>SS-100002</v>
+      </c>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3">
+        <v>50</v>
+      </c>
+      <c r="H77" s="3">
+        <v>60.3</v>
+      </c>
+      <c r="I77" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3">
+        <f t="shared" si="6"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3">
+        <v>1</v>
+      </c>
+      <c r="N77" s="3">
+        <f t="shared" si="10"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O77" s="3">
+        <f t="shared" si="12"/>
+        <v>7.9722594557894837</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A78" s="3">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="B78" s="3">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E78" s="3" t="str">
+        <f>D78&amp;1</f>
+        <v>SI-6031</v>
+      </c>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3">
+        <v>65</v>
+      </c>
+      <c r="H78" s="3">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="I78" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3">
+        <f t="shared" si="6"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L78" s="3"/>
+      <c r="M78" s="3">
+        <v>1</v>
+      </c>
+      <c r="N78" s="3">
+        <f t="shared" si="10"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="O78" s="3">
+        <f t="shared" si="12"/>
+        <v>13.422420054943197</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A79" s="3">
+        <v>6.3E-2</v>
+      </c>
+      <c r="B79" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E79" s="3" t="str">
+        <f>D79&amp;"01"</f>
+        <v>SI-210701</v>
+      </c>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3">
+        <v>65</v>
+      </c>
+      <c r="H79" s="3">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="I79" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3">
+        <f t="shared" si="6"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L79" s="3"/>
+      <c r="M79" s="3">
+        <v>1</v>
+      </c>
+      <c r="N79" s="3">
+        <f t="shared" si="10"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="O79" s="3">
+        <f t="shared" si="12"/>
+        <v>13.422420054943197</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A80" s="3">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="B80" s="3">
+        <v>0.84099999999999997</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E80" s="3" t="str">
+        <f>D80&amp;"02"</f>
+        <v>SI-220702</v>
+      </c>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3">
+        <v>50</v>
+      </c>
+      <c r="H80" s="3">
+        <v>60.3</v>
+      </c>
+      <c r="I80" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3">
+        <f t="shared" si="6"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3">
+        <v>1</v>
+      </c>
+      <c r="N80" s="3">
+        <f t="shared" si="10"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O80" s="3">
+        <f t="shared" si="12"/>
+        <v>7.9722594557894837</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A81" s="3">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="B81" s="3">
+        <v>0.86799999999999999</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E81" s="3" t="str">
+        <f>D81&amp;"03"</f>
+        <v>SI-2x0703</v>
+      </c>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3">
+        <v>80</v>
+      </c>
+      <c r="H81" s="3">
+        <v>88.9</v>
+      </c>
+      <c r="I81" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3">
+        <f t="shared" si="6"/>
+        <v>5.2424463468799948E-3</v>
+      </c>
+      <c r="L81" s="3"/>
+      <c r="M81" s="3">
+        <v>1</v>
+      </c>
+      <c r="N81" s="3">
+        <f t="shared" si="10"/>
+        <v>5.2424463468799948E-3</v>
+      </c>
+      <c r="O81" s="3">
+        <f t="shared" si="12"/>
+        <v>18.872806848767983</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E82" s="3" t="str">
+        <f>D82&amp;"04"</f>
+        <v>SS-210004</v>
+      </c>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3">
+        <v>50</v>
+      </c>
+      <c r="H82" s="3">
+        <v>60.3</v>
+      </c>
+      <c r="I82" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3">
+        <f t="shared" si="6"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L82" s="3"/>
+      <c r="M82" s="3">
+        <v>1</v>
+      </c>
+      <c r="N82" s="3">
+        <f t="shared" si="10"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O82" s="3">
+        <f t="shared" si="12"/>
+        <v>7.9722594557894837</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E83" s="3" t="str">
+        <f>D83&amp;"05"</f>
+        <v>SS-220005</v>
+      </c>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3">
+        <v>50</v>
+      </c>
+      <c r="H83" s="3">
+        <v>60.3</v>
+      </c>
+      <c r="I83" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3">
+        <f t="shared" si="6"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L83" s="3"/>
+      <c r="M83" s="3">
+        <v>1</v>
+      </c>
+      <c r="N83" s="3">
+        <f t="shared" si="10"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="O83" s="3">
+        <f t="shared" si="12"/>
+        <v>7.9722594557894837</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A84" s="3">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="B84" s="3">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E84" s="3" t="str">
+        <f>D84&amp;1</f>
+        <v>S-60021</v>
+      </c>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3">
+        <v>100</v>
+      </c>
+      <c r="H84" s="3">
+        <v>114.3</v>
+      </c>
+      <c r="I84" s="3">
+        <v>5</v>
+      </c>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3">
+        <f t="shared" si="6"/>
+        <v>8.5439460665375083E-3</v>
+      </c>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3">
+        <v>1</v>
+      </c>
+      <c r="N84" s="3">
+        <f t="shared" si="10"/>
+        <v>8.5439460665375083E-3</v>
+      </c>
+      <c r="O84" s="3">
+        <f t="shared" si="12"/>
+        <v>30.75820583953503</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K85" s="3">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="B73" s="3">
+      <c r="M85" s="3">
+        <v>1</v>
+      </c>
+      <c r="N85" s="3">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3"/>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3"/>
-      <c r="M74" s="3"/>
-      <c r="N74" s="3"/>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
-      <c r="J75" s="3"/>
-      <c r="K75" s="3"/>
-      <c r="L75" s="3"/>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3"/>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
-      <c r="J76" s="3"/>
-      <c r="K76" s="3"/>
-      <c r="L76" s="3"/>
-      <c r="M76" s="3"/>
-      <c r="N76" s="3"/>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
-      <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
-      <c r="L77" s="3"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3"/>
-      <c r="O77" s="3"/>
+      <c r="O85" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K86" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>1</v>
+      </c>
+      <c r="N86" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K87" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1" xr:uid="{80D9219E-119C-467C-9531-507D24E0A5C1}">

--- a/data/punts/punts-mesura-at.xlsx
+++ b/data/punts/punts-mesura-at.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\punts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1AB8AC-434F-424B-B264-AC4D13B79A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8914D5-D58E-4069-A03E-7882C8F638E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4CA701B3-5EB8-45D8-B6BB-1F057196BE44}"/>
   </bookViews>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <v>0.08</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="B72" s="3">
-        <v>0.32800000000000001</v>
+        <v>0.15759699999999999</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>229</v>
@@ -4821,10 +4821,10 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <v>0.08</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="B73" s="3">
-        <v>0.34100000000000003</v>
+        <v>0.168905</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>229</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <v>0.08</v>
+        <v>9.1499999999999998E-2</v>
       </c>
       <c r="B74" s="3">
-        <v>0.36799999999999999</v>
+        <v>0.20494699999999999</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>229</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <v>0.08</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="B75" s="3">
-        <v>0.374</v>
+        <v>0.21696099999999999</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>229</v>
@@ -4958,8 +4958,6 @@
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
       <c r="C76" s="3" t="s">
         <v>238</v>
       </c>
@@ -5000,10 +4998,10 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <v>0.28199999999999997</v>
+        <v>0.307</v>
       </c>
       <c r="B77" s="3">
-        <v>0.33600000000000002</v>
+        <v>0.16678399999999999</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>238</v>
@@ -5045,10 +5043,10 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>0.16800000000000001</v>
+        <v>0.14549999999999999</v>
       </c>
       <c r="B78" s="3">
-        <v>0.63700000000000001</v>
+        <v>0.46148400000000001</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>241</v>
@@ -5090,10 +5088,10 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <v>6.3E-2</v>
+        <v>0.1225</v>
       </c>
       <c r="B79" s="3">
-        <v>0.08</v>
+        <v>0.68551200000000001</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>243</v>
@@ -5135,10 +5133,10 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <v>7.5999999999999998E-2</v>
+        <v>0.111</v>
       </c>
       <c r="B80" s="3">
-        <v>0.84099999999999997</v>
+        <v>0.67349800000000004</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>244</v>
@@ -5180,10 +5178,10 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <v>8.2000000000000003E-2</v>
+        <v>7.85E-2</v>
       </c>
       <c r="B81" s="3">
-        <v>0.86799999999999999</v>
+        <v>0.66855100000000001</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>245</v>
@@ -5224,8 +5222,6 @@
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
       <c r="C82" s="3" t="s">
         <v>246</v>
       </c>
@@ -5306,11 +5302,11 @@
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A84" s="3">
-        <v>0.10199999999999999</v>
+      <c r="A84" s="1">
+        <v>0.121</v>
       </c>
       <c r="B84" s="3">
-        <v>0.86299999999999999</v>
+        <v>0.76183699999999999</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>253</v>

--- a/data/punts/punts-mesura-at.xlsx
+++ b/data/punts/punts-mesura-at.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\punts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8914D5-D58E-4069-A03E-7882C8F638E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C14452-6ED7-4AA7-9A7A-EB775AB914B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4CA701B3-5EB8-45D8-B6BB-1F057196BE44}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="267">
   <si>
     <t>id</t>
   </si>
@@ -503,9 +503,6 @@
     <t>V-700/V-800-07</t>
   </si>
   <si>
-    <t>-07</t>
-  </si>
-  <si>
     <t>E-70001</t>
   </si>
   <si>
@@ -804,6 +801,45 @@
   </si>
   <si>
     <t>S-6002</t>
+  </si>
+  <si>
+    <t>RI-153</t>
+  </si>
+  <si>
+    <t>R-150-01</t>
+  </si>
+  <si>
+    <t>R-150</t>
+  </si>
+  <si>
+    <t>AT-08</t>
+  </si>
+  <si>
+    <t>AT-09</t>
+  </si>
+  <si>
+    <t>AT-10</t>
+  </si>
+  <si>
+    <t>SS-800</t>
+  </si>
+  <si>
+    <t>SS-80001</t>
+  </si>
+  <si>
+    <t>SS-80102</t>
+  </si>
+  <si>
+    <t>SS-80203</t>
+  </si>
+  <si>
+    <t>SS800</t>
+  </si>
+  <si>
+    <t>SS801</t>
+  </si>
+  <si>
+    <t>SS802</t>
   </si>
 </sst>
 </file>
@@ -853,7 +889,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -876,11 +912,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -908,6 +957,13 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -1248,13 +1304,13 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O87"/>
+  <dimension ref="A1:AA91"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.88671875" style="1"/>
+    <col min="1" max="2" width="8.88671875" style="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.5546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="5.44140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.5546875" style="6" customWidth="1"/>
@@ -1268,7 +1324,7 @@
     <col min="16" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -1299,23 +1355,35 @@
       <c r="J1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="N1" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>0.45165189363416597</v>
       </c>
@@ -1323,14 +1391,14 @@
         <v>0.44729344729344728</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D2" s="3" t="str">
         <f>C2&amp;"-01"</f>
         <v>SS-700B-01</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>68</v>
@@ -1348,7 +1416,7 @@
         <v>84</v>
       </c>
       <c r="K2" s="3">
-        <f t="shared" ref="K2:K33" si="0">PI()*(((H2-2*I2)*10^-3)^2/4)</f>
+        <f t="shared" ref="K2:K36" si="0">PI()*(((H2-2*I2)*10^-3)^2/4)</f>
         <v>8.6590147514568668E-3</v>
       </c>
       <c r="L2" s="5"/>
@@ -1361,11 +1429,23 @@
         <v>8.6590147514568668E-3</v>
       </c>
       <c r="O2" s="3">
-        <f t="shared" ref="O2:O33" si="1">N2*3600</f>
+        <f t="shared" ref="O2:O36" si="1">N2*3600</f>
         <v>31.17245310524472</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>0.45568090249798548</v>
       </c>
@@ -1373,14 +1453,14 @@
         <v>0.44729344729344728</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D3" s="3" t="str">
         <f>C3&amp;"-02"</f>
         <v>SS-700B-02</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>68</v>
@@ -1403,19 +1483,31 @@
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="7">
-        <f t="shared" ref="M3:M66" si="2">IF(L3&gt;0, L3, 1)</f>
+        <f t="shared" ref="M3:M69" si="2">IF(L3&gt;0, L3, 1)</f>
         <v>1</v>
       </c>
       <c r="N3" s="3">
-        <f t="shared" ref="N3:N66" si="3">M3*K3</f>
+        <f t="shared" ref="N3:N69" si="3">M3*K3</f>
         <v>5.1402817537852556E-3</v>
       </c>
       <c r="O3" s="3">
         <f t="shared" si="1"/>
         <v>18.505014313626919</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>0.14101531023368252</v>
       </c>
@@ -1429,7 +1521,7 @@
         <v>89</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>3</v>
@@ -1465,8 +1557,20 @@
         <f t="shared" si="1"/>
         <v>213.63258243489281</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>0.14907332796132153</v>
       </c>
@@ -1480,7 +1584,7 @@
         <v>90</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>4</v>
@@ -1516,8 +1620,20 @@
         <f t="shared" si="1"/>
         <v>213.63258243489281</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>0.16035455278001612</v>
       </c>
@@ -1531,7 +1647,7 @@
         <v>91</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>5</v>
@@ -1567,8 +1683,20 @@
         <f t="shared" si="1"/>
         <v>213.63258243489281</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>0.16639806607574537</v>
       </c>
@@ -1582,7 +1710,7 @@
         <v>92</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>6</v>
@@ -1615,11 +1743,23 @@
         <v>6.7254701877651438E-2</v>
       </c>
       <c r="O7" s="3">
-        <f t="shared" si="1"/>
+        <f>N7*3600</f>
         <v>242.11692675954518</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>0.17324738114423852</v>
       </c>
@@ -1633,7 +1773,7 @@
         <v>93</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>7</v>
@@ -1669,8 +1809,20 @@
         <f t="shared" si="1"/>
         <v>242.11692675954518</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>0.19419822723609992</v>
       </c>
@@ -1684,7 +1836,7 @@
         <v>94</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>8</v>
@@ -1720,8 +1872,20 @@
         <f t="shared" si="1"/>
         <v>144.25094661837815</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>0.24174053182917002</v>
       </c>
@@ -1735,7 +1899,7 @@
         <v>95</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>9</v>
@@ -1771,174 +1935,220 @@
         <f t="shared" si="1"/>
         <v>766.2943219399798</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
-        <v>0.41982272360999195</v>
-      </c>
-      <c r="B11" s="3">
-        <v>0.44729344729344728</v>
-      </c>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>96</v>
+        <v>257</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>38</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H11" s="5">
-        <v>220</v>
-      </c>
-      <c r="I11" s="5"/>
+        <v>323</v>
+      </c>
+      <c r="I11" s="5">
+        <v>8</v>
+      </c>
       <c r="J11" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K11" s="3">
-        <f t="shared" si="0"/>
-        <v>3.8013271108436497E-2</v>
-      </c>
-      <c r="L11" s="5"/>
+        <f>PI()*(((H11-2*I11)*10^-3)^2/4)</f>
+        <v>7.4022991502046109E-2</v>
+      </c>
+      <c r="L11" s="5">
+        <v>2.48</v>
+      </c>
       <c r="M11" s="7">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(L11&gt;0, L11, 1)</f>
+        <v>2.48</v>
       </c>
       <c r="N11" s="3">
         <f t="shared" si="3"/>
-        <v>3.8013271108436497E-2</v>
+        <v>0.18357701892507436</v>
       </c>
       <c r="O11" s="3">
         <f t="shared" si="1"/>
-        <v>136.84777599037139</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <v>0.37389202256244963</v>
-      </c>
-      <c r="B12" s="3">
-        <v>0.42507122507122508</v>
-      </c>
+        <v>660.87726813026768</v>
+      </c>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="3">
-        <v>80</v>
+        <v>258</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>399</v>
       </c>
       <c r="H12" s="5">
-        <v>88.9</v>
+        <v>323</v>
       </c>
       <c r="I12" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K12" s="3">
         <f t="shared" si="0"/>
-        <v>5.1402817537852556E-3</v>
-      </c>
-      <c r="L12" s="5"/>
+        <v>7.4022991502046109E-2</v>
+      </c>
+      <c r="L12" s="5">
+        <v>2.2599999999999998</v>
+      </c>
       <c r="M12" s="7">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(L12&gt;0, L12, 1)</f>
+        <v>2.2599999999999998</v>
       </c>
       <c r="N12" s="3">
         <f t="shared" si="3"/>
-        <v>5.1402817537852556E-3</v>
+        <v>0.16729196079462419</v>
       </c>
       <c r="O12" s="3">
         <f t="shared" si="1"/>
-        <v>18.505014313626919</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
-        <v>0.37308622078968573</v>
-      </c>
-      <c r="B13" s="3">
-        <v>0.4774928774928775</v>
-      </c>
+        <v>602.25105886064705</v>
+      </c>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>101</v>
+        <v>259</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+        <v>259</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>250</v>
+      </c>
+      <c r="H13" s="5">
+        <v>273</v>
+      </c>
+      <c r="I13" s="5">
+        <v>8</v>
+      </c>
       <c r="J13" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K13" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5.1874763294238062E-2</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="7">
-        <f t="shared" si="2"/>
+        <f>IF(L13&gt;0, L13, 1)</f>
         <v>1</v>
       </c>
       <c r="N13" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.1874763294238062E-2</v>
       </c>
       <c r="O13" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+        <v>186.74914785925702</v>
+      </c>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>0.35535858178887991</v>
+        <v>0.41982272360999195</v>
       </c>
       <c r="B14" s="3">
-        <v>0.48148148148148145</v>
+        <v>0.44729344729344728</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>73</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="5"/>
+        <v>38</v>
+      </c>
+      <c r="G14" s="3">
+        <v>200</v>
+      </c>
+      <c r="H14" s="5">
+        <v>220</v>
+      </c>
       <c r="I14" s="5"/>
       <c r="J14" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K14" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.8013271108436497E-2</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="7">
@@ -1947,47 +2157,59 @@
       </c>
       <c r="N14" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.8013271108436497E-2</v>
       </c>
       <c r="O14" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+        <v>136.84777599037139</v>
+      </c>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>0.32755842062852536</v>
+        <v>0.37389202256244963</v>
       </c>
       <c r="B15" s="3">
-        <v>0.53276353276353272</v>
+        <v>0.42507122507122508</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>73</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H15" s="5">
-        <v>114</v>
+        <v>88.9</v>
       </c>
       <c r="I15" s="5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K15" s="3">
         <f t="shared" si="0"/>
-        <v>8.6590147514568668E-3</v>
+        <v>5.1402817537852556E-3</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="7">
@@ -1996,47 +2218,53 @@
       </c>
       <c r="N15" s="3">
         <f t="shared" si="3"/>
-        <v>8.6590147514568668E-3</v>
+        <v>5.1402817537852556E-3</v>
       </c>
       <c r="O15" s="3">
         <f t="shared" si="1"/>
-        <v>31.17245310524472</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18.505014313626919</v>
+      </c>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>0.32997582594681707</v>
+        <v>0.37308622078968573</v>
       </c>
       <c r="B16" s="3">
-        <v>0.55999999999999994</v>
+        <v>0.4774928774928775</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>73</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="3">
-        <v>65</v>
-      </c>
-      <c r="H16" s="5">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="I16" s="5">
-        <v>3.6</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
       <c r="J16" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K16" s="3">
         <f t="shared" si="0"/>
-        <v>3.728450015261999E-3</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="7">
@@ -2045,47 +2273,53 @@
       </c>
       <c r="N16" s="3">
         <f t="shared" si="3"/>
-        <v>3.728450015261999E-3</v>
+        <v>0</v>
       </c>
       <c r="O16" s="3">
         <f t="shared" si="1"/>
-        <v>13.422420054943197</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>0.33037872683319902</v>
+        <v>0.35535858178887991</v>
       </c>
       <c r="B17" s="3">
-        <v>0.57948717948717954</v>
+        <v>0.48148148148148145</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>73</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" s="3">
-        <v>80</v>
-      </c>
-      <c r="H17" s="5">
-        <v>88.9</v>
-      </c>
-      <c r="I17" s="5">
-        <v>4</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
       <c r="J17" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K17" s="3">
         <f t="shared" si="0"/>
-        <v>5.1402817537852556E-3</v>
+        <v>0</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="7">
@@ -2094,47 +2328,59 @@
       </c>
       <c r="N17" s="3">
         <f t="shared" si="3"/>
-        <v>5.1402817537852556E-3</v>
+        <v>0</v>
       </c>
       <c r="O17" s="3">
         <f t="shared" si="1"/>
-        <v>18.505014313626919</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="3"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3"/>
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>0.4323126510878324</v>
+        <v>0.32755842062852536</v>
       </c>
       <c r="B18" s="3">
-        <v>0.61595441595441591</v>
+        <v>0.53276353276353272</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>73</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G18" s="3">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H18" s="5">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="I18" s="5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K18" s="3">
         <f t="shared" si="0"/>
-        <v>1.3478217882063612E-2</v>
+        <v>8.6590147514568668E-3</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="7">
@@ -2143,82 +2389,104 @@
       </c>
       <c r="N18" s="3">
         <f t="shared" si="3"/>
-        <v>1.3478217882063612E-2</v>
+        <v>8.6590147514568668E-3</v>
       </c>
       <c r="O18" s="3">
         <f t="shared" si="1"/>
-        <v>48.521584375429001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+        <v>31.17245310524472</v>
+      </c>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>0.61039484286865431</v>
+        <v>0.32997582594681707</v>
       </c>
       <c r="B19" s="3">
-        <v>0.51908831908831909</v>
+        <v>0.55999999999999994</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G19" s="3">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="H19" s="5">
-        <v>155</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="I19" s="5">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K19" s="3">
         <f t="shared" si="0"/>
-        <v>1.8002865285469776E-2</v>
-      </c>
-      <c r="L19" s="5">
-        <v>0.7</v>
-      </c>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L19" s="5"/>
       <c r="M19" s="7">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="N19" s="3">
         <f t="shared" si="3"/>
-        <v>1.2602005699828842E-2</v>
+        <v>3.728450015261999E-3</v>
       </c>
       <c r="O19" s="3">
         <f t="shared" si="1"/>
-        <v>45.367220519383828</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+        <v>13.422420054943197</v>
+      </c>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>0.60596293311845284</v>
+        <v>0.33037872683319902</v>
       </c>
       <c r="B20" s="3">
-        <v>0.55099715099715096</v>
+        <v>0.57948717948717954</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G20" s="3">
         <v>80</v>
@@ -2227,155 +2495,189 @@
         <v>88.9</v>
       </c>
       <c r="I20" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K20" s="3">
         <f t="shared" si="0"/>
-        <v>5.661157815750442E-3</v>
-      </c>
-      <c r="L20" s="5">
-        <v>0.5</v>
-      </c>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="L20" s="5"/>
       <c r="M20" s="7">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N20" s="3">
         <f t="shared" si="3"/>
-        <v>2.830578907875221E-3</v>
+        <v>5.1402817537852556E-3</v>
       </c>
       <c r="O20" s="3">
         <f t="shared" si="1"/>
-        <v>10.190084068350796</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18.505014313626919</v>
+      </c>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>0.61442385173247382</v>
+        <v>0.4323126510878324</v>
       </c>
       <c r="B21" s="3">
-        <v>0.54245014245014245</v>
+        <v>0.61595441595441591</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G21" s="3">
         <v>125</v>
       </c>
       <c r="H21" s="5">
-        <v>139.69999999999999</v>
+        <v>141</v>
       </c>
       <c r="I21" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K21" s="3">
         <f t="shared" si="0"/>
-        <v>1.4462706625900674E-2</v>
-      </c>
-      <c r="L21" s="5">
-        <v>0.62</v>
-      </c>
+        <v>1.3478217882063612E-2</v>
+      </c>
+      <c r="L21" s="5"/>
       <c r="M21" s="7">
         <f t="shared" si="2"/>
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="N21" s="3">
         <f t="shared" si="3"/>
-        <v>8.9668781080584174E-3</v>
+        <v>1.3478217882063612E-2</v>
       </c>
       <c r="O21" s="3">
         <f t="shared" si="1"/>
-        <v>32.280761189010306</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <v>48.521584375429001</v>
+      </c>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>0.45165189363416597</v>
+        <v>0.61039484286865431</v>
       </c>
       <c r="B22" s="3">
-        <v>0.47122507122507123</v>
+        <v>0.51908831908831909</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G22" s="3">
-        <v>204</v>
+        <v>155</v>
       </c>
       <c r="H22" s="5">
-        <v>204</v>
+        <v>155</v>
       </c>
       <c r="I22" s="5">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>85</v>
       </c>
       <c r="K22" s="3">
         <f t="shared" si="0"/>
-        <v>3.1415926535897934E-2</v>
-      </c>
-      <c r="L22" s="5"/>
+        <v>1.8002865285469776E-2</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0.7</v>
+      </c>
       <c r="M22" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="N22" s="3">
         <f t="shared" si="3"/>
-        <v>3.1415926535897934E-2</v>
+        <v>1.2602005699828842E-2</v>
       </c>
       <c r="O22" s="3">
         <f t="shared" si="1"/>
-        <v>113.09733552923257</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <v>45.367220519383828</v>
+      </c>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>0.54754230459307007</v>
+        <v>0.60596293311845284</v>
       </c>
       <c r="B23" s="3">
-        <v>0.54472934472934476</v>
+        <v>0.55099715099715096</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G23" s="3">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="H23" s="5">
-        <v>204</v>
+        <v>88.9</v>
       </c>
       <c r="I23" s="5">
         <v>2</v>
@@ -2385,48 +2687,60 @@
       </c>
       <c r="K23" s="3">
         <f t="shared" si="0"/>
-        <v>3.1415926535897934E-2</v>
+        <v>5.661157815750442E-3</v>
       </c>
       <c r="L23" s="5">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M23" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="N23" s="3">
         <f t="shared" si="3"/>
-        <v>6.2831853071795868E-2</v>
+        <v>2.830578907875221E-3</v>
       </c>
       <c r="O23" s="3">
         <f t="shared" si="1"/>
-        <v>226.19467105846513</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <v>10.190084068350796</v>
+      </c>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>0.54754230459307007</v>
+        <v>0.61442385173247382</v>
       </c>
       <c r="B24" s="3">
-        <v>0.63133903133903135</v>
+        <v>0.54245014245014245</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G24" s="3">
-        <v>204</v>
+        <v>125</v>
       </c>
       <c r="H24" s="5">
-        <v>204</v>
+        <v>139.69999999999999</v>
       </c>
       <c r="I24" s="5">
         <v>2</v>
@@ -2436,48 +2750,60 @@
       </c>
       <c r="K24" s="3">
         <f t="shared" si="0"/>
-        <v>3.1415926535897934E-2</v>
+        <v>1.4462706625900674E-2</v>
       </c>
       <c r="L24" s="5">
-        <v>1.8</v>
+        <v>0.62</v>
       </c>
       <c r="M24" s="7">
         <f t="shared" si="2"/>
-        <v>1.8</v>
+        <v>0.62</v>
       </c>
       <c r="N24" s="3">
         <f t="shared" si="3"/>
-        <v>5.6548667764616284E-2</v>
+        <v>8.9668781080584174E-3</v>
       </c>
       <c r="O24" s="3">
         <f t="shared" si="1"/>
-        <v>203.57520395261861</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <v>32.280761189010306</v>
+      </c>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>0.54754230459307007</v>
+        <v>0.45165189363416597</v>
       </c>
       <c r="B25" s="3">
-        <v>0.66267806267806273</v>
+        <v>0.47122507122507123</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G25" s="3">
-        <v>155</v>
+        <v>204</v>
       </c>
       <c r="H25" s="5">
-        <v>154</v>
+        <v>204</v>
       </c>
       <c r="I25" s="5">
         <v>2</v>
@@ -2487,48 +2813,58 @@
       </c>
       <c r="K25" s="3">
         <f t="shared" si="0"/>
-        <v>1.7671458676442587E-2</v>
-      </c>
-      <c r="L25" s="5">
-        <v>2.8</v>
-      </c>
+        <v>3.1415926535897934E-2</v>
+      </c>
+      <c r="L25" s="5"/>
       <c r="M25" s="7">
         <f t="shared" si="2"/>
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="N25" s="3">
         <f t="shared" si="3"/>
-        <v>4.9480084294039238E-2</v>
+        <v>3.1415926535897934E-2</v>
       </c>
       <c r="O25" s="3">
         <f t="shared" si="1"/>
-        <v>178.12830345854127</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <v>113.09733552923257</v>
+      </c>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>0.54754230459307007</v>
       </c>
       <c r="B26" s="3">
-        <v>0.69971509971509971</v>
+        <v>0.54472934472934476</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G26" s="3">
-        <v>155</v>
+        <v>204</v>
       </c>
       <c r="H26" s="5">
-        <v>154</v>
+        <v>204</v>
       </c>
       <c r="I26" s="5">
         <v>2</v>
@@ -2538,48 +2874,60 @@
       </c>
       <c r="K26" s="3">
         <f t="shared" si="0"/>
-        <v>1.7671458676442587E-2</v>
+        <v>3.1415926535897934E-2</v>
       </c>
       <c r="L26" s="5">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M26" s="7">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N26" s="3">
         <f t="shared" si="3"/>
-        <v>4.4178646691106466E-2</v>
+        <v>6.2831853071795868E-2</v>
       </c>
       <c r="O26" s="3">
         <f t="shared" si="1"/>
-        <v>159.04312808798326</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+        <v>226.19467105846513</v>
+      </c>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>0.5398871877518131</v>
+        <v>0.54754230459307007</v>
       </c>
       <c r="B27" s="3">
-        <v>0.5196581196581197</v>
+        <v>0.63133903133903135</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G27" s="3">
-        <v>80</v>
+        <v>204</v>
       </c>
       <c r="H27" s="5">
-        <v>88.9</v>
+        <v>204</v>
       </c>
       <c r="I27" s="5">
         <v>2</v>
@@ -2589,46 +2937,60 @@
       </c>
       <c r="K27" s="3">
         <f t="shared" si="0"/>
-        <v>5.661157815750442E-3</v>
-      </c>
-      <c r="L27" s="5"/>
+        <v>3.1415926535897934E-2</v>
+      </c>
+      <c r="L27" s="5">
+        <v>1.8</v>
+      </c>
       <c r="M27" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="N27" s="3">
         <f t="shared" si="3"/>
-        <v>5.661157815750442E-3</v>
+        <v>5.6548667764616284E-2</v>
       </c>
       <c r="O27" s="3">
         <f t="shared" si="1"/>
-        <v>20.380168136701592</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+        <v>203.57520395261861</v>
+      </c>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="3"/>
+      <c r="Y27" s="3"/>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
-        <v>0.53867848509266725</v>
+        <v>0.54754230459307007</v>
       </c>
       <c r="B28" s="3">
-        <v>0.57150997150997151</v>
+        <v>0.66267806267806273</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G28" s="3">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="H28" s="5">
-        <v>88.9</v>
+        <v>154</v>
       </c>
       <c r="I28" s="5">
         <v>2</v>
@@ -2638,46 +3000,60 @@
       </c>
       <c r="K28" s="3">
         <f t="shared" si="0"/>
-        <v>5.661157815750442E-3</v>
-      </c>
-      <c r="L28" s="5"/>
+        <v>1.7671458676442587E-2</v>
+      </c>
+      <c r="L28" s="5">
+        <v>2.8</v>
+      </c>
       <c r="M28" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="N28" s="3">
         <f t="shared" si="3"/>
-        <v>5.661157815750442E-3</v>
+        <v>4.9480084294039238E-2</v>
       </c>
       <c r="O28" s="3">
         <f t="shared" si="1"/>
-        <v>20.380168136701592</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <v>178.12830345854127</v>
+      </c>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>0.5423045930701047</v>
+        <v>0.54754230459307007</v>
       </c>
       <c r="B29" s="3">
-        <v>0.71794871794871795</v>
+        <v>0.69971509971509971</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>171</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G29" s="3">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="H29" s="5">
-        <v>139.69999999999999</v>
+        <v>154</v>
       </c>
       <c r="I29" s="5">
         <v>2</v>
@@ -2687,48 +3063,60 @@
       </c>
       <c r="K29" s="3">
         <f t="shared" si="0"/>
-        <v>1.4462706625900674E-2</v>
+        <v>1.7671458676442587E-2</v>
       </c>
       <c r="L29" s="5">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="M29" s="7">
         <f t="shared" si="2"/>
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="N29" s="3">
         <f t="shared" si="3"/>
-        <v>2.6032871926621213E-2</v>
+        <v>4.4178646691106466E-2</v>
       </c>
       <c r="O29" s="3">
         <f t="shared" si="1"/>
-        <v>93.718338935836371</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>159.04312808798326</v>
+      </c>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="3"/>
+      <c r="Y29" s="3"/>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
-        <v>0.5423045930701047</v>
+        <v>0.5398871877518131</v>
       </c>
       <c r="B30" s="3">
-        <v>0.67635327635327636</v>
+        <v>0.5196581196581197</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G30" s="3">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="H30" s="5">
-        <v>139.69999999999999</v>
+        <v>88.9</v>
       </c>
       <c r="I30" s="5">
         <v>2</v>
@@ -2738,48 +3126,58 @@
       </c>
       <c r="K30" s="3">
         <f t="shared" si="0"/>
-        <v>1.4462706625900674E-2</v>
-      </c>
-      <c r="L30" s="5">
-        <v>0.9</v>
-      </c>
+        <v>5.661157815750442E-3</v>
+      </c>
+      <c r="L30" s="5"/>
       <c r="M30" s="7">
         <f t="shared" si="2"/>
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N30" s="3">
         <f t="shared" si="3"/>
-        <v>1.3016435963310606E-2</v>
+        <v>5.661157815750442E-3</v>
       </c>
       <c r="O30" s="3">
         <f t="shared" si="1"/>
-        <v>46.859169467918186</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>20.380168136701592</v>
+      </c>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <v>0.42264302981466562</v>
+        <v>0.53867848509266725</v>
       </c>
       <c r="B31" s="3">
-        <v>0.52022792022792019</v>
+        <v>0.57150997150997151</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" s="3">
         <v>80</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G31" s="3">
-        <v>204</v>
-      </c>
       <c r="H31" s="5">
-        <v>204</v>
+        <v>88.9</v>
       </c>
       <c r="I31" s="5">
         <v>2</v>
@@ -2789,7 +3187,7 @@
       </c>
       <c r="K31" s="3">
         <f t="shared" si="0"/>
-        <v>3.1415926535897934E-2</v>
+        <v>5.661157815750442E-3</v>
       </c>
       <c r="L31" s="5"/>
       <c r="M31" s="7">
@@ -2798,37 +3196,49 @@
       </c>
       <c r="N31" s="3">
         <f t="shared" si="3"/>
-        <v>3.1415926535897934E-2</v>
+        <v>5.661157815750442E-3</v>
       </c>
       <c r="O31" s="3">
         <f t="shared" si="1"/>
-        <v>113.09733552923257</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+        <v>20.380168136701592</v>
+      </c>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+      <c r="X31" s="3"/>
+      <c r="Y31" s="3"/>
+      <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <v>0.41257050765511682</v>
+        <v>0.5423045930701047</v>
       </c>
       <c r="B32" s="3">
-        <v>0.6541310541310541</v>
+        <v>0.71794871794871795</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G32" s="3">
-        <v>204</v>
+        <v>125</v>
       </c>
       <c r="H32" s="5">
-        <v>204</v>
+        <v>139.69999999999999</v>
       </c>
       <c r="I32" s="5">
         <v>2</v>
@@ -2838,46 +3248,60 @@
       </c>
       <c r="K32" s="3">
         <f t="shared" si="0"/>
-        <v>3.1415926535897934E-2</v>
-      </c>
-      <c r="L32" s="5"/>
+        <v>1.4462706625900674E-2</v>
+      </c>
+      <c r="L32" s="5">
+        <v>1.8</v>
+      </c>
       <c r="M32" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="N32" s="3">
         <f t="shared" si="3"/>
-        <v>3.1415926535897934E-2</v>
+        <v>2.6032871926621213E-2</v>
       </c>
       <c r="O32" s="3">
         <f t="shared" si="1"/>
-        <v>113.09733552923257</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+        <v>93.718338935836371</v>
+      </c>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
-        <v>0.41257050765511682</v>
+        <v>0.5423045930701047</v>
       </c>
       <c r="B33" s="3">
-        <v>0.70256410256410251</v>
+        <v>0.67635327635327636</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G33" s="3">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="H33" s="5">
-        <v>114</v>
+        <v>139.69999999999999</v>
       </c>
       <c r="I33" s="5">
         <v>2</v>
@@ -2887,46 +3311,60 @@
       </c>
       <c r="K33" s="3">
         <f t="shared" si="0"/>
-        <v>9.5033177771091243E-3</v>
-      </c>
-      <c r="L33" s="5"/>
+        <v>1.4462706625900674E-2</v>
+      </c>
+      <c r="L33" s="5">
+        <v>0.9</v>
+      </c>
       <c r="M33" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N33" s="3">
         <f t="shared" si="3"/>
-        <v>9.5033177771091243E-3</v>
+        <v>1.3016435963310606E-2</v>
       </c>
       <c r="O33" s="3">
         <f t="shared" si="1"/>
-        <v>34.211943997592847</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+        <v>46.859169467918186</v>
+      </c>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="3"/>
+      <c r="X33" s="3"/>
+      <c r="Y33" s="3"/>
+      <c r="Z33" s="3"/>
+      <c r="AA33" s="3"/>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
-        <v>0</v>
+        <v>0.42264302981466562</v>
       </c>
       <c r="B34" s="3">
-        <v>0</v>
+        <v>0.52022792022792019</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>80</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G34" s="3">
-        <v>129</v>
+        <v>204</v>
       </c>
       <c r="H34" s="5">
-        <v>129</v>
+        <v>204</v>
       </c>
       <c r="I34" s="5">
         <v>2</v>
@@ -2935,8 +3373,8 @@
         <v>85</v>
       </c>
       <c r="K34" s="3">
-        <f t="shared" ref="K34:K65" si="4">PI()*(((H34-2*I34)*10^-3)^2/4)</f>
-        <v>1.2271846303085129E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.1415926535897934E-2</v>
       </c>
       <c r="L34" s="5"/>
       <c r="M34" s="7">
@@ -2945,37 +3383,49 @@
       </c>
       <c r="N34" s="3">
         <f t="shared" si="3"/>
-        <v>1.2271846303085129E-2</v>
+        <v>3.1415926535897934E-2</v>
       </c>
       <c r="O34" s="3">
-        <f t="shared" ref="O34:O65" si="5">N34*3600</f>
-        <v>44.178646691106465</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>113.09733552923257</v>
+      </c>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+      <c r="Z34" s="3"/>
+      <c r="AA34" s="3"/>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <v>0.41095890410958902</v>
+        <v>0.41257050765511682</v>
       </c>
       <c r="B35" s="3">
-        <v>0.66894586894586894</v>
+        <v>0.6541310541310541</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>80</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>177</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G35" s="3">
-        <v>129</v>
+        <v>204</v>
       </c>
       <c r="H35" s="5">
-        <v>129</v>
+        <v>204</v>
       </c>
       <c r="I35" s="5">
         <v>2</v>
@@ -2984,8 +3434,8 @@
         <v>85</v>
       </c>
       <c r="K35" s="3">
-        <f t="shared" si="4"/>
-        <v>1.2271846303085129E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.1415926535897934E-2</v>
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="7">
@@ -2994,47 +3444,59 @@
       </c>
       <c r="N35" s="3">
         <f t="shared" si="3"/>
-        <v>1.2271846303085129E-2</v>
+        <v>3.1415926535897934E-2</v>
       </c>
       <c r="O35" s="3">
-        <f t="shared" si="5"/>
-        <v>44.178646691106465</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>113.09733552923257</v>
+      </c>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
+      <c r="V35" s="3"/>
+      <c r="W35" s="3"/>
+      <c r="X35" s="3"/>
+      <c r="Y35" s="3"/>
+      <c r="Z35" s="3"/>
+      <c r="AA35" s="3"/>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
-        <v>0.37590652699435939</v>
+        <v>0.41257050765511682</v>
       </c>
       <c r="B36" s="3">
-        <v>0.68603988603988608</v>
+        <v>0.70256410256410251</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G36" s="3">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="H36" s="5">
-        <v>76.099999999999994</v>
+        <v>114</v>
       </c>
       <c r="I36" s="5">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K36" s="3">
-        <f t="shared" si="4"/>
-        <v>3.728450015261999E-3</v>
+        <f t="shared" si="0"/>
+        <v>9.5033177771091243E-3</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="7">
@@ -3043,47 +3505,59 @@
       </c>
       <c r="N36" s="3">
         <f t="shared" si="3"/>
-        <v>3.728450015261999E-3</v>
+        <v>9.5033177771091243E-3</v>
       </c>
       <c r="O36" s="3">
-        <f t="shared" si="5"/>
-        <v>13.422420054943197</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>34.211943997592847</v>
+      </c>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3"/>
+      <c r="W36" s="3"/>
+      <c r="X36" s="3"/>
+      <c r="Y36" s="3"/>
+      <c r="Z36" s="3"/>
+      <c r="AA36" s="3"/>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
-        <v>0.37187751813053987</v>
+        <v>0</v>
       </c>
       <c r="B37" s="3">
-        <v>0.73618233618233619</v>
+        <v>0</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G37" s="3">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="H37" s="5">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="I37" s="5">
         <v>2</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K37" s="3">
-        <f t="shared" si="4"/>
-        <v>1.1945906065275189E-3</v>
+        <f t="shared" ref="K37:K68" si="4">PI()*(((H37-2*I37)*10^-3)^2/4)</f>
+        <v>1.2271846303085129E-2</v>
       </c>
       <c r="L37" s="5"/>
       <c r="M37" s="7">
@@ -3092,47 +3566,59 @@
       </c>
       <c r="N37" s="3">
         <f t="shared" si="3"/>
-        <v>1.1945906065275189E-3</v>
+        <v>1.2271846303085129E-2</v>
       </c>
       <c r="O37" s="3">
-        <f t="shared" si="5"/>
-        <v>4.300526183499068</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" ref="O37:O68" si="5">N37*3600</f>
+        <v>44.178646691106465</v>
+      </c>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3"/>
+      <c r="S37" s="3"/>
+      <c r="T37" s="3"/>
+      <c r="U37" s="3"/>
+      <c r="V37" s="3"/>
+      <c r="W37" s="3"/>
+      <c r="X37" s="3"/>
+      <c r="Y37" s="3"/>
+      <c r="Z37" s="3"/>
+      <c r="AA37" s="3"/>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
-        <v>0.31345688960515711</v>
+        <v>0.41095890410958902</v>
       </c>
       <c r="B38" s="3">
-        <v>0.73219373219373218</v>
+        <v>0.66894586894586894</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G38" s="3">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="H38" s="5">
-        <v>60.3</v>
+        <v>129</v>
       </c>
       <c r="I38" s="5">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K38" s="3">
         <f t="shared" si="4"/>
-        <v>2.2145165154970788E-3</v>
+        <v>1.2271846303085129E-2</v>
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="7">
@@ -3141,47 +3627,59 @@
       </c>
       <c r="N38" s="3">
         <f t="shared" si="3"/>
-        <v>2.2145165154970788E-3</v>
+        <v>1.2271846303085129E-2</v>
       </c>
       <c r="O38" s="3">
         <f t="shared" si="5"/>
-        <v>7.9722594557894837</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+        <v>44.178646691106465</v>
+      </c>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3"/>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
-        <v>0.37308622078968573</v>
+        <v>0.37590652699435939</v>
       </c>
       <c r="B39" s="3">
-        <v>0.62222222222222223</v>
+        <v>0.68603988603988608</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G39" s="3">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="H39" s="5">
-        <v>139</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="I39" s="5">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K39" s="3">
         <f t="shared" si="4"/>
-        <v>1.3069810837096936E-2</v>
+        <v>3.728450015261999E-3</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="7">
@@ -3190,47 +3688,59 @@
       </c>
       <c r="N39" s="3">
         <f t="shared" si="3"/>
-        <v>1.3069810837096936E-2</v>
+        <v>3.728450015261999E-3</v>
       </c>
       <c r="O39" s="3">
         <f t="shared" si="5"/>
-        <v>47.051319013548969</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+        <v>13.422420054943197</v>
+      </c>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <v>0.33158742949234488</v>
+        <v>0.37187751813053987</v>
       </c>
       <c r="B40" s="3">
-        <v>0.62279202279202284</v>
+        <v>0.73618233618233619</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G40" s="3">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="H40" s="5">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="I40" s="5">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K40" s="3">
         <f t="shared" si="4"/>
-        <v>8.6590147514568668E-3</v>
+        <v>1.1945906065275189E-3</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="7">
@@ -3239,31 +3749,43 @@
       </c>
       <c r="N40" s="3">
         <f t="shared" si="3"/>
-        <v>8.6590147514568668E-3</v>
+        <v>1.1945906065275189E-3</v>
       </c>
       <c r="O40" s="3">
         <f t="shared" si="5"/>
-        <v>31.17245310524472</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4.300526183499068</v>
+      </c>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <v>0.35777598710717162</v>
+        <v>0.31345688960515711</v>
       </c>
       <c r="B41" s="3">
-        <v>0.63190883190883196</v>
+        <v>0.73219373219373218</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G41" s="3">
         <v>50</v>
@@ -3294,41 +3816,53 @@
         <f t="shared" si="5"/>
         <v>7.9722594557894837</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
+      <c r="W41" s="3"/>
+      <c r="X41" s="3"/>
+      <c r="Y41" s="3"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <v>0.56003223207091057</v>
+        <v>0.37308622078968573</v>
       </c>
       <c r="B42" s="3">
-        <v>0.71111111111111114</v>
+        <v>0.62222222222222223</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="G42" s="3">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="H42" s="5">
-        <v>88.9</v>
+        <v>139</v>
       </c>
       <c r="I42" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K42" s="3">
         <f t="shared" si="4"/>
-        <v>5.1402817537852556E-3</v>
+        <v>1.3069810837096936E-2</v>
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="7">
@@ -3337,47 +3871,59 @@
       </c>
       <c r="N42" s="3">
         <f t="shared" si="3"/>
-        <v>5.1402817537852556E-3</v>
+        <v>1.3069810837096936E-2</v>
       </c>
       <c r="O42" s="3">
         <f t="shared" si="5"/>
-        <v>18.505014313626919</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+        <v>47.051319013548969</v>
+      </c>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3"/>
+      <c r="S42" s="3"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+      <c r="Z42" s="3"/>
+      <c r="AA42" s="3"/>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
-        <v>0.57050765511684121</v>
+        <v>0.33158742949234488</v>
       </c>
       <c r="B43" s="3">
-        <v>0.66951566951566954</v>
+        <v>0.62279202279202284</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G43" s="3">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="H43" s="5">
-        <v>48.3</v>
+        <v>114</v>
       </c>
       <c r="I43" s="5">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K43" s="3">
         <f t="shared" si="4"/>
-        <v>1.378852869642194E-3</v>
+        <v>8.6590147514568668E-3</v>
       </c>
       <c r="L43" s="5"/>
       <c r="M43" s="7">
@@ -3386,31 +3932,43 @@
       </c>
       <c r="N43" s="3">
         <f t="shared" si="3"/>
-        <v>1.378852869642194E-3</v>
+        <v>8.6590147514568668E-3</v>
       </c>
       <c r="O43" s="3">
         <f t="shared" si="5"/>
-        <v>4.9638703307118988</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+        <v>31.17245310524472</v>
+      </c>
+      <c r="P43" s="3"/>
+      <c r="Q43" s="3"/>
+      <c r="R43" s="3"/>
+      <c r="S43" s="3"/>
+      <c r="T43" s="3"/>
+      <c r="U43" s="3"/>
+      <c r="V43" s="3"/>
+      <c r="W43" s="3"/>
+      <c r="X43" s="3"/>
+      <c r="Y43" s="3"/>
+      <c r="Z43" s="3"/>
+      <c r="AA43" s="3"/>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <v>0.58581788879935537</v>
+        <v>0.35777598710717162</v>
       </c>
       <c r="B44" s="3">
-        <v>0.64387464387464388</v>
+        <v>0.63190883190883196</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="G44" s="3">
         <v>50</v>
@@ -3441,41 +3999,53 @@
         <f t="shared" si="5"/>
         <v>7.9722594557894837</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="3"/>
+      <c r="S44" s="3"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="3"/>
+      <c r="X44" s="3"/>
+      <c r="Y44" s="3"/>
+      <c r="Z44" s="3"/>
+      <c r="AA44" s="3"/>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
-        <v>0.63416599516518934</v>
+        <v>0.56003223207091057</v>
       </c>
       <c r="B45" s="3">
-        <v>0.65527065527065531</v>
+        <v>0.71111111111111114</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>78</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G45" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H45" s="5">
-        <v>60.3</v>
+        <v>88.9</v>
       </c>
       <c r="I45" s="5">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K45" s="3">
         <f t="shared" si="4"/>
-        <v>2.2145165154970788E-3</v>
+        <v>5.1402817537852556E-3</v>
       </c>
       <c r="L45" s="5"/>
       <c r="M45" s="7">
@@ -3484,31 +4054,43 @@
       </c>
       <c r="N45" s="3">
         <f t="shared" si="3"/>
-        <v>2.2145165154970788E-3</v>
+        <v>5.1402817537852556E-3</v>
       </c>
       <c r="O45" s="3">
         <f t="shared" si="5"/>
-        <v>7.9722594557894837</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18.505014313626919</v>
+      </c>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="3"/>
+      <c r="S45" s="3"/>
+      <c r="T45" s="3"/>
+      <c r="U45" s="3"/>
+      <c r="V45" s="3"/>
+      <c r="W45" s="3"/>
+      <c r="X45" s="3"/>
+      <c r="Y45" s="3"/>
+      <c r="Z45" s="3"/>
+      <c r="AA45" s="3"/>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <v>0.65632554391619657</v>
+        <v>0.57050765511684121</v>
       </c>
       <c r="B46" s="3">
-        <v>0.64501424501424498</v>
+        <v>0.66951566951566954</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>78</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G46" s="3">
         <v>40</v>
@@ -3539,25 +4121,37 @@
         <f t="shared" si="5"/>
         <v>4.9638703307118988</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="3"/>
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="3"/>
+      <c r="X46" s="3"/>
+      <c r="Y46" s="3"/>
+      <c r="Z46" s="3"/>
+      <c r="AA46" s="3"/>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <v>0.49717969379532634</v>
+        <v>0.58581788879935537</v>
       </c>
       <c r="B47" s="3">
-        <v>0.72421652421652427</v>
+        <v>0.64387464387464388</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G47" s="3">
         <v>50</v>
@@ -3588,25 +4182,37 @@
         <f t="shared" si="5"/>
         <v>7.9722594557894837</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P47" s="3"/>
+      <c r="Q47" s="3"/>
+      <c r="R47" s="3"/>
+      <c r="S47" s="3"/>
+      <c r="T47" s="3"/>
+      <c r="U47" s="3"/>
+      <c r="V47" s="3"/>
+      <c r="W47" s="3"/>
+      <c r="X47" s="3"/>
+      <c r="Y47" s="3"/>
+      <c r="Z47" s="3"/>
+      <c r="AA47" s="3"/>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <v>0.49033037872683322</v>
+        <v>0.63416599516518934</v>
       </c>
       <c r="B48" s="3">
-        <v>0.70484330484330482</v>
+        <v>0.65527065527065531</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G48" s="3">
         <v>50</v>
@@ -3637,41 +4243,53 @@
         <f t="shared" si="5"/>
         <v>7.9722594557894837</v>
       </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+      <c r="S48" s="3"/>
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="V48" s="3"/>
+      <c r="W48" s="3"/>
+      <c r="X48" s="3"/>
+      <c r="Y48" s="3"/>
+      <c r="Z48" s="3"/>
+      <c r="AA48" s="3"/>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>0.48992747784045126</v>
+        <v>0.65632554391619657</v>
       </c>
       <c r="B49" s="3">
-        <v>0.67464387464387465</v>
+        <v>0.64501424501424498</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G49" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H49" s="5">
-        <v>60.3</v>
+        <v>48.3</v>
       </c>
       <c r="I49" s="5">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K49" s="3">
         <f t="shared" si="4"/>
-        <v>2.2145165154970788E-3</v>
+        <v>1.378852869642194E-3</v>
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="7">
@@ -3680,394 +4298,490 @@
       </c>
       <c r="N49" s="3">
         <f t="shared" si="3"/>
-        <v>2.2145165154970788E-3</v>
+        <v>1.378852869642194E-3</v>
       </c>
       <c r="O49" s="3">
         <f t="shared" si="5"/>
-        <v>7.9722594557894837</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4.9638703307118988</v>
+      </c>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="3"/>
+      <c r="S49" s="3"/>
+      <c r="T49" s="3"/>
+      <c r="U49" s="3"/>
+      <c r="V49" s="3"/>
+      <c r="W49" s="3"/>
+      <c r="X49" s="3"/>
+      <c r="Y49" s="3"/>
+      <c r="Z49" s="3"/>
+      <c r="AA49" s="3"/>
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <v>0.60032232070910552</v>
+        <v>0.49717969379532634</v>
       </c>
       <c r="B50" s="3">
-        <v>0.17720797720797721</v>
+        <v>0.72421652421652427</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G50" s="3">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H50" s="5">
-        <v>220</v>
-      </c>
-      <c r="I50" s="5"/>
+        <v>60.3</v>
+      </c>
+      <c r="I50" s="5">
+        <v>3.6</v>
+      </c>
       <c r="J50" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K50" s="3">
         <f t="shared" si="4"/>
-        <v>3.8013271108436497E-2</v>
-      </c>
-      <c r="L50" s="5">
-        <v>0.9</v>
-      </c>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L50" s="5"/>
       <c r="M50" s="7">
         <f t="shared" si="2"/>
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N50" s="3">
         <f t="shared" si="3"/>
-        <v>3.421194399759285E-2</v>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="O50" s="3">
         <f t="shared" si="5"/>
-        <v>123.16299839133426</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3"/>
+      <c r="S50" s="3"/>
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="3"/>
+      <c r="X50" s="3"/>
+      <c r="Y50" s="3"/>
+      <c r="Z50" s="3"/>
+      <c r="AA50" s="3"/>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
-        <v>0.62570507655116836</v>
+        <v>0.49033037872683322</v>
       </c>
       <c r="B51" s="3">
-        <v>0.19658119658119658</v>
+        <v>0.70484330484330482</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G51" s="3">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="H51" s="5">
-        <v>141</v>
+        <v>60.3</v>
       </c>
       <c r="I51" s="5">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K51" s="3">
         <f t="shared" si="4"/>
-        <v>1.3478217882063612E-2</v>
-      </c>
-      <c r="L51" s="5">
-        <v>1.9</v>
-      </c>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L51" s="5"/>
       <c r="M51" s="7">
         <f t="shared" si="2"/>
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="N51" s="3">
         <f t="shared" si="3"/>
-        <v>2.560861397592086E-2</v>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="O51" s="3">
         <f t="shared" si="5"/>
-        <v>92.191010313315104</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="3"/>
+      <c r="S51" s="3"/>
+      <c r="T51" s="3"/>
+      <c r="U51" s="3"/>
+      <c r="V51" s="3"/>
+      <c r="W51" s="3"/>
+      <c r="X51" s="3"/>
+      <c r="Y51" s="3"/>
+      <c r="Z51" s="3"/>
+      <c r="AA51" s="3"/>
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
-        <v>0.61804995970991139</v>
+        <v>0.48992747784045126</v>
       </c>
       <c r="B52" s="3">
-        <v>0.24843304843304842</v>
+        <v>0.67464387464387465</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G52" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H52" s="5">
-        <v>88.9</v>
+        <v>60.3</v>
       </c>
       <c r="I52" s="5">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K52" s="3">
         <f t="shared" si="4"/>
-        <v>5.1402817537852556E-3</v>
-      </c>
-      <c r="L52" s="5">
-        <v>3</v>
-      </c>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L52" s="5"/>
       <c r="M52" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N52" s="3">
         <f t="shared" si="3"/>
-        <v>1.5420845261355766E-2</v>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="O52" s="3">
         <f t="shared" si="5"/>
-        <v>55.515042940880754</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3"/>
+      <c r="S52" s="3"/>
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="3"/>
+      <c r="X52" s="3"/>
+      <c r="Y52" s="3"/>
+      <c r="Z52" s="3"/>
+      <c r="AA52" s="3"/>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <v>0.62087026591458505</v>
+        <v>0.60032232070910552</v>
       </c>
       <c r="B53" s="3">
-        <v>0.27122507122507122</v>
+        <v>0.17720797720797721</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G53" s="3">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="H53" s="5">
-        <v>88.9</v>
-      </c>
-      <c r="I53" s="5">
-        <v>4</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="I53" s="5"/>
       <c r="J53" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K53" s="3">
         <f t="shared" si="4"/>
-        <v>5.1402817537852556E-3</v>
+        <v>3.8013271108436497E-2</v>
       </c>
       <c r="L53" s="5">
-        <v>0.46</v>
+        <v>0.9</v>
       </c>
       <c r="M53" s="7">
         <f t="shared" si="2"/>
-        <v>0.46</v>
+        <v>0.9</v>
       </c>
       <c r="N53" s="3">
         <f t="shared" si="3"/>
-        <v>2.3645296067412178E-3</v>
+        <v>3.421194399759285E-2</v>
       </c>
       <c r="O53" s="3">
         <f t="shared" si="5"/>
-        <v>8.5123065842683836</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+        <v>123.16299839133426</v>
+      </c>
+      <c r="P53" s="3"/>
+      <c r="Q53" s="3"/>
+      <c r="R53" s="3"/>
+      <c r="S53" s="3"/>
+      <c r="T53" s="3"/>
+      <c r="U53" s="3"/>
+      <c r="V53" s="3"/>
+      <c r="W53" s="3"/>
+      <c r="X53" s="3"/>
+      <c r="Y53" s="3"/>
+      <c r="Z53" s="3"/>
+      <c r="AA53" s="3"/>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <v>0.63255439161966154</v>
+        <v>0.62570507655116836</v>
       </c>
       <c r="B54" s="3">
-        <v>0.21652421652421652</v>
+        <v>0.19658119658119658</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G54" s="3">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="H54" s="5">
-        <v>220</v>
-      </c>
-      <c r="I54" s="5"/>
+        <v>141</v>
+      </c>
+      <c r="I54" s="5">
+        <v>5</v>
+      </c>
       <c r="J54" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K54" s="3">
         <f t="shared" si="4"/>
-        <v>3.8013271108436497E-2</v>
-      </c>
-      <c r="L54" s="5"/>
+        <v>1.3478217882063612E-2</v>
+      </c>
+      <c r="L54" s="5">
+        <v>1.9</v>
+      </c>
       <c r="M54" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="N54" s="3">
         <f t="shared" si="3"/>
-        <v>3.8013271108436497E-2</v>
+        <v>2.560861397592086E-2</v>
       </c>
       <c r="O54" s="3">
         <f t="shared" si="5"/>
-        <v>136.84777599037139</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+        <v>92.191010313315104</v>
+      </c>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3"/>
+      <c r="R54" s="3"/>
+      <c r="S54" s="3"/>
+      <c r="T54" s="3"/>
+      <c r="U54" s="3"/>
+      <c r="V54" s="3"/>
+      <c r="W54" s="3"/>
+      <c r="X54" s="3"/>
+      <c r="Y54" s="3"/>
+      <c r="Z54" s="3"/>
+      <c r="AA54" s="3"/>
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
-        <v>0.64464141821112009</v>
+        <v>0.61804995970991139</v>
       </c>
       <c r="B55" s="3">
-        <v>0.25413105413105413</v>
+        <v>0.24843304843304842</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G55" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H55" s="5">
-        <v>60.3</v>
+        <v>88.9</v>
       </c>
       <c r="I55" s="5">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K55" s="3">
         <f t="shared" si="4"/>
-        <v>2.2145165154970788E-3</v>
-      </c>
-      <c r="L55" s="5"/>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="L55" s="5">
+        <v>3</v>
+      </c>
       <c r="M55" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N55" s="3">
         <f t="shared" si="3"/>
-        <v>2.2145165154970788E-3</v>
+        <v>1.5420845261355766E-2</v>
       </c>
       <c r="O55" s="3">
         <f t="shared" si="5"/>
-        <v>7.9722594557894837</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+        <v>55.515042940880754</v>
+      </c>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <v>0.68573730862207893</v>
+        <v>0.62087026591458505</v>
       </c>
       <c r="B56" s="3">
-        <v>0.26381766381766381</v>
+        <v>0.27122507122507122</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G56" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H56" s="5">
-        <v>60.3</v>
+        <v>88.9</v>
       </c>
       <c r="I56" s="5">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K56" s="3">
         <f t="shared" si="4"/>
-        <v>2.2145165154970788E-3</v>
+        <v>5.1402817537852556E-3</v>
       </c>
       <c r="L56" s="5">
-        <v>3</v>
+        <v>0.46</v>
       </c>
       <c r="M56" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0.46</v>
       </c>
       <c r="N56" s="3">
         <f t="shared" si="3"/>
-        <v>6.6435495464912363E-3</v>
+        <v>2.3645296067412178E-3</v>
       </c>
       <c r="O56" s="3">
         <f t="shared" si="5"/>
-        <v>23.916778367368451</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+        <v>8.5123065842683836</v>
+      </c>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
-        <v>0</v>
+        <v>0.63255439161966154</v>
       </c>
       <c r="B57" s="3">
-        <v>0</v>
+        <v>0.21652421652421652</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F57" s="3"/>
+        <v>193</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G57" s="3">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="H57" s="5">
-        <v>88.9</v>
-      </c>
-      <c r="I57" s="5">
-        <v>4</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="I57" s="5"/>
       <c r="J57" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K57" s="3">
         <f t="shared" si="4"/>
-        <v>5.1402817537852556E-3</v>
+        <v>3.8013271108436497E-2</v>
       </c>
       <c r="L57" s="5"/>
       <c r="M57" s="7">
@@ -4076,37 +4790,49 @@
       </c>
       <c r="N57" s="3">
         <f t="shared" si="3"/>
-        <v>5.1402817537852556E-3</v>
+        <v>3.8013271108436497E-2</v>
       </c>
       <c r="O57" s="3">
         <f t="shared" si="5"/>
-        <v>18.505014313626919</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+        <v>136.84777599037139</v>
+      </c>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3"/>
+      <c r="R57" s="3"/>
+      <c r="S57" s="3"/>
+      <c r="T57" s="3"/>
+      <c r="U57" s="3"/>
+      <c r="V57" s="3"/>
+      <c r="W57" s="3"/>
+      <c r="X57" s="3"/>
+      <c r="Y57" s="3"/>
+      <c r="Z57" s="3"/>
+      <c r="AA57" s="3"/>
+    </row>
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
-        <v>0.76027397260273977</v>
+        <v>0.64464141821112009</v>
       </c>
       <c r="B58" s="3">
-        <v>0.51111111111111107</v>
+        <v>0.25413105413105413</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G58" s="3">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H58" s="5">
-        <v>76.099999999999994</v>
+        <v>60.3</v>
       </c>
       <c r="I58" s="5">
         <v>3.6</v>
@@ -4116,7 +4842,7 @@
       </c>
       <c r="K58" s="3">
         <f t="shared" si="4"/>
-        <v>3.728450015261999E-3</v>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="7">
@@ -4125,96 +4851,120 @@
       </c>
       <c r="N58" s="3">
         <f t="shared" si="3"/>
-        <v>3.728450015261999E-3</v>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="O58" s="3">
         <f t="shared" si="5"/>
-        <v>13.422420054943197</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3"/>
+      <c r="S58" s="3"/>
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="3"/>
+      <c r="X58" s="3"/>
+      <c r="Y58" s="3"/>
+      <c r="Z58" s="3"/>
+      <c r="AA58" s="3"/>
+    </row>
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <v>0.70668815471394042</v>
+        <v>0.68573730862207893</v>
       </c>
       <c r="B59" s="3">
-        <v>0.50980056980056987</v>
+        <v>0.26381766381766381</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G59" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H59" s="5">
-        <v>114</v>
+        <v>60.3</v>
       </c>
       <c r="I59" s="5">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K59" s="3">
         <f t="shared" si="4"/>
-        <v>8.6590147514568668E-3</v>
-      </c>
-      <c r="L59" s="5"/>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L59" s="5">
+        <v>3</v>
+      </c>
       <c r="M59" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N59" s="3">
         <f t="shared" si="3"/>
-        <v>8.6590147514568668E-3</v>
+        <v>6.6435495464912363E-3</v>
       </c>
       <c r="O59" s="3">
         <f t="shared" si="5"/>
-        <v>31.17245310524472</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+        <v>23.916778367368451</v>
+      </c>
+      <c r="P59" s="3"/>
+      <c r="Q59" s="3"/>
+      <c r="R59" s="3"/>
+      <c r="S59" s="3"/>
+      <c r="T59" s="3"/>
+      <c r="U59" s="3"/>
+      <c r="V59" s="3"/>
+      <c r="W59" s="3"/>
+      <c r="X59" s="3"/>
+      <c r="Y59" s="3"/>
+      <c r="Z59" s="3"/>
+      <c r="AA59" s="3"/>
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <v>0.75423045930701049</v>
+        <v>0</v>
       </c>
       <c r="B60" s="3">
-        <v>0.53789173789173794</v>
+        <v>0</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="F60" s="3"/>
       <c r="G60" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H60" s="5">
-        <v>60.3</v>
+        <v>88.9</v>
       </c>
       <c r="I60" s="5">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K60" s="3">
         <f t="shared" si="4"/>
-        <v>2.2145165154970788E-3</v>
+        <v>5.1402817537852556E-3</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="7">
@@ -4223,31 +4973,43 @@
       </c>
       <c r="N60" s="3">
         <f t="shared" si="3"/>
-        <v>2.2145165154970788E-3</v>
+        <v>5.1402817537852556E-3</v>
       </c>
       <c r="O60" s="3">
         <f t="shared" si="5"/>
-        <v>7.9722594557894837</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18.505014313626919</v>
+      </c>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3"/>
+      <c r="S60" s="3"/>
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="V60" s="3"/>
+      <c r="W60" s="3"/>
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="3"/>
+      <c r="AA60" s="3"/>
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>0.70064464141821114</v>
+        <v>0.76027397260273977</v>
       </c>
       <c r="B61" s="3">
-        <v>0.54529914529914525</v>
+        <v>0.51111111111111107</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G61" s="3">
         <v>65</v>
@@ -4265,56 +5027,66 @@
         <f t="shared" si="4"/>
         <v>3.728450015261999E-3</v>
       </c>
-      <c r="L61" s="5">
-        <v>1.1000000000000001</v>
-      </c>
+      <c r="L61" s="5"/>
       <c r="M61" s="7">
         <f t="shared" si="2"/>
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="N61" s="3">
         <f t="shared" si="3"/>
-        <v>4.1012950167881989E-3</v>
+        <v>3.728450015261999E-3</v>
       </c>
       <c r="O61" s="3">
         <f t="shared" si="5"/>
-        <v>14.764662060437516</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+        <v>13.422420054943197</v>
+      </c>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3"/>
+      <c r="R61" s="3"/>
+      <c r="S61" s="3"/>
+      <c r="T61" s="3"/>
+      <c r="U61" s="3"/>
+      <c r="V61" s="3"/>
+      <c r="W61" s="3"/>
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3"/>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>0.75463336019339244</v>
+        <v>0.70668815471394042</v>
       </c>
       <c r="B62" s="3">
-        <v>0.56182336182336179</v>
+        <v>0.50980056980056987</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G62" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H62" s="5">
-        <v>60.3</v>
+        <v>114</v>
       </c>
       <c r="I62" s="5">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K62" s="3">
         <f t="shared" si="4"/>
-        <v>2.2145165154970788E-3</v>
+        <v>8.6590147514568668E-3</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="7">
@@ -4323,37 +5095,49 @@
       </c>
       <c r="N62" s="3">
         <f t="shared" si="3"/>
-        <v>2.2145165154970788E-3</v>
+        <v>8.6590147514568668E-3</v>
       </c>
       <c r="O62" s="3">
         <f t="shared" si="5"/>
-        <v>7.9722594557894837</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+        <v>31.17245310524472</v>
+      </c>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3"/>
+      <c r="S62" s="3"/>
+      <c r="T62" s="3"/>
+      <c r="U62" s="3"/>
+      <c r="V62" s="3"/>
+      <c r="W62" s="3"/>
+      <c r="X62" s="3"/>
+      <c r="Y62" s="3"/>
+      <c r="Z62" s="3"/>
+      <c r="AA62" s="3"/>
+    </row>
+    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
-        <v>0.70427074939564871</v>
+        <v>0.75423045930701049</v>
       </c>
       <c r="B63" s="3">
-        <v>0.52307692307692311</v>
+        <v>0.53789173789173794</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G63" s="3">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H63" s="5">
-        <v>76.099999999999994</v>
+        <v>60.3</v>
       </c>
       <c r="I63" s="5">
         <v>3.6</v>
@@ -4363,107 +5147,131 @@
       </c>
       <c r="K63" s="3">
         <f t="shared" si="4"/>
-        <v>3.728450015261999E-3</v>
-      </c>
-      <c r="L63" s="5">
-        <v>1</v>
-      </c>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L63" s="5"/>
       <c r="M63" s="7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N63" s="3">
         <f t="shared" si="3"/>
-        <v>3.728450015261999E-3</v>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="O63" s="3">
         <f t="shared" si="5"/>
-        <v>13.422420054943197</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="P63" s="3"/>
+      <c r="Q63" s="3"/>
+      <c r="R63" s="3"/>
+      <c r="S63" s="3"/>
+      <c r="T63" s="3"/>
+      <c r="U63" s="3"/>
+      <c r="V63" s="3"/>
+      <c r="W63" s="3"/>
+      <c r="X63" s="3"/>
+      <c r="Y63" s="3"/>
+      <c r="Z63" s="3"/>
+      <c r="AA63" s="3"/>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
-        <v>0.77356970185334406</v>
+        <v>0.70064464141821114</v>
       </c>
       <c r="B64" s="3">
-        <v>0.56980056980056981</v>
+        <v>0.54529914529914525</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G64" s="3">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="H64" s="5">
-        <v>42.2</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="I64" s="5">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K64" s="3">
         <f t="shared" si="4"/>
-        <v>1.0065977021367059E-3</v>
-      </c>
-      <c r="L64" s="5"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L64" s="5">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="M64" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N64" s="3">
         <f t="shared" si="3"/>
-        <v>1.0065977021367059E-3</v>
+        <v>4.1012950167881989E-3</v>
       </c>
       <c r="O64" s="3">
         <f t="shared" si="5"/>
-        <v>3.6237517276921412</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+        <v>14.764662060437516</v>
+      </c>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3"/>
+      <c r="S64" s="3"/>
+      <c r="T64" s="3"/>
+      <c r="U64" s="3"/>
+      <c r="V64" s="3"/>
+      <c r="W64" s="3"/>
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3"/>
+      <c r="Z64" s="3"/>
+      <c r="AA64" s="3"/>
+    </row>
+    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
-        <v>0.39605157131345686</v>
+        <v>0.75463336019339244</v>
       </c>
       <c r="B65" s="3">
-        <v>0.54245014245014245</v>
+        <v>0.56182336182336179</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="G65" s="3">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="H65" s="5">
-        <v>168.3</v>
+        <v>60.3</v>
       </c>
       <c r="I65" s="5">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K65" s="3">
         <f t="shared" si="4"/>
-        <v>1.9681206182778688E-2</v>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="L65" s="5"/>
       <c r="M65" s="7">
@@ -4472,292 +5280,366 @@
       </c>
       <c r="N65" s="3">
         <f t="shared" si="3"/>
-        <v>1.9681206182778688E-2</v>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="O65" s="3">
         <f t="shared" si="5"/>
-        <v>70.852342258003276</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="P65" s="3"/>
+      <c r="Q65" s="3"/>
+      <c r="R65" s="3"/>
+      <c r="S65" s="3"/>
+      <c r="T65" s="3"/>
+      <c r="U65" s="3"/>
+      <c r="V65" s="3"/>
+      <c r="W65" s="3"/>
+      <c r="X65" s="3"/>
+      <c r="Y65" s="3"/>
+      <c r="Z65" s="3"/>
+      <c r="AA65" s="3"/>
+    </row>
+    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
-        <v>0</v>
+        <v>0.70427074939564871</v>
       </c>
       <c r="B66" s="3">
-        <v>0</v>
+        <v>0.52307692307692311</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="G66" s="3">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="H66" s="5">
-        <v>114</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="I66" s="5">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>84</v>
       </c>
       <c r="K66" s="3">
-        <f t="shared" ref="K66:K87" si="6">PI()*(((H66-2*I66)*10^-3)^2/4)</f>
-        <v>8.4948665353068026E-3</v>
-      </c>
-      <c r="L66" s="5"/>
+        <f t="shared" si="4"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="L66" s="5">
+        <v>1</v>
+      </c>
       <c r="M66" s="7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N66" s="3">
         <f t="shared" si="3"/>
+        <v>3.728450015261999E-3</v>
+      </c>
+      <c r="O66" s="3">
+        <f t="shared" si="5"/>
+        <v>13.422420054943197</v>
+      </c>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3"/>
+      <c r="S66" s="3"/>
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
+      <c r="Z66" s="3"/>
+      <c r="AA66" s="3"/>
+    </row>
+    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A67" s="3">
+        <v>0.77356970185334406</v>
+      </c>
+      <c r="B67" s="3">
+        <v>0.56980056980056981</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G67" s="3">
+        <v>32</v>
+      </c>
+      <c r="H67" s="5">
+        <v>42.2</v>
+      </c>
+      <c r="I67" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K67" s="3">
+        <f t="shared" si="4"/>
+        <v>1.0065977021367059E-3</v>
+      </c>
+      <c r="L67" s="5"/>
+      <c r="M67" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N67" s="3">
+        <f t="shared" si="3"/>
+        <v>1.0065977021367059E-3</v>
+      </c>
+      <c r="O67" s="3">
+        <f t="shared" si="5"/>
+        <v>3.6237517276921412</v>
+      </c>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A68" s="3">
+        <v>0.39605157131345686</v>
+      </c>
+      <c r="B68" s="3">
+        <v>0.54245014245014245</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G68" s="3">
+        <v>150</v>
+      </c>
+      <c r="H68" s="5">
+        <v>168.3</v>
+      </c>
+      <c r="I68" s="5">
+        <v>5</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K68" s="3">
+        <f t="shared" si="4"/>
+        <v>1.9681206182778688E-2</v>
+      </c>
+      <c r="L68" s="5"/>
+      <c r="M68" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N68" s="3">
+        <f t="shared" si="3"/>
+        <v>1.9681206182778688E-2</v>
+      </c>
+      <c r="O68" s="3">
+        <f t="shared" si="5"/>
+        <v>70.852342258003276</v>
+      </c>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3"/>
+      <c r="S68" s="3"/>
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
+      <c r="Z68" s="3"/>
+      <c r="AA68" s="3"/>
+    </row>
+    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A69" s="3">
+        <v>0</v>
+      </c>
+      <c r="B69" s="3">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G69" s="3">
+        <v>100</v>
+      </c>
+      <c r="H69" s="5">
+        <v>114</v>
+      </c>
+      <c r="I69" s="5">
+        <v>5</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K69" s="3">
+        <f t="shared" ref="K69:K91" si="6">PI()*(((H69-2*I69)*10^-3)^2/4)</f>
         <v>8.4948665353068026E-3</v>
       </c>
-      <c r="O66" s="3">
-        <f t="shared" ref="O66:O71" si="7">N66*3600</f>
+      <c r="L69" s="5"/>
+      <c r="M69" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N69" s="3">
+        <f t="shared" si="3"/>
+        <v>8.4948665353068026E-3</v>
+      </c>
+      <c r="O69" s="3">
+        <f t="shared" ref="O69:O74" si="7">N69*3600</f>
         <v>30.58151952710449</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A67" s="3">
+      <c r="P69" s="3"/>
+      <c r="Q69" s="3"/>
+      <c r="R69" s="3"/>
+      <c r="S69" s="3"/>
+      <c r="T69" s="3"/>
+      <c r="U69" s="3"/>
+      <c r="V69" s="3"/>
+      <c r="W69" s="3"/>
+      <c r="X69" s="3"/>
+      <c r="Y69" s="3"/>
+      <c r="Z69" s="3"/>
+      <c r="AA69" s="3"/>
+    </row>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A70" s="3">
         <v>0</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B70" s="3">
         <v>0</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E67" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F67" s="3" t="s">
+      <c r="E70" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F70" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G67" s="3">
+      <c r="G70" s="3">
         <v>100</v>
       </c>
-      <c r="H67" s="5">
+      <c r="H70" s="5">
         <v>114</v>
       </c>
-      <c r="I67" s="5">
+      <c r="I70" s="5">
         <v>4.5</v>
       </c>
-      <c r="J67" s="3" t="s">
+      <c r="J70" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K67" s="3">
+      <c r="K70" s="3">
         <f t="shared" si="6"/>
         <v>8.6590147514568668E-3</v>
       </c>
-      <c r="L67" s="5"/>
-      <c r="M67" s="7">
-        <f t="shared" ref="M67:M71" si="8">IF(L67&gt;0, L67, 1)</f>
+      <c r="L70" s="5"/>
+      <c r="M70" s="7">
+        <f t="shared" ref="M70:M74" si="8">IF(L70&gt;0, L70, 1)</f>
         <v>1</v>
       </c>
-      <c r="N67" s="3">
-        <f t="shared" ref="N67:N71" si="9">M67*K67</f>
+      <c r="N70" s="3">
+        <f t="shared" ref="N70:N74" si="9">M70*K70</f>
         <v>8.6590147514568668E-3</v>
       </c>
-      <c r="O67" s="3">
+      <c r="O70" s="3">
         <f t="shared" si="7"/>
         <v>31.17245310524472</v>
       </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A68" s="3">
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3"/>
+      <c r="S70" s="3"/>
+      <c r="T70" s="3"/>
+      <c r="U70" s="3"/>
+      <c r="V70" s="3"/>
+      <c r="W70" s="3"/>
+      <c r="X70" s="3"/>
+      <c r="Y70" s="3"/>
+      <c r="Z70" s="3"/>
+      <c r="AA70" s="3"/>
+    </row>
+    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A71" s="3">
         <v>0.41700241740531829</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B71" s="3">
         <v>0.58290598290598294</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D71" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E68" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F68" s="3" t="s">
+      <c r="E71" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F71" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G68" s="3">
+      <c r="G71" s="3">
         <v>65</v>
       </c>
-      <c r="H68" s="5">
+      <c r="H71" s="5">
         <v>73</v>
       </c>
-      <c r="I68" s="5">
+      <c r="I71" s="5">
         <v>3.6</v>
       </c>
-      <c r="J68" s="3" t="s">
+      <c r="J71" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K68" s="3">
+      <c r="K71" s="3">
         <f t="shared" si="6"/>
         <v>3.4004913041721279E-3</v>
-      </c>
-      <c r="L68" s="5"/>
-      <c r="M68" s="7">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="N68" s="3">
-        <f t="shared" si="9"/>
-        <v>3.4004913041721279E-3</v>
-      </c>
-      <c r="O68" s="3">
-        <f t="shared" si="7"/>
-        <v>12.24176869501966</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A69" s="3">
-        <v>0</v>
-      </c>
-      <c r="B69" s="3">
-        <v>0</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G69" s="3">
-        <v>50</v>
-      </c>
-      <c r="H69" s="5">
-        <v>60.3</v>
-      </c>
-      <c r="I69" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K69" s="3">
-        <f t="shared" si="6"/>
-        <v>2.2145165154970788E-3</v>
-      </c>
-      <c r="L69" s="5"/>
-      <c r="M69" s="7">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="N69" s="3">
-        <f t="shared" si="9"/>
-        <v>2.2145165154970788E-3</v>
-      </c>
-      <c r="O69" s="3">
-        <f t="shared" si="7"/>
-        <v>7.9722594557894837</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A70" s="3">
-        <v>0.41539081385979049</v>
-      </c>
-      <c r="B70" s="3">
-        <v>0.53048433048433052</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G70" s="3">
-        <v>65</v>
-      </c>
-      <c r="H70" s="5">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="I70" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K70" s="3">
-        <f t="shared" si="6"/>
-        <v>3.728450015261999E-3</v>
-      </c>
-      <c r="L70" s="5"/>
-      <c r="M70" s="7">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="N70" s="3">
-        <f t="shared" si="9"/>
-        <v>3.728450015261999E-3</v>
-      </c>
-      <c r="O70" s="3">
-        <f t="shared" si="7"/>
-        <v>13.422420054943197</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A71" s="3">
-        <v>0</v>
-      </c>
-      <c r="B71" s="3">
-        <v>0</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G71" s="3">
-        <v>50</v>
-      </c>
-      <c r="H71" s="5">
-        <v>60.3</v>
-      </c>
-      <c r="I71" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K71" s="3">
-        <f t="shared" si="6"/>
-        <v>2.2145165154970788E-3</v>
       </c>
       <c r="L71" s="5"/>
       <c r="M71" s="7">
@@ -4766,37 +5648,51 @@
       </c>
       <c r="N71" s="3">
         <f t="shared" si="9"/>
-        <v>2.2145165154970788E-3</v>
+        <v>3.4004913041721279E-3</v>
       </c>
       <c r="O71" s="3">
         <f t="shared" si="7"/>
-        <v>7.9722594557894837</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+        <v>12.24176869501966</v>
+      </c>
+      <c r="P71" s="3"/>
+      <c r="Q71" s="3"/>
+      <c r="R71" s="3"/>
+      <c r="S71" s="3"/>
+      <c r="T71" s="3"/>
+      <c r="U71" s="3"/>
+      <c r="V71" s="3"/>
+      <c r="W71" s="3"/>
+      <c r="X71" s="3"/>
+      <c r="Y71" s="3"/>
+      <c r="Z71" s="3"/>
+      <c r="AA71" s="3"/>
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <v>9.2999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="B72" s="3">
-        <v>0.15759699999999999</v>
+        <v>0</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>229</v>
+        <v>72</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>230</v>
+        <v>152</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F72" s="3"/>
+        <v>213</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="G72" s="3">
-        <v>65</v>
-      </c>
-      <c r="H72" s="3">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="I72" s="3">
+        <v>50</v>
+      </c>
+      <c r="H72" s="5">
+        <v>60.3</v>
+      </c>
+      <c r="I72" s="5">
         <v>3.6</v>
       </c>
       <c r="J72" s="3" t="s">
@@ -4804,45 +5700,60 @@
       </c>
       <c r="K72" s="3">
         <f t="shared" si="6"/>
-        <v>3.728450015261999E-3</v>
-      </c>
-      <c r="L72" s="3"/>
-      <c r="M72" s="3">
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L72" s="5"/>
+      <c r="M72" s="7">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N72" s="3">
-        <f t="shared" ref="N72:N86" si="10">M72*K72</f>
-        <v>3.728450015261999E-3</v>
+        <f t="shared" si="9"/>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="O72" s="3">
-        <f t="shared" ref="O72:O75" si="11">N72*3600</f>
-        <v>13.422420054943197</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3"/>
+      <c r="S72" s="3"/>
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
+      <c r="X72" s="3"/>
+      <c r="Y72" s="3"/>
+      <c r="Z72" s="3"/>
+      <c r="AA72" s="3"/>
+    </row>
+    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <v>9.7000000000000003E-2</v>
+        <v>0.41539081385979049</v>
       </c>
       <c r="B73" s="3">
-        <v>0.168905</v>
+        <v>0.53048433048433052</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>229</v>
+        <v>72</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>231</v>
+        <v>151</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="F73" s="3"/>
+        <v>212</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="G73" s="3">
         <v>65</v>
       </c>
-      <c r="H73" s="3">
+      <c r="H73" s="5">
         <v>76.099999999999994</v>
       </c>
-      <c r="I73" s="3">
+      <c r="I73" s="5">
         <v>3.6</v>
       </c>
       <c r="J73" s="3" t="s">
@@ -4852,43 +5763,58 @@
         <f t="shared" si="6"/>
         <v>3.728450015261999E-3</v>
       </c>
-      <c r="L73" s="3"/>
-      <c r="M73" s="3">
+      <c r="L73" s="5"/>
+      <c r="M73" s="7">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N73" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3.728450015261999E-3</v>
       </c>
       <c r="O73" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>13.422420054943197</v>
       </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P73" s="3"/>
+      <c r="Q73" s="3"/>
+      <c r="R73" s="3"/>
+      <c r="S73" s="3"/>
+      <c r="T73" s="3"/>
+      <c r="U73" s="3"/>
+      <c r="V73" s="3"/>
+      <c r="W73" s="3"/>
+      <c r="X73" s="3"/>
+      <c r="Y73" s="3"/>
+      <c r="Z73" s="3"/>
+      <c r="AA73" s="3"/>
+    </row>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <v>9.1499999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="B74" s="3">
-        <v>0.20494699999999999</v>
+        <v>0</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>229</v>
+        <v>72</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>232</v>
+        <v>153</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="F74" s="3"/>
+        <v>214</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="G74" s="3">
-        <v>65</v>
-      </c>
-      <c r="H74" s="3">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="I74" s="3">
+        <v>50</v>
+      </c>
+      <c r="H74" s="5">
+        <v>60.3</v>
+      </c>
+      <c r="I74" s="5">
         <v>3.6</v>
       </c>
       <c r="J74" s="3" t="s">
@@ -4896,36 +5822,49 @@
       </c>
       <c r="K74" s="3">
         <f t="shared" si="6"/>
-        <v>3.728450015261999E-3</v>
-      </c>
-      <c r="L74" s="3"/>
-      <c r="M74" s="3">
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L74" s="5"/>
+      <c r="M74" s="7">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N74" s="3">
-        <f t="shared" si="10"/>
-        <v>3.728450015261999E-3</v>
+        <f t="shared" si="9"/>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="O74" s="3">
-        <f t="shared" si="11"/>
-        <v>13.422420054943197</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3"/>
+      <c r="S74" s="3"/>
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74" s="3"/>
+      <c r="W74" s="3"/>
+      <c r="X74" s="3"/>
+      <c r="Y74" s="3"/>
+      <c r="Z74" s="3"/>
+      <c r="AA74" s="3"/>
+    </row>
+    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="B75" s="3">
-        <v>0.21696099999999999</v>
+        <v>0.15759699999999999</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="E75" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3">
@@ -4949,39 +5888,58 @@
         <v>1</v>
       </c>
       <c r="N75" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="N75:N91" si="10">M75*K75</f>
         <v>3.728450015261999E-3</v>
       </c>
       <c r="O75" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="O75:O78" si="11">N75*3600</f>
         <v>13.422420054943197</v>
       </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P75" s="3"/>
+      <c r="Q75" s="3"/>
+      <c r="R75" s="3"/>
+      <c r="S75" s="3"/>
+      <c r="T75" s="3"/>
+      <c r="U75" s="3"/>
+      <c r="V75" s="3"/>
+      <c r="W75" s="3"/>
+      <c r="X75" s="3"/>
+      <c r="Y75" s="3"/>
+      <c r="Z75" s="3"/>
+      <c r="AA75" s="3"/>
+    </row>
+    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A76" s="3">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="B76" s="3">
+        <v>0.168905</v>
+      </c>
       <c r="C76" s="3" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E76" s="3" t="str">
-        <f>D76&amp;"01"</f>
-        <v>SS-300001</v>
+        <v>230</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>234</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H76" s="3">
-        <v>60.3</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="I76" s="3">
         <v>3.6</v>
       </c>
-      <c r="J76" s="3"/>
+      <c r="J76" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="K76" s="3">
         <f t="shared" si="6"/>
-        <v>2.2145165154970788E-3</v>
+        <v>3.728450015261999E-3</v>
       </c>
       <c r="L76" s="3"/>
       <c r="M76" s="3">
@@ -4989,44 +5947,57 @@
       </c>
       <c r="N76" s="3">
         <f t="shared" si="10"/>
-        <v>2.2145165154970788E-3</v>
+        <v>3.728450015261999E-3</v>
       </c>
       <c r="O76" s="3">
-        <f t="shared" ref="O76:O86" si="12">N76*3600</f>
-        <v>7.9722594557894837</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v>13.422420054943197</v>
+      </c>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3"/>
+      <c r="S76" s="3"/>
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
+      <c r="X76" s="3"/>
+      <c r="Y76" s="3"/>
+      <c r="Z76" s="3"/>
+      <c r="AA76" s="3"/>
+    </row>
+    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <v>0.307</v>
+        <v>9.1499999999999998E-2</v>
       </c>
       <c r="B77" s="3">
-        <v>0.16678399999999999</v>
+        <v>0.20494699999999999</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E77" s="3" t="str">
-        <f>D77&amp;"02"</f>
-        <v>SS-100002</v>
+        <v>231</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H77" s="3">
-        <v>60.3</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="I77" s="3">
         <v>3.6</v>
       </c>
-      <c r="J77" s="3"/>
+      <c r="J77" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="K77" s="3">
         <f t="shared" si="6"/>
-        <v>2.2145165154970788E-3</v>
+        <v>3.728450015261999E-3</v>
       </c>
       <c r="L77" s="3"/>
       <c r="M77" s="3">
@@ -5034,29 +6005,40 @@
       </c>
       <c r="N77" s="3">
         <f t="shared" si="10"/>
-        <v>2.2145165154970788E-3</v>
+        <v>3.728450015261999E-3</v>
       </c>
       <c r="O77" s="3">
-        <f t="shared" si="12"/>
-        <v>7.9722594557894837</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v>13.422420054943197</v>
+      </c>
+      <c r="P77" s="3"/>
+      <c r="Q77" s="3"/>
+      <c r="R77" s="3"/>
+      <c r="S77" s="3"/>
+      <c r="T77" s="3"/>
+      <c r="U77" s="3"/>
+      <c r="V77" s="3"/>
+      <c r="W77" s="3"/>
+      <c r="X77" s="3"/>
+      <c r="Y77" s="3"/>
+      <c r="Z77" s="3"/>
+      <c r="AA77" s="3"/>
+    </row>
+    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>0.14549999999999999</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="B78" s="3">
-        <v>0.46148400000000001</v>
+        <v>0.21696099999999999</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E78" s="3" t="str">
-        <f>D78&amp;1</f>
-        <v>SI-6031</v>
+        <v>232</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>236</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3">
@@ -5068,7 +6050,9 @@
       <c r="I78" s="3">
         <v>3.6</v>
       </c>
-      <c r="J78" s="3"/>
+      <c r="J78" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="K78" s="3">
         <f t="shared" si="6"/>
         <v>3.728450015261999E-3</v>
@@ -5082,33 +6066,39 @@
         <v>3.728450015261999E-3</v>
       </c>
       <c r="O78" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>13.422420054943197</v>
       </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A79" s="3">
-        <v>0.1225</v>
-      </c>
-      <c r="B79" s="3">
-        <v>0.68551200000000001</v>
-      </c>
+      <c r="P78" s="3"/>
+      <c r="Q78" s="3"/>
+      <c r="R78" s="3"/>
+      <c r="S78" s="3"/>
+      <c r="T78" s="3"/>
+      <c r="U78" s="3"/>
+      <c r="V78" s="3"/>
+      <c r="W78" s="3"/>
+      <c r="X78" s="3"/>
+      <c r="Y78" s="3"/>
+      <c r="Z78" s="3"/>
+      <c r="AA78" s="3"/>
+    </row>
+    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C79" s="3" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E79" s="3" t="str">
         <f>D79&amp;"01"</f>
-        <v>SI-210701</v>
+        <v>SS-300001</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H79" s="3">
-        <v>76.099999999999994</v>
+        <v>60.3</v>
       </c>
       <c r="I79" s="3">
         <v>3.6</v>
@@ -5116,37 +6106,49 @@
       <c r="J79" s="3"/>
       <c r="K79" s="3">
         <f t="shared" si="6"/>
-        <v>3.728450015261999E-3</v>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="L79" s="3"/>
       <c r="M79" s="3">
         <v>1</v>
       </c>
       <c r="N79" s="3">
-        <f t="shared" si="10"/>
-        <v>3.728450015261999E-3</v>
+        <f>M79*K79</f>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="O79" s="3">
-        <f t="shared" si="12"/>
-        <v>13.422420054943197</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" ref="O79:O91" si="12">N79*3600</f>
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="P79" s="3"/>
+      <c r="Q79" s="3"/>
+      <c r="R79" s="3"/>
+      <c r="S79" s="3"/>
+      <c r="T79" s="3"/>
+      <c r="U79" s="3"/>
+      <c r="V79" s="3"/>
+      <c r="W79" s="3"/>
+      <c r="X79" s="3"/>
+      <c r="Y79" s="3"/>
+      <c r="Z79" s="3"/>
+      <c r="AA79" s="3"/>
+    </row>
+    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <v>0.111</v>
+        <v>0.307</v>
       </c>
       <c r="B80" s="3">
-        <v>0.67349800000000004</v>
+        <v>0.16678399999999999</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="E80" s="3" t="str">
         <f>D80&amp;"02"</f>
-        <v>SI-220702</v>
+        <v>SS-100002</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3">
@@ -5175,30 +6177,42 @@
         <f t="shared" si="12"/>
         <v>7.9722594557894837</v>
       </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P80" s="3"/>
+      <c r="Q80" s="3"/>
+      <c r="R80" s="3"/>
+      <c r="S80" s="3"/>
+      <c r="T80" s="3"/>
+      <c r="U80" s="3"/>
+      <c r="V80" s="3"/>
+      <c r="W80" s="3"/>
+      <c r="X80" s="3"/>
+      <c r="Y80" s="3"/>
+      <c r="Z80" s="3"/>
+      <c r="AA80" s="3"/>
+    </row>
+    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <v>7.85E-2</v>
+        <v>0.14549999999999999</v>
       </c>
       <c r="B81" s="3">
-        <v>0.66855100000000001</v>
+        <v>0.46148400000000001</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E81" s="3" t="str">
-        <f>D81&amp;"03"</f>
-        <v>SI-2x0703</v>
+        <f>D81&amp;1</f>
+        <v>SI-6031</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H81" s="3">
-        <v>88.9</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="I81" s="3">
         <v>3.6</v>
@@ -5206,7 +6220,7 @@
       <c r="J81" s="3"/>
       <c r="K81" s="3">
         <f t="shared" si="6"/>
-        <v>5.2424463468799948E-3</v>
+        <v>3.728450015261999E-3</v>
       </c>
       <c r="L81" s="3"/>
       <c r="M81" s="3">
@@ -5214,30 +6228,48 @@
       </c>
       <c r="N81" s="3">
         <f t="shared" si="10"/>
-        <v>5.2424463468799948E-3</v>
+        <v>3.728450015261999E-3</v>
       </c>
       <c r="O81" s="3">
         <f t="shared" si="12"/>
-        <v>18.872806848767983</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+        <v>13.422420054943197</v>
+      </c>
+      <c r="P81" s="3"/>
+      <c r="Q81" s="3"/>
+      <c r="R81" s="3"/>
+      <c r="S81" s="3"/>
+      <c r="T81" s="3"/>
+      <c r="U81" s="3"/>
+      <c r="V81" s="3"/>
+      <c r="W81" s="3"/>
+      <c r="X81" s="3"/>
+      <c r="Y81" s="3"/>
+      <c r="Z81" s="3"/>
+      <c r="AA81" s="3"/>
+    </row>
+    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A82" s="3">
+        <v>0.1225</v>
+      </c>
+      <c r="B82" s="3">
+        <v>0.68551200000000001</v>
+      </c>
       <c r="C82" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E82" s="3" t="str">
-        <f>D82&amp;"04"</f>
-        <v>SS-210004</v>
+        <f>D82&amp;"01"</f>
+        <v>SI-210701</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H82" s="3">
-        <v>60.3</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="I82" s="3">
         <v>3.6</v>
@@ -5245,7 +6277,7 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3">
         <f t="shared" si="6"/>
-        <v>2.2145165154970788E-3</v>
+        <v>3.728450015261999E-3</v>
       </c>
       <c r="L82" s="3"/>
       <c r="M82" s="3">
@@ -5253,25 +6285,41 @@
       </c>
       <c r="N82" s="3">
         <f t="shared" si="10"/>
-        <v>2.2145165154970788E-3</v>
+        <v>3.728450015261999E-3</v>
       </c>
       <c r="O82" s="3">
         <f t="shared" si="12"/>
-        <v>7.9722594557894837</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
+        <v>13.422420054943197</v>
+      </c>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A83" s="3">
+        <v>0.111</v>
+      </c>
+      <c r="B83" s="3">
+        <v>0.67349800000000004</v>
+      </c>
       <c r="C83" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E83" s="3" t="str">
-        <f>D83&amp;"05"</f>
-        <v>SS-220005</v>
+        <f>D83&amp;"02"</f>
+        <v>SI-220702</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3">
@@ -5300,38 +6348,50 @@
         <f t="shared" si="12"/>
         <v>7.9722594557894837</v>
       </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A84" s="1">
-        <v>0.121</v>
+      <c r="P83" s="3"/>
+      <c r="Q83" s="3"/>
+      <c r="R83" s="3"/>
+      <c r="S83" s="3"/>
+      <c r="T83" s="3"/>
+      <c r="U83" s="3"/>
+      <c r="V83" s="3"/>
+      <c r="W83" s="3"/>
+      <c r="X83" s="3"/>
+      <c r="Y83" s="3"/>
+      <c r="Z83" s="3"/>
+      <c r="AA83" s="3"/>
+    </row>
+    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A84" s="3">
+        <v>7.85E-2</v>
       </c>
       <c r="B84" s="3">
-        <v>0.76183699999999999</v>
+        <v>0.66855100000000001</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E84" s="3" t="str">
-        <f>D84&amp;1</f>
-        <v>S-60021</v>
+        <f>D84&amp;"03"</f>
+        <v>SI-2x0703</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H84" s="3">
-        <v>114.3</v>
+        <v>88.9</v>
       </c>
       <c r="I84" s="3">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="J84" s="3"/>
       <c r="K84" s="3">
         <f t="shared" si="6"/>
-        <v>8.5439460665375083E-3</v>
+        <v>5.2424463468799948E-3</v>
       </c>
       <c r="L84" s="3"/>
       <c r="M84" s="3">
@@ -5339,51 +6399,384 @@
       </c>
       <c r="N84" s="3">
         <f t="shared" si="10"/>
-        <v>8.5439460665375083E-3</v>
+        <v>5.2424463468799948E-3</v>
       </c>
       <c r="O84" s="3">
         <f t="shared" si="12"/>
-        <v>30.75820583953503</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18.872806848767983</v>
+      </c>
+      <c r="P84" s="3"/>
+      <c r="Q84" s="3"/>
+      <c r="R84" s="3"/>
+      <c r="S84" s="3"/>
+      <c r="T84" s="3"/>
+      <c r="U84" s="3"/>
+      <c r="V84" s="3"/>
+      <c r="W84" s="3"/>
+      <c r="X84" s="3"/>
+      <c r="Y84" s="3"/>
+      <c r="Z84" s="3"/>
+      <c r="AA84" s="3"/>
+    </row>
+    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C85" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E85" s="3" t="str">
+        <f>D85&amp;"04"</f>
+        <v>SS-210004</v>
+      </c>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3">
+        <v>50</v>
+      </c>
+      <c r="H85" s="3">
+        <v>60.3</v>
+      </c>
+      <c r="I85" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="J85" s="3"/>
       <c r="K85" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L85" s="3"/>
       <c r="M85" s="3">
         <v>1</v>
       </c>
       <c r="N85" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="O85" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="P85" s="3"/>
+      <c r="Q85" s="3"/>
+      <c r="R85" s="3"/>
+      <c r="S85" s="3"/>
+      <c r="T85" s="3"/>
+      <c r="U85" s="3"/>
+      <c r="V85" s="3"/>
+      <c r="W85" s="3"/>
+      <c r="X85" s="3"/>
+      <c r="Y85" s="3"/>
+      <c r="Z85" s="3"/>
+      <c r="AA85" s="3"/>
+    </row>
+    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E86" s="3" t="str">
+        <f>D86&amp;"05"</f>
+        <v>SS-220005</v>
+      </c>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3">
+        <v>50</v>
+      </c>
+      <c r="H86" s="3">
+        <v>60.3</v>
+      </c>
+      <c r="I86" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="J86" s="3"/>
       <c r="K86" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
+        <v>2.2145165154970788E-3</v>
+      </c>
+      <c r="L86" s="3"/>
       <c r="M86" s="3">
         <v>1</v>
       </c>
       <c r="N86" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.2145165154970788E-3</v>
       </c>
       <c r="O86" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="P86" s="3"/>
+      <c r="Q86" s="3"/>
+      <c r="R86" s="3"/>
+      <c r="S86" s="3"/>
+      <c r="T86" s="3"/>
+      <c r="U86" s="3"/>
+      <c r="V86" s="3"/>
+      <c r="W86" s="3"/>
+      <c r="X86" s="3"/>
+      <c r="Y86" s="3"/>
+      <c r="Z86" s="3"/>
+      <c r="AA86" s="3"/>
+    </row>
+    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>0.121</v>
+      </c>
+      <c r="B87" s="3">
+        <v>0.76183699999999999</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E87" s="3" t="str">
+        <f>D87&amp;1</f>
+        <v>S-60021</v>
+      </c>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3">
+        <v>100</v>
+      </c>
+      <c r="H87" s="3">
+        <v>114.3</v>
+      </c>
+      <c r="I87" s="3">
+        <v>5</v>
+      </c>
+      <c r="J87" s="3"/>
       <c r="K87" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>8.5439460665375083E-3</v>
+      </c>
+      <c r="L87" s="3"/>
+      <c r="M87" s="3">
+        <v>1</v>
+      </c>
+      <c r="N87" s="3">
+        <f t="shared" si="10"/>
+        <v>8.5439460665375083E-3</v>
+      </c>
+      <c r="O87" s="3">
+        <f t="shared" si="12"/>
+        <v>30.75820583953503</v>
+      </c>
+      <c r="P87" s="3"/>
+      <c r="Q87" s="3"/>
+      <c r="R87" s="3"/>
+      <c r="S87" s="3"/>
+      <c r="T87" s="3"/>
+      <c r="U87" s="3"/>
+      <c r="V87" s="3"/>
+      <c r="W87" s="3"/>
+      <c r="X87" s="3"/>
+      <c r="Y87" s="3"/>
+      <c r="Z87" s="3"/>
+      <c r="AA87" s="3"/>
+    </row>
+    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A88" s="3">
+        <v>0.37308622078968573</v>
+      </c>
+      <c r="B88" s="3">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G88" s="3">
+        <v>80</v>
+      </c>
+      <c r="H88" s="3">
+        <v>88.9</v>
+      </c>
+      <c r="I88" s="3">
+        <v>4</v>
+      </c>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3">
+        <f t="shared" si="6"/>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3">
+        <v>1</v>
+      </c>
+      <c r="N88" s="3">
+        <f t="shared" si="10"/>
+        <v>5.1402817537852556E-3</v>
+      </c>
+      <c r="O88" s="3">
+        <f t="shared" si="12"/>
+        <v>18.505014313626919</v>
+      </c>
+      <c r="P88" s="3"/>
+      <c r="Q88" s="3"/>
+      <c r="R88" s="3"/>
+      <c r="S88" s="3"/>
+      <c r="T88" s="3"/>
+      <c r="U88" s="3"/>
+      <c r="V88" s="3"/>
+      <c r="W88" s="3"/>
+      <c r="X88" s="3"/>
+      <c r="Y88" s="3"/>
+      <c r="Z88" s="3"/>
+      <c r="AA88" s="3"/>
+    </row>
+    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D89" s="3" t="str">
+        <f>C89&amp;"-1"</f>
+        <v>SS-800-1</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G89" s="3">
+        <v>100</v>
+      </c>
+      <c r="H89" s="3">
+        <v>114</v>
+      </c>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="3">
+        <f t="shared" si="6"/>
+        <v>1.0207034531513238E-2</v>
+      </c>
+      <c r="L89" s="3"/>
+      <c r="M89" s="3">
+        <v>1</v>
+      </c>
+      <c r="N89" s="3">
+        <f t="shared" si="10"/>
+        <v>1.0207034531513238E-2</v>
+      </c>
+      <c r="O89" s="3">
+        <f t="shared" si="12"/>
+        <v>36.745324313447661</v>
+      </c>
+      <c r="P89" s="3"/>
+      <c r="Q89" s="3"/>
+      <c r="R89" s="3"/>
+      <c r="S89" s="3"/>
+      <c r="T89" s="3"/>
+      <c r="U89" s="3"/>
+      <c r="V89" s="3"/>
+      <c r="W89" s="3"/>
+      <c r="X89" s="3"/>
+      <c r="Y89" s="3"/>
+      <c r="Z89" s="3"/>
+      <c r="AA89" s="3"/>
+    </row>
+    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D90" s="3" t="str">
+        <f>C90&amp;"-2"</f>
+        <v>SS-800-2</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G90" s="3">
+        <v>80</v>
+      </c>
+      <c r="H90" s="6">
+        <v>88.9</v>
+      </c>
+      <c r="K90" s="3">
+        <f t="shared" si="6"/>
+        <v>6.2071666189443481E-3</v>
+      </c>
+      <c r="L90" s="5"/>
+      <c r="M90" s="7">
+        <v>1</v>
+      </c>
+      <c r="N90" s="3">
+        <f t="shared" si="10"/>
+        <v>6.2071666189443481E-3</v>
+      </c>
+      <c r="O90" s="3">
+        <f t="shared" si="12"/>
+        <v>22.345799828199652</v>
+      </c>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D91" s="3" t="str">
+        <f>C91&amp;"-3"</f>
+        <v>SS-800-3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G91" s="3">
+        <v>50</v>
+      </c>
+      <c r="H91" s="6">
+        <v>60.3</v>
+      </c>
+      <c r="K91" s="1">
+        <f t="shared" si="6"/>
+        <v>2.8557784079478277E-3</v>
+      </c>
+      <c r="M91" s="8">
+        <v>1</v>
+      </c>
+      <c r="N91" s="1">
+        <f t="shared" si="10"/>
+        <v>2.8557784079478277E-3</v>
+      </c>
+      <c r="O91" s="1">
+        <f t="shared" si="12"/>
+        <v>10.280802268612179</v>
       </c>
     </row>
   </sheetData>
@@ -5392,11 +6785,11 @@
       <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N72">
-    <sortCondition ref="C40:C72"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D90:D91">
+    <sortCondition ref="D90:D91"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="71" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="29" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>